--- a/RHA_concrete_ML_dataset.xlsx
+++ b/RHA_concrete_ML_dataset.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z42"/>
+  <dimension ref="A1:Z122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4722,6 +4722,8244 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Mix1 (0% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>375</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>650</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>7</v>
+      </c>
+      <c r="R43" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Mix1 (0% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>375</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>650</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>21</v>
+      </c>
+      <c r="R44" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Mix1 (0% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>375</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>650</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>28</v>
+      </c>
+      <c r="R45" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Mix2 (5% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="K46" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="L46" t="n">
+        <v>5</v>
+      </c>
+      <c r="M46" t="n">
+        <v>650</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>7</v>
+      </c>
+      <c r="R46" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Mix2 (5% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="K47" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="L47" t="n">
+        <v>5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>650</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>21</v>
+      </c>
+      <c r="R47" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Mix2 (5% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="K48" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="L48" t="n">
+        <v>5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>650</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>28</v>
+      </c>
+      <c r="R48" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Mix3 (10% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L49" t="n">
+        <v>10</v>
+      </c>
+      <c r="M49" t="n">
+        <v>650</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>7</v>
+      </c>
+      <c r="R49" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Mix3 (10% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L50" t="n">
+        <v>10</v>
+      </c>
+      <c r="M50" t="n">
+        <v>650</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>21</v>
+      </c>
+      <c r="R50" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Mix3 (10% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L51" t="n">
+        <v>10</v>
+      </c>
+      <c r="M51" t="n">
+        <v>650</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>28</v>
+      </c>
+      <c r="R51" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Mix4 (15% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>318.75</v>
+      </c>
+      <c r="K52" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="L52" t="n">
+        <v>15</v>
+      </c>
+      <c r="M52" t="n">
+        <v>650</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>7</v>
+      </c>
+      <c r="R52" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Mix4 (15% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>318.75</v>
+      </c>
+      <c r="K53" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="L53" t="n">
+        <v>15</v>
+      </c>
+      <c r="M53" t="n">
+        <v>650</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>21</v>
+      </c>
+      <c r="R53" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Mix4 (15% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>318.75</v>
+      </c>
+      <c r="K54" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="L54" t="n">
+        <v>15</v>
+      </c>
+      <c r="M54" t="n">
+        <v>650</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>28</v>
+      </c>
+      <c r="R54" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Mix5 (20% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>300</v>
+      </c>
+      <c r="K55" t="n">
+        <v>75</v>
+      </c>
+      <c r="L55" t="n">
+        <v>20</v>
+      </c>
+      <c r="M55" t="n">
+        <v>650</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>7</v>
+      </c>
+      <c r="R55" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Mix5 (20% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>300</v>
+      </c>
+      <c r="K56" t="n">
+        <v>75</v>
+      </c>
+      <c r="L56" t="n">
+        <v>20</v>
+      </c>
+      <c r="M56" t="n">
+        <v>650</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>21</v>
+      </c>
+      <c r="R56" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Mix5 (20% RHA, no SF)</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>300</v>
+      </c>
+      <c r="K57" t="n">
+        <v>75</v>
+      </c>
+      <c r="L57" t="n">
+        <v>20</v>
+      </c>
+      <c r="M57" t="n">
+        <v>650</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>28</v>
+      </c>
+      <c r="R57" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Mix6 (5% RHA + 0.5% SF + SP)</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="K58" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="L58" t="n">
+        <v>5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>650</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Hooked steel fibers 1.875 kg/m3 (0.5% vol); superplasticizer Conplast SP430 2.50 kg/m3</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>7</v>
+      </c>
+      <c r="R58" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Mix6 (5% RHA + 0.5% SF + SP)</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="K59" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="L59" t="n">
+        <v>5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>650</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Hooked steel fibers 1.875 kg/m3 (0.5% vol); superplasticizer Conplast SP430 2.50 kg/m3</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>21</v>
+      </c>
+      <c r="R59" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Mix6 (5% RHA + 0.5% SF + SP)</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="K60" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="L60" t="n">
+        <v>5</v>
+      </c>
+      <c r="M60" t="n">
+        <v>650</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Hooked steel fibers 1.875 kg/m3 (0.5% vol); superplasticizer Conplast SP430 2.50 kg/m3</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>28</v>
+      </c>
+      <c r="R60" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Mix7 (10% RHA + 1.0% SF + SP)</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L61" t="n">
+        <v>10</v>
+      </c>
+      <c r="M61" t="n">
+        <v>650</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Hooked steel fibers 3.75 kg/m3 (1.0% vol); superplasticizer 2.50 kg/m3</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>7</v>
+      </c>
+      <c r="R61" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Mix7 (10% RHA + 1.0% SF + SP)</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L62" t="n">
+        <v>10</v>
+      </c>
+      <c r="M62" t="n">
+        <v>650</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Hooked steel fibers 3.75 kg/m3 (1.0% vol); superplasticizer 2.50 kg/m3</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>21</v>
+      </c>
+      <c r="R62" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Mix7 (10% RHA + 1.0% SF + SP)</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L63" t="n">
+        <v>10</v>
+      </c>
+      <c r="M63" t="n">
+        <v>650</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Hooked steel fibers 3.75 kg/m3 (1.0% vol); superplasticizer 2.50 kg/m3</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>28</v>
+      </c>
+      <c r="R63" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Mix8 (15% RHA + 1.5% SF + SP)</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>318.75</v>
+      </c>
+      <c r="K64" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="L64" t="n">
+        <v>15</v>
+      </c>
+      <c r="M64" t="n">
+        <v>650</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Hooked steel fibers 5.625 kg/m3 (1.5% vol); superplasticizer 2.50 kg/m3</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>7</v>
+      </c>
+      <c r="R64" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Mix8 (15% RHA + 1.5% SF + SP)</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>318.75</v>
+      </c>
+      <c r="K65" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="L65" t="n">
+        <v>15</v>
+      </c>
+      <c r="M65" t="n">
+        <v>650</v>
+      </c>
+      <c r="N65" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Hooked steel fibers 5.625 kg/m3 (1.5% vol); superplasticizer 2.50 kg/m3</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>21</v>
+      </c>
+      <c r="R65" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Mix8 (15% RHA + 1.5% SF + SP)</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>318.75</v>
+      </c>
+      <c r="K66" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="L66" t="n">
+        <v>15</v>
+      </c>
+      <c r="M66" t="n">
+        <v>650</v>
+      </c>
+      <c r="N66" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Hooked steel fibers 5.625 kg/m3 (1.5% vol); superplasticizer 2.50 kg/m3</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>28</v>
+      </c>
+      <c r="R66" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Mix9 (20% RHA + 2.0% SF + SP)</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>300</v>
+      </c>
+      <c r="K67" t="n">
+        <v>75</v>
+      </c>
+      <c r="L67" t="n">
+        <v>20</v>
+      </c>
+      <c r="M67" t="n">
+        <v>650</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Hooked steel fibers 7.5 kg/m3 (2.0% vol); superplasticizer 2.50 kg/m3</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>7</v>
+      </c>
+      <c r="R67" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Mix9 (20% RHA + 2.0% SF + SP)</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>300</v>
+      </c>
+      <c r="K68" t="n">
+        <v>75</v>
+      </c>
+      <c r="L68" t="n">
+        <v>20</v>
+      </c>
+      <c r="M68" t="n">
+        <v>650</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Hooked steel fibers 7.5 kg/m3 (2.0% vol); superplasticizer 2.50 kg/m3</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>21</v>
+      </c>
+      <c r="R68" t="n">
+        <v>14.37</v>
+      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2021_01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Effect of Incorporation of Rice Husk Ash Instead of Cement on the Performance of Steel Fibers Reinforced Concrete</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Zaid, Ahmad, Siddique, Aslam</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Pakistan (Risalpur; sand from Lawrancepur, coarse agg from Margalla)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Rice milling industry, Pakistan; husk burnt ~700C</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Concrete (1:1.5:3) +/- hooked-end steel fibers + superplasticizer</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Mix9 (20% RHA + 2.0% SF + SP)</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>300</v>
+      </c>
+      <c r="K69" t="n">
+        <v>75</v>
+      </c>
+      <c r="L69" t="n">
+        <v>20</v>
+      </c>
+      <c r="M69" t="n">
+        <v>650</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1310</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Hooked steel fibers 7.5 kg/m3 (2.0% vol); superplasticizer 2.50 kg/m3</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>28</v>
+      </c>
+      <c r="R69" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>partial (strengths reported as control psi + % reductions in text; figures only for plots)</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 6 (verbatim); strengths COMPUTED from stated control psi (Fig text) x stated % reductions, psi-&gt;MPa (x0.00689476)</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Mix 2 cement printed as 365.25 in OCR; correct value 356.25 = 375*0.95 (RHA 18.75=5%). Binder held at 375 kg/m3; w/c=165/375=0.44. Strengths NOT tabulated: control (no SF) comp 2554/2750/2910 psi at 7/21/28d, split 265/295/335 psi; control (with SF+SP) split 258/279/294 psi (comp control reused 2554/2750/2910). Absolute MPa values back-computed from those controls and the explicit % reductions in text; flag as computed.</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Table 6 quantification of materials. Comp (no SF) decreases vs control: 5%:5.4/3.6/3.9; 10%:12.1/13.2/13.5; 15%:20.3/21.7/23.4; 20%:25.4/26.1/28.5. Split (no SF) decreases: 5%:4.4/4.2/3.8; 10%:9.6/11.9/13.0; 15%:16.1/17.2/19.4; 20%:25.2/26.3/26.9. Comp (SF+SP) decreases: 5%:4.6/3.3/3.0; 10%:9.4/10.1/10.5; 15%:15.2/17.0/17.3; 20%:22.4/24.2/25.5. Split (SF+SP) control 258/279/294 psi; decreases 5%:3.5/3.8/3.0; 10%:7.2/7.6/6.8; 15%:14.3/14.9/15.3; 20%:21.9/22.8/23.3.</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>2021/01_Effect_of_Incorporation_of_Rice_Husk_Ash_Instead_of_Cement_on_the_Performance_of_Steel_Fibers_Reinforced_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2021_02</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Performance of Sustainable Green Concrete Incorporated with Fly Ash, Rice Husk Ash, and Stone Dust</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Siddika, Amin, Rayhan, Islam, Al Mamun, Alyousef, Amran</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Bangladesh (Pabna University of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>RHA from different mills and factories, Bangladesh (ground, 150 mesh; uncontrolled burning, high carbon)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Concrete (1:2:4) with FA+RHA replacing cement, stone dust replacing sand</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>OPC+RHA+FA</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>F0R0S0 (control)</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>380</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>760</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1520</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>none (FA 0, SD 0)</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>28</v>
+      </c>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>figure_only for comp &amp; split tensile; flexural computed from stated %+range</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 2 (verbatim). Flexural COMPUTED from stated reductions (16.4/12.93/9.48/8.62%) and stated range 2.91-3.18 MPa =&gt; control 3.48. Comp &amp; split absolute only in Fig 5/8 (not tabulated, no control absolute) -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Binder (cement+FA+RHA) = 380 kg/m3 for all mixes; water 190 kg/m3 -&gt; w/binder 0.5. RHA% = RHA/(binder). FA also replaces cement; stone dust (SD) replaces fine aggregate. Comp strength reductions vs control: 11.42/3.99/6.50/3.49% (F5R10S0/F10R5S0/F10R10S5/F5R5S10) but control comp absolute not given numerically -&gt; comp left blank. Split reductions 14.16/9.74/8.41/7.52% similarly figure-only.</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Table 2 mix proportion kg/m3. Flexural: 'between 2.91 and 3.18 MPa', reductions 16.4/12.93/9.48/8.62% =&gt; control 3.48, F5R10S0 2.91, F10R5S0 3.03, F10R10S5 3.15, F5R5S10 3.18. All tests at 28 days.</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>2021/02_PERFORMANCE_OF_SUSTAINABLE_GREEN_CONCRETE_INCORPORATED_WITH_FLY_ASH_RICE_HUSK_ASH_AND_STONE_DUST.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2021_02</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Performance of Sustainable Green Concrete Incorporated with Fly Ash, Rice Husk Ash, and Stone Dust</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Siddika, Amin, Rayhan, Islam, Al Mamun, Alyousef, Amran</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Bangladesh (Pabna University of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>RHA from different mills and factories, Bangladesh (ground, 150 mesh; uncontrolled burning, high carbon)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Concrete (1:2:4) with FA+RHA replacing cement, stone dust replacing sand</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>OPC+RHA+FA</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>F5R10S0</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>323</v>
+      </c>
+      <c r="K71" t="n">
+        <v>38</v>
+      </c>
+      <c r="L71" t="n">
+        <v>10</v>
+      </c>
+      <c r="M71" t="n">
+        <v>760</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1520</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Fly ash 19 kg/m3 (5%); stone dust 0</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>28</v>
+      </c>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>figure_only for comp &amp; split tensile; flexural computed from stated %+range</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 2 (verbatim). Flexural COMPUTED from stated reductions (16.4/12.93/9.48/8.62%) and stated range 2.91-3.18 MPa =&gt; control 3.48. Comp &amp; split absolute only in Fig 5/8 (not tabulated, no control absolute) -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Binder (cement+FA+RHA) = 380 kg/m3 for all mixes; water 190 kg/m3 -&gt; w/binder 0.5. RHA% = RHA/(binder). FA also replaces cement; stone dust (SD) replaces fine aggregate. Comp strength reductions vs control: 11.42/3.99/6.50/3.49% (F5R10S0/F10R5S0/F10R10S5/F5R5S10) but control comp absolute not given numerically -&gt; comp left blank. Split reductions 14.16/9.74/8.41/7.52% similarly figure-only.</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Table 2 mix proportion kg/m3. Flexural: 'between 2.91 and 3.18 MPa', reductions 16.4/12.93/9.48/8.62% =&gt; control 3.48, F5R10S0 2.91, F10R5S0 3.03, F10R10S5 3.15, F5R5S10 3.18. All tests at 28 days.</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>2021/02_PERFORMANCE_OF_SUSTAINABLE_GREEN_CONCRETE_INCORPORATED_WITH_FLY_ASH_RICE_HUSK_ASH_AND_STONE_DUST.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2021_02</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Performance of Sustainable Green Concrete Incorporated with Fly Ash, Rice Husk Ash, and Stone Dust</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Siddika, Amin, Rayhan, Islam, Al Mamun, Alyousef, Amran</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Bangladesh (Pabna University of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>RHA from different mills and factories, Bangladesh (ground, 150 mesh; uncontrolled burning, high carbon)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Concrete (1:2:4) with FA+RHA replacing cement, stone dust replacing sand</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>OPC+RHA+FA</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>F10R5S0</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>323</v>
+      </c>
+      <c r="K72" t="n">
+        <v>19</v>
+      </c>
+      <c r="L72" t="n">
+        <v>5</v>
+      </c>
+      <c r="M72" t="n">
+        <v>760</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1520</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Fly ash 38 kg/m3 (10%); stone dust 0</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>28</v>
+      </c>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>figure_only for comp &amp; split tensile; flexural computed from stated %+range</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 2 (verbatim). Flexural COMPUTED from stated reductions (16.4/12.93/9.48/8.62%) and stated range 2.91-3.18 MPa =&gt; control 3.48. Comp &amp; split absolute only in Fig 5/8 (not tabulated, no control absolute) -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Binder (cement+FA+RHA) = 380 kg/m3 for all mixes; water 190 kg/m3 -&gt; w/binder 0.5. RHA% = RHA/(binder). FA also replaces cement; stone dust (SD) replaces fine aggregate. Comp strength reductions vs control: 11.42/3.99/6.50/3.49% (F5R10S0/F10R5S0/F10R10S5/F5R5S10) but control comp absolute not given numerically -&gt; comp left blank. Split reductions 14.16/9.74/8.41/7.52% similarly figure-only.</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Table 2 mix proportion kg/m3. Flexural: 'between 2.91 and 3.18 MPa', reductions 16.4/12.93/9.48/8.62% =&gt; control 3.48, F5R10S0 2.91, F10R5S0 3.03, F10R10S5 3.15, F5R5S10 3.18. All tests at 28 days.</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>2021/02_PERFORMANCE_OF_SUSTAINABLE_GREEN_CONCRETE_INCORPORATED_WITH_FLY_ASH_RICE_HUSK_ASH_AND_STONE_DUST.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2021_02</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Performance of Sustainable Green Concrete Incorporated with Fly Ash, Rice Husk Ash, and Stone Dust</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Siddika, Amin, Rayhan, Islam, Al Mamun, Alyousef, Amran</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Bangladesh (Pabna University of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>RHA from different mills and factories, Bangladesh (ground, 150 mesh; uncontrolled burning, high carbon)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Concrete (1:2:4) with FA+RHA replacing cement, stone dust replacing sand</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>OPC+RHA+FA</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>F10R10S5</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>304</v>
+      </c>
+      <c r="K73" t="n">
+        <v>38</v>
+      </c>
+      <c r="L73" t="n">
+        <v>10</v>
+      </c>
+      <c r="M73" t="n">
+        <v>722</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1520</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Fly ash 38 kg/m3 (10%); stone dust 38 kg/m3 (5% of sand)</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>28</v>
+      </c>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>figure_only for comp &amp; split tensile; flexural computed from stated %+range</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 2 (verbatim). Flexural COMPUTED from stated reductions (16.4/12.93/9.48/8.62%) and stated range 2.91-3.18 MPa =&gt; control 3.48. Comp &amp; split absolute only in Fig 5/8 (not tabulated, no control absolute) -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Binder (cement+FA+RHA) = 380 kg/m3 for all mixes; water 190 kg/m3 -&gt; w/binder 0.5. RHA% = RHA/(binder). FA also replaces cement; stone dust (SD) replaces fine aggregate. Comp strength reductions vs control: 11.42/3.99/6.50/3.49% (F5R10S0/F10R5S0/F10R10S5/F5R5S10) but control comp absolute not given numerically -&gt; comp left blank. Split reductions 14.16/9.74/8.41/7.52% similarly figure-only.</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>Table 2 mix proportion kg/m3. Flexural: 'between 2.91 and 3.18 MPa', reductions 16.4/12.93/9.48/8.62% =&gt; control 3.48, F5R10S0 2.91, F10R5S0 3.03, F10R10S5 3.15, F5R5S10 3.18. All tests at 28 days.</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>2021/02_PERFORMANCE_OF_SUSTAINABLE_GREEN_CONCRETE_INCORPORATED_WITH_FLY_ASH_RICE_HUSK_ASH_AND_STONE_DUST.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2021_02</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Performance of Sustainable Green Concrete Incorporated with Fly Ash, Rice Husk Ash, and Stone Dust</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Siddika, Amin, Rayhan, Islam, Al Mamun, Alyousef, Amran</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Bangladesh (Pabna University of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>RHA from different mills and factories, Bangladesh (ground, 150 mesh; uncontrolled burning, high carbon)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Concrete (1:2:4) with FA+RHA replacing cement, stone dust replacing sand</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>OPC+RHA+FA</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>F5R5S10</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>342</v>
+      </c>
+      <c r="K74" t="n">
+        <v>19</v>
+      </c>
+      <c r="L74" t="n">
+        <v>5</v>
+      </c>
+      <c r="M74" t="n">
+        <v>684</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1520</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Fly ash 19 kg/m3 (5%); stone dust 76 kg/m3 (10% of sand)</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>28</v>
+      </c>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>figure_only for comp &amp; split tensile; flexural computed from stated %+range</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>kg/m3 from Table 2 (verbatim). Flexural COMPUTED from stated reductions (16.4/12.93/9.48/8.62%) and stated range 2.91-3.18 MPa =&gt; control 3.48. Comp &amp; split absolute only in Fig 5/8 (not tabulated, no control absolute) -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Binder (cement+FA+RHA) = 380 kg/m3 for all mixes; water 190 kg/m3 -&gt; w/binder 0.5. RHA% = RHA/(binder). FA also replaces cement; stone dust (SD) replaces fine aggregate. Comp strength reductions vs control: 11.42/3.99/6.50/3.49% (F5R10S0/F10R5S0/F10R10S5/F5R5S10) but control comp absolute not given numerically -&gt; comp left blank. Split reductions 14.16/9.74/8.41/7.52% similarly figure-only.</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Table 2 mix proportion kg/m3. Flexural: 'between 2.91 and 3.18 MPa', reductions 16.4/12.93/9.48/8.62% =&gt; control 3.48, F5R10S0 2.91, F10R5S0 3.03, F10R10S5 3.15, F5R5S10 3.18. All tests at 28 days.</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>2021/02_PERFORMANCE_OF_SUSTAINABLE_GREEN_CONCRETE_INCORPORATED_WITH_FLY_ASH_RICE_HUSK_ASH_AND_STONE_DUST.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Partial replacement of cement with rice husk ash in concrete production: an exploratory cost-benefit analysis for low-income communities</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Muleya, Muwila, Tembo, Lungu</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Zambia (Copperbelt University)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Rice husk from National Milling Company (NMC), Zambia; burnt in incinerator at 600C, pulverised</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Concrete (normal), two w/c series 0.3 and 0.5; no superplasticizer</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Mix1 (0% RHA, w/c 0.3)</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>400</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>600</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1200</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>28</v>
+      </c>
+      <c r="R75" t="n">
+        <v>33</v>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>tabulated (Table 5; compressive at 28 days)</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Cement kg/m3 from Table 5 design binder (400 for 0.3 series, 270 for 0.5 series), split into cement+RHA by % (binder constant per series). Fine/coarse/water kg/m3 COMPUTED from batch masses (sand 13.2 kg, stone 26.4 kg, water 4 or 4.57 kg) divided by batch volume (=binder_batch/binder_density: 8.8/400=0.022 m3 for 0.3; 7.74/270=0.02867 m3 for 0.5). Comp strength verbatim Table 5.</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Only 28-day strengths for main mixes (trial 7-day not tabulated). Stated w/c (0.3, 0.5) is nominal/design; batch-derived water/binder differs (4/8.8=0.45 for 0.3 series; 4.57/7.74=0.59 for 0.5 series) - recorded nominal w/c, see this note. Aggregate kg/m3 computed (sand 600 / stone 1200 for 0.3 series; sand 460 / stone 921 for 0.5 series). No flexural or split tensile tested.</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Table 5: 0.3 series binder 8.8 kg batch=400 kg/m3, comp 33/25/16 MPa at RHA 0/10/20%; 0.5 series binder 7.74 kg=270 kg/m3, comp 25/22/18/14 MPa at RHA 0/10/20/30%. Sand 13.2 kg, stone 26.4 kg per batch (all mixes).</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>2021/03_Partial_replacement_of_cement_with_rice_husk_ash_in_concrete_production_an_exploratory_cost-benefit_analysis_for_low-inc.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Partial replacement of cement with rice husk ash in concrete production: an exploratory cost-benefit analysis for low-income communities</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Muleya, Muwila, Tembo, Lungu</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Zambia (Copperbelt University)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Rice husk from National Milling Company (NMC), Zambia; burnt in incinerator at 600C, pulverised</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Concrete (normal), two w/c series 0.3 and 0.5; no superplasticizer</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Mix2 (10% RHA, w/c 0.3)</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>360</v>
+      </c>
+      <c r="K76" t="n">
+        <v>40</v>
+      </c>
+      <c r="L76" t="n">
+        <v>10</v>
+      </c>
+      <c r="M76" t="n">
+        <v>600</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1200</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>28</v>
+      </c>
+      <c r="R76" t="n">
+        <v>25</v>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>tabulated (Table 5; compressive at 28 days)</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Cement kg/m3 from Table 5 design binder (400 for 0.3 series, 270 for 0.5 series), split into cement+RHA by % (binder constant per series). Fine/coarse/water kg/m3 COMPUTED from batch masses (sand 13.2 kg, stone 26.4 kg, water 4 or 4.57 kg) divided by batch volume (=binder_batch/binder_density: 8.8/400=0.022 m3 for 0.3; 7.74/270=0.02867 m3 for 0.5). Comp strength verbatim Table 5.</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Only 28-day strengths for main mixes (trial 7-day not tabulated). Stated w/c (0.3, 0.5) is nominal/design; batch-derived water/binder differs (4/8.8=0.45 for 0.3 series; 4.57/7.74=0.59 for 0.5 series) - recorded nominal w/c, see this note. Aggregate kg/m3 computed (sand 600 / stone 1200 for 0.3 series; sand 460 / stone 921 for 0.5 series). No flexural or split tensile tested.</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Table 5: 0.3 series binder 8.8 kg batch=400 kg/m3, comp 33/25/16 MPa at RHA 0/10/20%; 0.5 series binder 7.74 kg=270 kg/m3, comp 25/22/18/14 MPa at RHA 0/10/20/30%. Sand 13.2 kg, stone 26.4 kg per batch (all mixes).</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>2021/03_Partial_replacement_of_cement_with_rice_husk_ash_in_concrete_production_an_exploratory_cost-benefit_analysis_for_low-inc.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Partial replacement of cement with rice husk ash in concrete production: an exploratory cost-benefit analysis for low-income communities</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Muleya, Muwila, Tembo, Lungu</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Zambia (Copperbelt University)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Rice husk from National Milling Company (NMC), Zambia; burnt in incinerator at 600C, pulverised</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Concrete (normal), two w/c series 0.3 and 0.5; no superplasticizer</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Mix3 (20% RHA, w/c 0.3)</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>320</v>
+      </c>
+      <c r="K77" t="n">
+        <v>80</v>
+      </c>
+      <c r="L77" t="n">
+        <v>20</v>
+      </c>
+      <c r="M77" t="n">
+        <v>600</v>
+      </c>
+      <c r="N77" t="n">
+        <v>1200</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>28</v>
+      </c>
+      <c r="R77" t="n">
+        <v>16</v>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>tabulated (Table 5; compressive at 28 days)</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Cement kg/m3 from Table 5 design binder (400 for 0.3 series, 270 for 0.5 series), split into cement+RHA by % (binder constant per series). Fine/coarse/water kg/m3 COMPUTED from batch masses (sand 13.2 kg, stone 26.4 kg, water 4 or 4.57 kg) divided by batch volume (=binder_batch/binder_density: 8.8/400=0.022 m3 for 0.3; 7.74/270=0.02867 m3 for 0.5). Comp strength verbatim Table 5.</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Only 28-day strengths for main mixes (trial 7-day not tabulated). Stated w/c (0.3, 0.5) is nominal/design; batch-derived water/binder differs (4/8.8=0.45 for 0.3 series; 4.57/7.74=0.59 for 0.5 series) - recorded nominal w/c, see this note. Aggregate kg/m3 computed (sand 600 / stone 1200 for 0.3 series; sand 460 / stone 921 for 0.5 series). No flexural or split tensile tested.</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>Table 5: 0.3 series binder 8.8 kg batch=400 kg/m3, comp 33/25/16 MPa at RHA 0/10/20%; 0.5 series binder 7.74 kg=270 kg/m3, comp 25/22/18/14 MPa at RHA 0/10/20/30%. Sand 13.2 kg, stone 26.4 kg per batch (all mixes).</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>2021/03_Partial_replacement_of_cement_with_rice_husk_ash_in_concrete_production_an_exploratory_cost-benefit_analysis_for_low-inc.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Partial replacement of cement with rice husk ash in concrete production: an exploratory cost-benefit analysis for low-income communities</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Muleya, Muwila, Tembo, Lungu</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Zambia (Copperbelt University)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Rice husk from National Milling Company (NMC), Zambia; burnt in incinerator at 600C, pulverised</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Concrete (normal), two w/c series 0.3 and 0.5; no superplasticizer</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Mix4 (0% RHA, w/c 0.5)</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>270</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>460</v>
+      </c>
+      <c r="N78" t="n">
+        <v>921</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>28</v>
+      </c>
+      <c r="R78" t="n">
+        <v>25</v>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>tabulated (Table 5; compressive at 28 days)</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Cement kg/m3 from Table 5 design binder (400 for 0.3 series, 270 for 0.5 series), split into cement+RHA by % (binder constant per series). Fine/coarse/water kg/m3 COMPUTED from batch masses (sand 13.2 kg, stone 26.4 kg, water 4 or 4.57 kg) divided by batch volume (=binder_batch/binder_density: 8.8/400=0.022 m3 for 0.3; 7.74/270=0.02867 m3 for 0.5). Comp strength verbatim Table 5.</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Only 28-day strengths for main mixes (trial 7-day not tabulated). Stated w/c (0.3, 0.5) is nominal/design; batch-derived water/binder differs (4/8.8=0.45 for 0.3 series; 4.57/7.74=0.59 for 0.5 series) - recorded nominal w/c, see this note. Aggregate kg/m3 computed (sand 600 / stone 1200 for 0.3 series; sand 460 / stone 921 for 0.5 series). No flexural or split tensile tested.</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Table 5: 0.3 series binder 8.8 kg batch=400 kg/m3, comp 33/25/16 MPa at RHA 0/10/20%; 0.5 series binder 7.74 kg=270 kg/m3, comp 25/22/18/14 MPa at RHA 0/10/20/30%. Sand 13.2 kg, stone 26.4 kg per batch (all mixes).</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>2021/03_Partial_replacement_of_cement_with_rice_husk_ash_in_concrete_production_an_exploratory_cost-benefit_analysis_for_low-inc.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Partial replacement of cement with rice husk ash in concrete production: an exploratory cost-benefit analysis for low-income communities</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Muleya, Muwila, Tembo, Lungu</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Zambia (Copperbelt University)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Rice husk from National Milling Company (NMC), Zambia; burnt in incinerator at 600C, pulverised</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Concrete (normal), two w/c series 0.3 and 0.5; no superplasticizer</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Mix5 (10% RHA, w/c 0.5)</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>243</v>
+      </c>
+      <c r="K79" t="n">
+        <v>27</v>
+      </c>
+      <c r="L79" t="n">
+        <v>10</v>
+      </c>
+      <c r="M79" t="n">
+        <v>460</v>
+      </c>
+      <c r="N79" t="n">
+        <v>921</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>28</v>
+      </c>
+      <c r="R79" t="n">
+        <v>22</v>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>tabulated (Table 5; compressive at 28 days)</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Cement kg/m3 from Table 5 design binder (400 for 0.3 series, 270 for 0.5 series), split into cement+RHA by % (binder constant per series). Fine/coarse/water kg/m3 COMPUTED from batch masses (sand 13.2 kg, stone 26.4 kg, water 4 or 4.57 kg) divided by batch volume (=binder_batch/binder_density: 8.8/400=0.022 m3 for 0.3; 7.74/270=0.02867 m3 for 0.5). Comp strength verbatim Table 5.</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Only 28-day strengths for main mixes (trial 7-day not tabulated). Stated w/c (0.3, 0.5) is nominal/design; batch-derived water/binder differs (4/8.8=0.45 for 0.3 series; 4.57/7.74=0.59 for 0.5 series) - recorded nominal w/c, see this note. Aggregate kg/m3 computed (sand 600 / stone 1200 for 0.3 series; sand 460 / stone 921 for 0.5 series). No flexural or split tensile tested.</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Table 5: 0.3 series binder 8.8 kg batch=400 kg/m3, comp 33/25/16 MPa at RHA 0/10/20%; 0.5 series binder 7.74 kg=270 kg/m3, comp 25/22/18/14 MPa at RHA 0/10/20/30%. Sand 13.2 kg, stone 26.4 kg per batch (all mixes).</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>2021/03_Partial_replacement_of_cement_with_rice_husk_ash_in_concrete_production_an_exploratory_cost-benefit_analysis_for_low-inc.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Partial replacement of cement with rice husk ash in concrete production: an exploratory cost-benefit analysis for low-income communities</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Muleya, Muwila, Tembo, Lungu</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Zambia (Copperbelt University)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Rice husk from National Milling Company (NMC), Zambia; burnt in incinerator at 600C, pulverised</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Concrete (normal), two w/c series 0.3 and 0.5; no superplasticizer</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Mix6 (20% RHA, w/c 0.5)</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>216</v>
+      </c>
+      <c r="K80" t="n">
+        <v>54</v>
+      </c>
+      <c r="L80" t="n">
+        <v>20</v>
+      </c>
+      <c r="M80" t="n">
+        <v>460</v>
+      </c>
+      <c r="N80" t="n">
+        <v>921</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>28</v>
+      </c>
+      <c r="R80" t="n">
+        <v>18</v>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>tabulated (Table 5; compressive at 28 days)</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Cement kg/m3 from Table 5 design binder (400 for 0.3 series, 270 for 0.5 series), split into cement+RHA by % (binder constant per series). Fine/coarse/water kg/m3 COMPUTED from batch masses (sand 13.2 kg, stone 26.4 kg, water 4 or 4.57 kg) divided by batch volume (=binder_batch/binder_density: 8.8/400=0.022 m3 for 0.3; 7.74/270=0.02867 m3 for 0.5). Comp strength verbatim Table 5.</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Only 28-day strengths for main mixes (trial 7-day not tabulated). Stated w/c (0.3, 0.5) is nominal/design; batch-derived water/binder differs (4/8.8=0.45 for 0.3 series; 4.57/7.74=0.59 for 0.5 series) - recorded nominal w/c, see this note. Aggregate kg/m3 computed (sand 600 / stone 1200 for 0.3 series; sand 460 / stone 921 for 0.5 series). No flexural or split tensile tested.</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Table 5: 0.3 series binder 8.8 kg batch=400 kg/m3, comp 33/25/16 MPa at RHA 0/10/20%; 0.5 series binder 7.74 kg=270 kg/m3, comp 25/22/18/14 MPa at RHA 0/10/20/30%. Sand 13.2 kg, stone 26.4 kg per batch (all mixes).</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>2021/03_Partial_replacement_of_cement_with_rice_husk_ash_in_concrete_production_an_exploratory_cost-benefit_analysis_for_low-inc.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Partial replacement of cement with rice husk ash in concrete production: an exploratory cost-benefit analysis for low-income communities</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Muleya, Muwila, Tembo, Lungu</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Zambia (Copperbelt University)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Rice husk from National Milling Company (NMC), Zambia; burnt in incinerator at 600C, pulverised</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Concrete (normal), two w/c series 0.3 and 0.5; no superplasticizer</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Mix7 (30% RHA, w/c 0.5)</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>189</v>
+      </c>
+      <c r="K81" t="n">
+        <v>81</v>
+      </c>
+      <c r="L81" t="n">
+        <v>30</v>
+      </c>
+      <c r="M81" t="n">
+        <v>460</v>
+      </c>
+      <c r="N81" t="n">
+        <v>921</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>28</v>
+      </c>
+      <c r="R81" t="n">
+        <v>14</v>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>tabulated (Table 5; compressive at 28 days)</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Cement kg/m3 from Table 5 design binder (400 for 0.3 series, 270 for 0.5 series), split into cement+RHA by % (binder constant per series). Fine/coarse/water kg/m3 COMPUTED from batch masses (sand 13.2 kg, stone 26.4 kg, water 4 or 4.57 kg) divided by batch volume (=binder_batch/binder_density: 8.8/400=0.022 m3 for 0.3; 7.74/270=0.02867 m3 for 0.5). Comp strength verbatim Table 5.</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Only 28-day strengths for main mixes (trial 7-day not tabulated). Stated w/c (0.3, 0.5) is nominal/design; batch-derived water/binder differs (4/8.8=0.45 for 0.3 series; 4.57/7.74=0.59 for 0.5 series) - recorded nominal w/c, see this note. Aggregate kg/m3 computed (sand 600 / stone 1200 for 0.3 series; sand 460 / stone 921 for 0.5 series). No flexural or split tensile tested.</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Table 5: 0.3 series binder 8.8 kg batch=400 kg/m3, comp 33/25/16 MPa at RHA 0/10/20%; 0.5 series binder 7.74 kg=270 kg/m3, comp 25/22/18/14 MPa at RHA 0/10/20/30%. Sand 13.2 kg, stone 26.4 kg per batch (all mixes).</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>2021/03_Partial_replacement_of_cement_with_rice_husk_ash_in_concrete_production_an_exploratory_cost-benefit_analysis_for_low-inc.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2021_05</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>A Study on Experimental Investigation Using Cement Concrete with Varying Percentage of Rice Husk Ash</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Valli, Dhevasenaa</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>India (Govt College of Engineering, Srirangam, Trichy, Tamil Nadu)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Not specified; RHA silica 92.1%, bulk density 104.9 kg/m3, sp.gr 1.96</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Concrete (IS mix design, w/c 0.42)</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Conventional (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>442.86</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>725.11</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1429.61</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>7</v>
+      </c>
+      <c r="R82" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>tabulated (avg of 3 trials at 7/14/28 days)</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>kg/m3 from mix proportion table (verbatim). Comp avg from Tables 10.1-10.4; split tensile from Table 8.6 (verbatim).</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Binder (cement+RHA)=442.86 kg/m3 for all. Conventional (0% RHA) mix proportions assumed same aggregates/water (only 10/20/30% rows tabulated). Paper keyword mentions quarry dust but mix table lists fine aggregate 725.11 kg/m3 (quarry dust likely used as fine aggregate). 28-day split tensile of control 5.50 MPa is unusually high - recorded as-reported. No flexural.</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Mix table (w/c 0.42): 10% cement 398.58/RHA 44.28; 20% cement 354.3/RHA 88.56; 30% cement 310.02/RHA 132.84; fine 725.11, coarse 1429.61, water 186. Comp avg: 0%:22.1/30.6/33.66; 10%:19.84/25.48/32.87; 20%:15.11/19.11/27.48; 30%:10.81/14.92/19.35. Split (Table 8.6): 0%:1.45/2.50/5.50; 10%:1.32/2.40/5.21; 20%:0.71/1.55/3.21; 30%:0.25/0.56/1.82.</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>2021/05_A_STUDY_ON_EXPERIMENTAL_INVESTIGATION_USING_CEMENT_CONCRETE_WITH_VARIYING_PERCENTAGE_OF_RICE_HUSK_ASH.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2021_05</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>A Study on Experimental Investigation Using Cement Concrete with Varying Percentage of Rice Husk Ash</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Valli, Dhevasenaa</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>India (Govt College of Engineering, Srirangam, Trichy, Tamil Nadu)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Not specified; RHA silica 92.1%, bulk density 104.9 kg/m3, sp.gr 1.96</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Concrete (IS mix design, w/c 0.42)</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Conventional (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>442.86</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>725.11</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1429.61</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>14</v>
+      </c>
+      <c r="R83" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>tabulated (avg of 3 trials at 7/14/28 days)</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>kg/m3 from mix proportion table (verbatim). Comp avg from Tables 10.1-10.4; split tensile from Table 8.6 (verbatim).</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Binder (cement+RHA)=442.86 kg/m3 for all. Conventional (0% RHA) mix proportions assumed same aggregates/water (only 10/20/30% rows tabulated). Paper keyword mentions quarry dust but mix table lists fine aggregate 725.11 kg/m3 (quarry dust likely used as fine aggregate). 28-day split tensile of control 5.50 MPa is unusually high - recorded as-reported. No flexural.</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Mix table (w/c 0.42): 10% cement 398.58/RHA 44.28; 20% cement 354.3/RHA 88.56; 30% cement 310.02/RHA 132.84; fine 725.11, coarse 1429.61, water 186. Comp avg: 0%:22.1/30.6/33.66; 10%:19.84/25.48/32.87; 20%:15.11/19.11/27.48; 30%:10.81/14.92/19.35. Split (Table 8.6): 0%:1.45/2.50/5.50; 10%:1.32/2.40/5.21; 20%:0.71/1.55/3.21; 30%:0.25/0.56/1.82.</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>2021/05_A_STUDY_ON_EXPERIMENTAL_INVESTIGATION_USING_CEMENT_CONCRETE_WITH_VARIYING_PERCENTAGE_OF_RICE_HUSK_ASH.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2021_05</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>A Study on Experimental Investigation Using Cement Concrete with Varying Percentage of Rice Husk Ash</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Valli, Dhevasenaa</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>India (Govt College of Engineering, Srirangam, Trichy, Tamil Nadu)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Not specified; RHA silica 92.1%, bulk density 104.9 kg/m3, sp.gr 1.96</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Concrete (IS mix design, w/c 0.42)</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Conventional (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>442.86</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>725.11</v>
+      </c>
+      <c r="N84" t="n">
+        <v>1429.61</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>28</v>
+      </c>
+      <c r="R84" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>tabulated (avg of 3 trials at 7/14/28 days)</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>kg/m3 from mix proportion table (verbatim). Comp avg from Tables 10.1-10.4; split tensile from Table 8.6 (verbatim).</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Binder (cement+RHA)=442.86 kg/m3 for all. Conventional (0% RHA) mix proportions assumed same aggregates/water (only 10/20/30% rows tabulated). Paper keyword mentions quarry dust but mix table lists fine aggregate 725.11 kg/m3 (quarry dust likely used as fine aggregate). 28-day split tensile of control 5.50 MPa is unusually high - recorded as-reported. No flexural.</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Mix table (w/c 0.42): 10% cement 398.58/RHA 44.28; 20% cement 354.3/RHA 88.56; 30% cement 310.02/RHA 132.84; fine 725.11, coarse 1429.61, water 186. Comp avg: 0%:22.1/30.6/33.66; 10%:19.84/25.48/32.87; 20%:15.11/19.11/27.48; 30%:10.81/14.92/19.35. Split (Table 8.6): 0%:1.45/2.50/5.50; 10%:1.32/2.40/5.21; 20%:0.71/1.55/3.21; 30%:0.25/0.56/1.82.</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>2021/05_A_STUDY_ON_EXPERIMENTAL_INVESTIGATION_USING_CEMENT_CONCRETE_WITH_VARIYING_PERCENTAGE_OF_RICE_HUSK_ASH.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2021_05</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>A Study on Experimental Investigation Using Cement Concrete with Varying Percentage of Rice Husk Ash</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Valli, Dhevasenaa</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>India (Govt College of Engineering, Srirangam, Trichy, Tamil Nadu)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Not specified; RHA silica 92.1%, bulk density 104.9 kg/m3, sp.gr 1.96</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Concrete (IS mix design, w/c 0.42)</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10% RHA</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>398.58</v>
+      </c>
+      <c r="K85" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="L85" t="n">
+        <v>10</v>
+      </c>
+      <c r="M85" t="n">
+        <v>725.11</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1429.61</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>7</v>
+      </c>
+      <c r="R85" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>tabulated (avg of 3 trials at 7/14/28 days)</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>kg/m3 from mix proportion table (verbatim). Comp avg from Tables 10.1-10.4; split tensile from Table 8.6 (verbatim).</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Binder (cement+RHA)=442.86 kg/m3 for all. Conventional (0% RHA) mix proportions assumed same aggregates/water (only 10/20/30% rows tabulated). Paper keyword mentions quarry dust but mix table lists fine aggregate 725.11 kg/m3 (quarry dust likely used as fine aggregate). 28-day split tensile of control 5.50 MPa is unusually high - recorded as-reported. No flexural.</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>Mix table (w/c 0.42): 10% cement 398.58/RHA 44.28; 20% cement 354.3/RHA 88.56; 30% cement 310.02/RHA 132.84; fine 725.11, coarse 1429.61, water 186. Comp avg: 0%:22.1/30.6/33.66; 10%:19.84/25.48/32.87; 20%:15.11/19.11/27.48; 30%:10.81/14.92/19.35. Split (Table 8.6): 0%:1.45/2.50/5.50; 10%:1.32/2.40/5.21; 20%:0.71/1.55/3.21; 30%:0.25/0.56/1.82.</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>2021/05_A_STUDY_ON_EXPERIMENTAL_INVESTIGATION_USING_CEMENT_CONCRETE_WITH_VARIYING_PERCENTAGE_OF_RICE_HUSK_ASH.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2021_05</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>A Study on Experimental Investigation Using Cement Concrete with Varying Percentage of Rice Husk Ash</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Valli, Dhevasenaa</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>India (Govt College of Engineering, Srirangam, Trichy, Tamil Nadu)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Not specified; RHA silica 92.1%, bulk density 104.9 kg/m3, sp.gr 1.96</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Concrete (IS mix design, w/c 0.42)</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>10% RHA</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>398.58</v>
+      </c>
+      <c r="K86" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="L86" t="n">
+        <v>10</v>
+      </c>
+      <c r="M86" t="n">
+        <v>725.11</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1429.61</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>14</v>
+      </c>
+      <c r="R86" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>tabulated (avg of 3 trials at 7/14/28 days)</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>kg/m3 from mix proportion table (verbatim). Comp avg from Tables 10.1-10.4; split tensile from Table 8.6 (verbatim).</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Binder (cement+RHA)=442.86 kg/m3 for all. Conventional (0% RHA) mix proportions assumed same aggregates/water (only 10/20/30% rows tabulated). Paper keyword mentions quarry dust but mix table lists fine aggregate 725.11 kg/m3 (quarry dust likely used as fine aggregate). 28-day split tensile of control 5.50 MPa is unusually high - recorded as-reported. No flexural.</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>Mix table (w/c 0.42): 10% cement 398.58/RHA 44.28; 20% cement 354.3/RHA 88.56; 30% cement 310.02/RHA 132.84; fine 725.11, coarse 1429.61, water 186. Comp avg: 0%:22.1/30.6/33.66; 10%:19.84/25.48/32.87; 20%:15.11/19.11/27.48; 30%:10.81/14.92/19.35. Split (Table 8.6): 0%:1.45/2.50/5.50; 10%:1.32/2.40/5.21; 20%:0.71/1.55/3.21; 30%:0.25/0.56/1.82.</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>2021/05_A_STUDY_ON_EXPERIMENTAL_INVESTIGATION_USING_CEMENT_CONCRETE_WITH_VARIYING_PERCENTAGE_OF_RICE_HUSK_ASH.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2021_05</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>A Study on Experimental Investigation Using Cement Concrete with Varying Percentage of Rice Husk Ash</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Valli, Dhevasenaa</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>India (Govt College of Engineering, Srirangam, Trichy, Tamil Nadu)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Not specified; RHA silica 92.1%, bulk density 104.9 kg/m3, sp.gr 1.96</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Concrete (IS mix design, w/c 0.42)</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>10% RHA</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>398.58</v>
+      </c>
+      <c r="K87" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="L87" t="n">
+        <v>10</v>
+      </c>
+      <c r="M87" t="n">
+        <v>725.11</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1429.61</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>28</v>
+      </c>
+      <c r="R87" t="n">
+        <v>32.87</v>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>tabulated (avg of 3 trials at 7/14/28 days)</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>kg/m3 from mix proportion table (verbatim). Comp avg from Tables 10.1-10.4; split tensile from Table 8.6 (verbatim).</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Binder (cement+RHA)=442.86 kg/m3 for all. Conventional (0% RHA) mix proportions assumed same aggregates/water (only 10/20/30% rows tabulated). Paper keyword mentions quarry dust but mix table lists fine aggregate 725.11 kg/m3 (quarry dust likely used as fine aggregate). 28-day split tensile of control 5.50 MPa is unusually high - recorded as-reported. No flexural.</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>Mix table (w/c 0.42): 10% cement 398.58/RHA 44.28; 20% cement 354.3/RHA 88.56; 30% cement 310.02/RHA 132.84; fine 725.11, coarse 1429.61, water 186. Comp avg: 0%:22.1/30.6/33.66; 10%:19.84/25.48/32.87; 20%:15.11/19.11/27.48; 30%:10.81/14.92/19.35. Split (Table 8.6): 0%:1.45/2.50/5.50; 10%:1.32/2.40/5.21; 20%:0.71/1.55/3.21; 30%:0.25/0.56/1.82.</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>2021/05_A_STUDY_ON_EXPERIMENTAL_INVESTIGATION_USING_CEMENT_CONCRETE_WITH_VARIYING_PERCENTAGE_OF_RICE_HUSK_ASH.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2021_05</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>A Study on Experimental Investigation Using Cement Concrete with Varying Percentage of Rice Husk Ash</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Valli, Dhevasenaa</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>India (Govt College of Engineering, Srirangam, Trichy, Tamil Nadu)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Not specified; RHA silica 92.1%, bulk density 104.9 kg/m3, sp.gr 1.96</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Concrete (IS mix design, w/c 0.42)</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>20% RHA</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>354.3</v>
+      </c>
+      <c r="K88" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="L88" t="n">
+        <v>20</v>
+      </c>
+      <c r="M88" t="n">
+        <v>725.11</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1429.61</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>7</v>
+      </c>
+      <c r="R88" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>tabulated (avg of 3 trials at 7/14/28 days)</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>kg/m3 from mix proportion table (verbatim). Comp avg from Tables 10.1-10.4; split tensile from Table 8.6 (verbatim).</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Binder (cement+RHA)=442.86 kg/m3 for all. Conventional (0% RHA) mix proportions assumed same aggregates/water (only 10/20/30% rows tabulated). Paper keyword mentions quarry dust but mix table lists fine aggregate 725.11 kg/m3 (quarry dust likely used as fine aggregate). 28-day split tensile of control 5.50 MPa is unusually high - recorded as-reported. No flexural.</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>Mix table (w/c 0.42): 10% cement 398.58/RHA 44.28; 20% cement 354.3/RHA 88.56; 30% cement 310.02/RHA 132.84; fine 725.11, coarse 1429.61, water 186. Comp avg: 0%:22.1/30.6/33.66; 10%:19.84/25.48/32.87; 20%:15.11/19.11/27.48; 30%:10.81/14.92/19.35. Split (Table 8.6): 0%:1.45/2.50/5.50; 10%:1.32/2.40/5.21; 20%:0.71/1.55/3.21; 30%:0.25/0.56/1.82.</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>2021/05_A_STUDY_ON_EXPERIMENTAL_INVESTIGATION_USING_CEMENT_CONCRETE_WITH_VARIYING_PERCENTAGE_OF_RICE_HUSK_ASH.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2021_05</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>A Study on Experimental Investigation Using Cement Concrete with Varying Percentage of Rice Husk Ash</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Valli, Dhevasenaa</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>India (Govt College of Engineering, Srirangam, Trichy, Tamil Nadu)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Not specified; RHA silica 92.1%, bulk density 104.9 kg/m3, sp.gr 1.96</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Concrete (IS mix design, w/c 0.42)</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>20% RHA</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>354.3</v>
+      </c>
+      <c r="K89" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="L89" t="n">
+        <v>20</v>
+      </c>
+      <c r="M89" t="n">
+        <v>725.11</v>
+      </c>
+      <c r="N89" t="n">
+        <v>1429.61</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>14</v>
+      </c>
+      <c r="R89" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>tabulated (avg of 3 trials at 7/14/28 days)</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>kg/m3 from mix proportion table (verbatim). Comp avg from Tables 10.1-10.4; split tensile from Table 8.6 (verbatim).</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Binder (cement+RHA)=442.86 kg/m3 for all. Conventional (0% RHA) mix proportions assumed same aggregates/water (only 10/20/30% rows tabulated). Paper keyword mentions quarry dust but mix table lists fine aggregate 725.11 kg/m3 (quarry dust likely used as fine aggregate). 28-day split tensile of control 5.50 MPa is unusually high - recorded as-reported. No flexural.</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>Mix table (w/c 0.42): 10% cement 398.58/RHA 44.28; 20% cement 354.3/RHA 88.56; 30% cement 310.02/RHA 132.84; fine 725.11, coarse 1429.61, water 186. Comp avg: 0%:22.1/30.6/33.66; 10%:19.84/25.48/32.87; 20%:15.11/19.11/27.48; 30%:10.81/14.92/19.35. Split (Table 8.6): 0%:1.45/2.50/5.50; 10%:1.32/2.40/5.21; 20%:0.71/1.55/3.21; 30%:0.25/0.56/1.82.</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>2021/05_A_STUDY_ON_EXPERIMENTAL_INVESTIGATION_USING_CEMENT_CONCRETE_WITH_VARIYING_PERCENTAGE_OF_RICE_HUSK_ASH.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2021_05</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>A Study on Experimental Investigation Using Cement Concrete with Varying Percentage of Rice Husk Ash</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Valli, Dhevasenaa</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>India (Govt College of Engineering, Srirangam, Trichy, Tamil Nadu)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Not specified; RHA silica 92.1%, bulk density 104.9 kg/m3, sp.gr 1.96</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Concrete (IS mix design, w/c 0.42)</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>20% RHA</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>354.3</v>
+      </c>
+      <c r="K90" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="L90" t="n">
+        <v>20</v>
+      </c>
+      <c r="M90" t="n">
+        <v>725.11</v>
+      </c>
+      <c r="N90" t="n">
+        <v>1429.61</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>28</v>
+      </c>
+      <c r="R90" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>tabulated (avg of 3 trials at 7/14/28 days)</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>kg/m3 from mix proportion table (verbatim). Comp avg from Tables 10.1-10.4; split tensile from Table 8.6 (verbatim).</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Binder (cement+RHA)=442.86 kg/m3 for all. Conventional (0% RHA) mix proportions assumed same aggregates/water (only 10/20/30% rows tabulated). Paper keyword mentions quarry dust but mix table lists fine aggregate 725.11 kg/m3 (quarry dust likely used as fine aggregate). 28-day split tensile of control 5.50 MPa is unusually high - recorded as-reported. No flexural.</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Mix table (w/c 0.42): 10% cement 398.58/RHA 44.28; 20% cement 354.3/RHA 88.56; 30% cement 310.02/RHA 132.84; fine 725.11, coarse 1429.61, water 186. Comp avg: 0%:22.1/30.6/33.66; 10%:19.84/25.48/32.87; 20%:15.11/19.11/27.48; 30%:10.81/14.92/19.35. Split (Table 8.6): 0%:1.45/2.50/5.50; 10%:1.32/2.40/5.21; 20%:0.71/1.55/3.21; 30%:0.25/0.56/1.82.</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>2021/05_A_STUDY_ON_EXPERIMENTAL_INVESTIGATION_USING_CEMENT_CONCRETE_WITH_VARIYING_PERCENTAGE_OF_RICE_HUSK_ASH.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2021_05</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>A Study on Experimental Investigation Using Cement Concrete with Varying Percentage of Rice Husk Ash</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Valli, Dhevasenaa</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>India (Govt College of Engineering, Srirangam, Trichy, Tamil Nadu)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Not specified; RHA silica 92.1%, bulk density 104.9 kg/m3, sp.gr 1.96</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Concrete (IS mix design, w/c 0.42)</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>30% RHA</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>310.02</v>
+      </c>
+      <c r="K91" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="L91" t="n">
+        <v>30</v>
+      </c>
+      <c r="M91" t="n">
+        <v>725.11</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1429.61</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>7</v>
+      </c>
+      <c r="R91" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>tabulated (avg of 3 trials at 7/14/28 days)</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>kg/m3 from mix proportion table (verbatim). Comp avg from Tables 10.1-10.4; split tensile from Table 8.6 (verbatim).</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Binder (cement+RHA)=442.86 kg/m3 for all. Conventional (0% RHA) mix proportions assumed same aggregates/water (only 10/20/30% rows tabulated). Paper keyword mentions quarry dust but mix table lists fine aggregate 725.11 kg/m3 (quarry dust likely used as fine aggregate). 28-day split tensile of control 5.50 MPa is unusually high - recorded as-reported. No flexural.</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>Mix table (w/c 0.42): 10% cement 398.58/RHA 44.28; 20% cement 354.3/RHA 88.56; 30% cement 310.02/RHA 132.84; fine 725.11, coarse 1429.61, water 186. Comp avg: 0%:22.1/30.6/33.66; 10%:19.84/25.48/32.87; 20%:15.11/19.11/27.48; 30%:10.81/14.92/19.35. Split (Table 8.6): 0%:1.45/2.50/5.50; 10%:1.32/2.40/5.21; 20%:0.71/1.55/3.21; 30%:0.25/0.56/1.82.</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>2021/05_A_STUDY_ON_EXPERIMENTAL_INVESTIGATION_USING_CEMENT_CONCRETE_WITH_VARIYING_PERCENTAGE_OF_RICE_HUSK_ASH.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2021_05</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>A Study on Experimental Investigation Using Cement Concrete with Varying Percentage of Rice Husk Ash</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Valli, Dhevasenaa</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>India (Govt College of Engineering, Srirangam, Trichy, Tamil Nadu)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Not specified; RHA silica 92.1%, bulk density 104.9 kg/m3, sp.gr 1.96</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Concrete (IS mix design, w/c 0.42)</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>30% RHA</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>310.02</v>
+      </c>
+      <c r="K92" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="L92" t="n">
+        <v>30</v>
+      </c>
+      <c r="M92" t="n">
+        <v>725.11</v>
+      </c>
+      <c r="N92" t="n">
+        <v>1429.61</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>14</v>
+      </c>
+      <c r="R92" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>tabulated (avg of 3 trials at 7/14/28 days)</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>kg/m3 from mix proportion table (verbatim). Comp avg from Tables 10.1-10.4; split tensile from Table 8.6 (verbatim).</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Binder (cement+RHA)=442.86 kg/m3 for all. Conventional (0% RHA) mix proportions assumed same aggregates/water (only 10/20/30% rows tabulated). Paper keyword mentions quarry dust but mix table lists fine aggregate 725.11 kg/m3 (quarry dust likely used as fine aggregate). 28-day split tensile of control 5.50 MPa is unusually high - recorded as-reported. No flexural.</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>Mix table (w/c 0.42): 10% cement 398.58/RHA 44.28; 20% cement 354.3/RHA 88.56; 30% cement 310.02/RHA 132.84; fine 725.11, coarse 1429.61, water 186. Comp avg: 0%:22.1/30.6/33.66; 10%:19.84/25.48/32.87; 20%:15.11/19.11/27.48; 30%:10.81/14.92/19.35. Split (Table 8.6): 0%:1.45/2.50/5.50; 10%:1.32/2.40/5.21; 20%:0.71/1.55/3.21; 30%:0.25/0.56/1.82.</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>2021/05_A_STUDY_ON_EXPERIMENTAL_INVESTIGATION_USING_CEMENT_CONCRETE_WITH_VARIYING_PERCENTAGE_OF_RICE_HUSK_ASH.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2021_05</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>A Study on Experimental Investigation Using Cement Concrete with Varying Percentage of Rice Husk Ash</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Valli, Dhevasenaa</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>India (Govt College of Engineering, Srirangam, Trichy, Tamil Nadu)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Not specified; RHA silica 92.1%, bulk density 104.9 kg/m3, sp.gr 1.96</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Concrete (IS mix design, w/c 0.42)</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>30% RHA</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>310.02</v>
+      </c>
+      <c r="K93" t="n">
+        <v>132.84</v>
+      </c>
+      <c r="L93" t="n">
+        <v>30</v>
+      </c>
+      <c r="M93" t="n">
+        <v>725.11</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1429.61</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>28</v>
+      </c>
+      <c r="R93" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>tabulated (avg of 3 trials at 7/14/28 days)</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>kg/m3 from mix proportion table (verbatim). Comp avg from Tables 10.1-10.4; split tensile from Table 8.6 (verbatim).</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Binder (cement+RHA)=442.86 kg/m3 for all. Conventional (0% RHA) mix proportions assumed same aggregates/water (only 10/20/30% rows tabulated). Paper keyword mentions quarry dust but mix table lists fine aggregate 725.11 kg/m3 (quarry dust likely used as fine aggregate). 28-day split tensile of control 5.50 MPa is unusually high - recorded as-reported. No flexural.</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>Mix table (w/c 0.42): 10% cement 398.58/RHA 44.28; 20% cement 354.3/RHA 88.56; 30% cement 310.02/RHA 132.84; fine 725.11, coarse 1429.61, water 186. Comp avg: 0%:22.1/30.6/33.66; 10%:19.84/25.48/32.87; 20%:15.11/19.11/27.48; 30%:10.81/14.92/19.35. Split (Table 8.6): 0%:1.45/2.50/5.50; 10%:1.32/2.40/5.21; 20%:0.71/1.55/3.21; 30%:0.25/0.56/1.82.</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>2021/05_A_STUDY_ON_EXPERIMENTAL_INVESTIGATION_USING_CEMENT_CONCRETE_WITH_VARIYING_PERCENTAGE_OF_RICE_HUSK_ASH.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2021_14</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Experimental Investigation on Properties of Concrete Enhanced by Replacement of Cement with Rice Husk Ash as an Admixture</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Neeraja, Bala Padmaja</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>India (Mahatma Gandhi Institute of Technology, Hyderabad)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Not specified (RHA ~85-90% amorphous silica)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Concrete M40 grade</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>0% RHA (control, M40)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>superplasticizer used (qty not given)</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="n">
+        <v>7</v>
+      </c>
+      <c r="R94" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>tabulated (comp &amp; split at 7/14 days); mix proportions not reported</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Comp from Table 1; split tensile from Table 3 (verbatim N/mm2=MPa).</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>M40 grade but no kg/m3 mix proportions or w/c reported - left blank. Tests at 7 and 14 days only (no 28-day). No flexural (future scope). RHA 0/5/10% tabulated (study also mentions 15% RHA and granite fines but not in result tables).</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>Table 1 comp (N/mm2): 7d 0%/5%/10% = 25.3/29.33/13.33; 14d = 37.9/38.22/22.22. Table 3 split tensile: 7d = 1.27/1.41/0.84; 14d = 1.69/1.98/1.13.</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>2021/14_Experimental_Investigation_on_Properties_of_Concrete_Enhanced_by_Replacement_of_Cement_with_Rice_Husk_Ash_as_an_Admixtur.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2021_14</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Experimental Investigation on Properties of Concrete Enhanced by Replacement of Cement with Rice Husk Ash as an Admixture</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Neeraja, Bala Padmaja</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>India (Mahatma Gandhi Institute of Technology, Hyderabad)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Not specified (RHA ~85-90% amorphous silica)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Concrete M40 grade</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>0% RHA (control, M40)</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>superplasticizer used (qty not given)</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="n">
+        <v>14</v>
+      </c>
+      <c r="R95" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>tabulated (comp &amp; split at 7/14 days); mix proportions not reported</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Comp from Table 1; split tensile from Table 3 (verbatim N/mm2=MPa).</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>M40 grade but no kg/m3 mix proportions or w/c reported - left blank. Tests at 7 and 14 days only (no 28-day). No flexural (future scope). RHA 0/5/10% tabulated (study also mentions 15% RHA and granite fines but not in result tables).</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>Table 1 comp (N/mm2): 7d 0%/5%/10% = 25.3/29.33/13.33; 14d = 37.9/38.22/22.22. Table 3 split tensile: 7d = 1.27/1.41/0.84; 14d = 1.69/1.98/1.13.</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>2021/14_Experimental_Investigation_on_Properties_of_Concrete_Enhanced_by_Replacement_of_Cement_with_Rice_Husk_Ash_as_an_Admixtur.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2021_14</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Experimental Investigation on Properties of Concrete Enhanced by Replacement of Cement with Rice Husk Ash as an Admixture</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Neeraja, Bala Padmaja</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>India (Mahatma Gandhi Institute of Technology, Hyderabad)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Not specified (RHA ~85-90% amorphous silica)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Concrete M40 grade</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>5% RHA (M40)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="n">
+        <v>5</v>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>superplasticizer used (qty not given)</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="n">
+        <v>7</v>
+      </c>
+      <c r="R96" t="n">
+        <v>29.33</v>
+      </c>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>tabulated (comp &amp; split at 7/14 days); mix proportions not reported</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Comp from Table 1; split tensile from Table 3 (verbatim N/mm2=MPa).</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>M40 grade but no kg/m3 mix proportions or w/c reported - left blank. Tests at 7 and 14 days only (no 28-day). No flexural (future scope). RHA 0/5/10% tabulated (study also mentions 15% RHA and granite fines but not in result tables).</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>Table 1 comp (N/mm2): 7d 0%/5%/10% = 25.3/29.33/13.33; 14d = 37.9/38.22/22.22. Table 3 split tensile: 7d = 1.27/1.41/0.84; 14d = 1.69/1.98/1.13.</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>2021/14_Experimental_Investigation_on_Properties_of_Concrete_Enhanced_by_Replacement_of_Cement_with_Rice_Husk_Ash_as_an_Admixtur.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2021_14</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Experimental Investigation on Properties of Concrete Enhanced by Replacement of Cement with Rice Husk Ash as an Admixture</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Neeraja, Bala Padmaja</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>India (Mahatma Gandhi Institute of Technology, Hyderabad)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Not specified (RHA ~85-90% amorphous silica)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Concrete M40 grade</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>5% RHA (M40)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="n">
+        <v>5</v>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>superplasticizer used (qty not given)</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="n">
+        <v>14</v>
+      </c>
+      <c r="R97" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>tabulated (comp &amp; split at 7/14 days); mix proportions not reported</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Comp from Table 1; split tensile from Table 3 (verbatim N/mm2=MPa).</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>M40 grade but no kg/m3 mix proportions or w/c reported - left blank. Tests at 7 and 14 days only (no 28-day). No flexural (future scope). RHA 0/5/10% tabulated (study also mentions 15% RHA and granite fines but not in result tables).</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>Table 1 comp (N/mm2): 7d 0%/5%/10% = 25.3/29.33/13.33; 14d = 37.9/38.22/22.22. Table 3 split tensile: 7d = 1.27/1.41/0.84; 14d = 1.69/1.98/1.13.</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>2021/14_Experimental_Investigation_on_Properties_of_Concrete_Enhanced_by_Replacement_of_Cement_with_Rice_Husk_Ash_as_an_Admixtur.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2021_14</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Experimental Investigation on Properties of Concrete Enhanced by Replacement of Cement with Rice Husk Ash as an Admixture</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Neeraja, Bala Padmaja</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>India (Mahatma Gandhi Institute of Technology, Hyderabad)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Not specified (RHA ~85-90% amorphous silica)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Concrete M40 grade</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>10% RHA (M40)</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="n">
+        <v>10</v>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>superplasticizer used (qty not given)</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="n">
+        <v>7</v>
+      </c>
+      <c r="R98" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>tabulated (comp &amp; split at 7/14 days); mix proportions not reported</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Comp from Table 1; split tensile from Table 3 (verbatim N/mm2=MPa).</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>M40 grade but no kg/m3 mix proportions or w/c reported - left blank. Tests at 7 and 14 days only (no 28-day). No flexural (future scope). RHA 0/5/10% tabulated (study also mentions 15% RHA and granite fines but not in result tables).</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>Table 1 comp (N/mm2): 7d 0%/5%/10% = 25.3/29.33/13.33; 14d = 37.9/38.22/22.22. Table 3 split tensile: 7d = 1.27/1.41/0.84; 14d = 1.69/1.98/1.13.</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>2021/14_Experimental_Investigation_on_Properties_of_Concrete_Enhanced_by_Replacement_of_Cement_with_Rice_Husk_Ash_as_an_Admixtur.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2021_14</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Experimental Investigation on Properties of Concrete Enhanced by Replacement of Cement with Rice Husk Ash as an Admixture</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Neeraja, Bala Padmaja</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>India (Mahatma Gandhi Institute of Technology, Hyderabad)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Not specified (RHA ~85-90% amorphous silica)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Concrete M40 grade</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>10% RHA (M40)</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="n">
+        <v>10</v>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>superplasticizer used (qty not given)</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="n">
+        <v>14</v>
+      </c>
+      <c r="R99" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>tabulated (comp &amp; split at 7/14 days); mix proportions not reported</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Comp from Table 1; split tensile from Table 3 (verbatim N/mm2=MPa).</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>M40 grade but no kg/m3 mix proportions or w/c reported - left blank. Tests at 7 and 14 days only (no 28-day). No flexural (future scope). RHA 0/5/10% tabulated (study also mentions 15% RHA and granite fines but not in result tables).</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>Table 1 comp (N/mm2): 7d 0%/5%/10% = 25.3/29.33/13.33; 14d = 37.9/38.22/22.22. Table 3 split tensile: 7d = 1.27/1.41/0.84; 14d = 1.69/1.98/1.13.</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>2021/14_Experimental_Investigation_on_Properties_of_Concrete_Enhanced_by_Replacement_of_Cement_with_Rice_Husk_Ash_as_an_Admixtur.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Obilade(2014) 0%</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Obilade(2014) 10%</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="n">
+        <v>10</v>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Obilade(2014) 20%</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="n">
+        <v>20</v>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Obilade(2014) 30%</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="n">
+        <v>30</v>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Al-Khalaf&amp;Yousif(1984) 0%</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Al-Khalaf&amp;Yousif(1984) 10%</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="n">
+        <v>10</v>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Al-Khalaf&amp;Yousif(1984) 20%</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="n">
+        <v>20</v>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Al-Khalaf&amp;Yousif(1984) 30%</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="n">
+        <v>30</v>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Ephraim(2012) 10%</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="n">
+        <v>10</v>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="n">
+        <v>22</v>
+      </c>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Ephraim(2012) 20%</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="n">
+        <v>20</v>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="n">
+        <v>20</v>
+      </c>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Ephraim(2012) 30%</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="n">
+        <v>30</v>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="n">
+        <v>19</v>
+      </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Akeke(2013) 10%</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="n">
+        <v>10</v>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>cited (density 2017 kg/m3)</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="n">
+        <v>22</v>
+      </c>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Akeke(2013) 20%</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="n">
+        <v>20</v>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>cited (density 1950 kg/m3)</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="n">
+        <v>20</v>
+      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Akeke(2013) 30%</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="n">
+        <v>30</v>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="n">
+        <v>19</v>
+      </c>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Krishna(2017) 0%</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="n">
+        <v>27</v>
+      </c>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Krishna(2017) 10%</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="n">
+        <v>10</v>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Krishna(2017) 20%</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="n">
+        <v>20</v>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Krishna(2015) 0%</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="n">
+        <v>39</v>
+      </c>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Krishna(2015) 10%</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="n">
+        <v>10</v>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Krishna(2015) 30%</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="n">
+        <v>30</v>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Ahsan&amp;Hossain(2018) 0%</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Ahsan&amp;Hossain(2018) 10%</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="n">
+        <v>10</v>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>cited (density 2323 kg/m3)</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2021_03_citedTable4</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Cited RHA compressive-strength data compiled in Muleya et al. (2021) Table 4</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>various (compiled by Muleya et al. 2021)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>various (see mix_id / cited source)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>various cited studies</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Concrete (RHA cement replacement)</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Ahsan&amp;Hossain(2018) 20%</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="n">
+        <v>20</v>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>tabulated (secondary compilation; curing age not stated)</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Compressive strength from Table 4 of 2021_03 (compiled from listed references).</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>SECONDARY/CITED data compiled in 2021_03 Table 4 - NOT measured in 2021_03. Curing age not stated in the compiled table (typical 28d; left blank rather than assumed). No mix proportions, w/c, or aggregates given. Density (kg/m3) values also reported in source but omitted (not a target output). Provided so cited datasets are captured; verify against original papers (see Cited_sources_to_fetch).</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>Table 4 (Muleya 2021): comp strength MPa at RHA 0/10/20/30% - Obilade(2014) 29.15/20.88/18.59/13.29; Al-Khalaf&amp;Yousif(1984) 23.30/25.40/24.10/22.80; Ephraim(2012) -/22.00/20.00/19.00; Akeke(2013) -/22.00/20.00/19.00; Krishna(2017) 27.00/29.80/16.03/-; Krishna(2015) 39.00/40.50/-/32.50; Ahsan&amp;Hossain(2018) 36.10/22.80/16.80/-.</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>2021/03 (Table 4 - compiled literature values)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4959,7 +13197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5087,6 +13325,206 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>Silica production overview; no concrete strength data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2021_04</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Experimental Investigation on the Mechanical Properties of Natural Fiber Reinforced Concrete (sisal/coir)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>No rice husk ash; natural fiber (sisal/coir) reinforced concrete - out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2021_06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Obtaining Biochar from Rice Husk and Straw</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Biochar/pyrolysis study; no concrete/mortar mix or strength data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2021_07</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Techno-economic and Environmental Feasibility Analysis of Rice Husk Fired Energy System</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Energy/power generation feasibility; no concrete mix or strength data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2021_08</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hydric and Durability Performances of Compressed Earth Blocks Stabilized with Calcium Carbide Residue and Rice Husk Ash</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Contains RHA but the material is compressed/stabilized earth blocks (soil), not concrete/mortar; no comp/flexural/split MPa for concrete - out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2021_09</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Investigating the Effect of Olive Husk Ash on the Properties of Asphalt Concrete Mixture</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Olive husk ash in asphalt (bituminous) mixture; not RHA, not cementitious concrete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2021_10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Geopolymer Concrete Compressive Strength via ANN/ANFIS/GEP</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fly-ash geopolymer concrete ML modeling; no RHA, no new experimental RHA mix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2021_11</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Effects of Controlled Burn Rice Husk Ash on Geotechnical Properties of the Soil</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RHA used for soil stabilization (geotechnical), not concrete/mortar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2021_12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Experimental Study of Stabilization of Expansive Soil Using Marble Dust, Rice Husk Ash and Cement</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Soil stabilization (subgrade), not concrete/mortar strength.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2021_13</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Assessment of Longstanding Effects of Fly Ash and Silica Fume on the Compressive Strength of Concrete Using Extreme Learning Machine</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>No RHA; fly ash + silica fume ML modeling - out of scope (no RHA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2021_15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Effects of Steam Explosion Pretreatment on the Extraction of Xylooligosaccharide from Rice Husk</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Biochemical extraction from rice husk; no concrete.</t>
         </is>
       </c>
     </row>
@@ -5101,7 +13539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5227,6 +13665,161 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>10.1007/s41062-018-0127-6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Obilade, I. O. (2014). Use of rice husk ash as partial replacement for cement in concrete. Int. J. of Engineering, 5(04), 8269.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RHA comp strength data compiled in Table 4 (0/10/20/30%); fetch original to confirm curing age, mix proportions.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Al-Khalaf, M. N., &amp; Yousif, H. A. (1984). Use of rice husk ash in concrete. Int. J. Cement Composites and Lightweight Concrete, 6(4), 241-248.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RHA comp strength data in Table 4.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ephraim, M. E., Akeke, G. A., &amp; Ukpata, J. O. (2012). Compressive strength of concrete with rice husk ash as partial replacement of OPC. Scholarly Journal of Engineering Research, 1(2), 32-36.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RHA comp strength data in Table 4.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Akeke, G. A., Ephraim, M. E., Akobo, I. Z. S., &amp; Ukpata, J. O. (2013). Structural properties of rice husk ash concrete. Int. J. of Engineering, 3(3), 8269.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RHA comp strength + density data in Table 4.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Krishna, N. K., Sandeep, S., &amp; Mini, K. M. (2016). Study on concrete with partial replacement of cement by rice husk ash. IOP Conf. Ser. MSE, 149(1), 012109.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RHA comp strength data in Table 4 (listed as Krishna 2017).</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10.1088/1757-899X/149/1/012109</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Krishna, R., Chaudhary, M., &amp; Sen, A. (2015). Effect of partial replacement of cement by rice husk ash in concrete. Int. J. of Science and Research, 4(5), 1572-1574.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RHA comp strength data in Table 4.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2021_03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ahsan, M. B., &amp; Hossain, Z. (2018). Supplemental use of rice husk ash (RHA) as a cementitious material in concrete. Construction and Building Materials, 178, 1-9.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RHA comp strength + density data in Table 4.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10.1016/j.conbuildmat.2018.05.101</t>
         </is>
       </c>
     </row>

--- a/RHA_concrete_ML_dataset.xlsx
+++ b/RHA_concrete_ML_dataset.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z122"/>
+  <dimension ref="A1:Z214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12960,6 +12960,9422 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>B-1 (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>1</v>
+      </c>
+      <c r="R123" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>B-1 (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>3</v>
+      </c>
+      <c r="R124" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>B-1 (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>7</v>
+      </c>
+      <c r="R125" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>B-1 (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>28</v>
+      </c>
+      <c r="R126" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>B-2 (5% RHA)</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="n">
+        <v>5</v>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>1</v>
+      </c>
+      <c r="R127" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>B-2 (5% RHA)</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="n">
+        <v>5</v>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>3</v>
+      </c>
+      <c r="R128" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>B-2 (5% RHA)</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="n">
+        <v>5</v>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>7</v>
+      </c>
+      <c r="R129" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>B-2 (5% RHA)</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="n">
+        <v>5</v>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>28</v>
+      </c>
+      <c r="R130" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>B-3 (10% RHA)</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="n">
+        <v>10</v>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>1</v>
+      </c>
+      <c r="R131" t="n">
+        <v>23</v>
+      </c>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>B-3 (10% RHA)</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="n">
+        <v>10</v>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>3</v>
+      </c>
+      <c r="R132" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>B-3 (10% RHA)</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="n">
+        <v>10</v>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>7</v>
+      </c>
+      <c r="R133" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>B-3 (10% RHA)</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="n">
+        <v>10</v>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>28</v>
+      </c>
+      <c r="R134" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>B-4 (15% RHA)</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="n">
+        <v>15</v>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>1</v>
+      </c>
+      <c r="R135" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>B-4 (15% RHA)</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="n">
+        <v>15</v>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>3</v>
+      </c>
+      <c r="R136" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>B-4 (15% RHA)</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="n">
+        <v>15</v>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>7</v>
+      </c>
+      <c r="R137" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>B-4 (15% RHA)</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="n">
+        <v>15</v>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>28</v>
+      </c>
+      <c r="R138" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>B-5 (20% RHA)</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="n">
+        <v>20</v>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>1</v>
+      </c>
+      <c r="R139" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>B-5 (20% RHA)</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="n">
+        <v>20</v>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>3</v>
+      </c>
+      <c r="R140" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>B-5 (20% RHA)</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="n">
+        <v>20</v>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>7</v>
+      </c>
+      <c r="R141" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>B-5 (20% RHA)</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="n">
+        <v>20</v>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>28</v>
+      </c>
+      <c r="R142" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>B-6 (25% RHA)</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="n">
+        <v>25</v>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1</v>
+      </c>
+      <c r="R143" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>B-6 (25% RHA)</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="n">
+        <v>25</v>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>3</v>
+      </c>
+      <c r="R144" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>B-6 (25% RHA)</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="n">
+        <v>25</v>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>7</v>
+      </c>
+      <c r="R145" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>B-6 (25% RHA)</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="n">
+        <v>25</v>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>28</v>
+      </c>
+      <c r="R146" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>B-7 (30% RHA)</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="n">
+        <v>30</v>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>1</v>
+      </c>
+      <c r="R147" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>B-7 (30% RHA)</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="n">
+        <v>30</v>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>3</v>
+      </c>
+      <c r="R148" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>B-7 (30% RHA)</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="n">
+        <v>30</v>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>7</v>
+      </c>
+      <c r="R149" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2022_03</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Rice Husk Ash (RHA) Based Concrete: Workability and Compressive Strength with Different Dosages and Curing Ages</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Wagan, Memon A.H., Memon N.A., Memon F.T., Lashari</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Pakistan (Nawabshah; QUEST)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Local rice mill, Nawabshah, Pakistan; husk burnt in lab at low temperature (~200C, likely incomplete combustion)</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Concrete (mix 1:2:4 by weight), no admixture</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>B-7 (30% RHA)</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="n">
+        <v>30</v>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>none (1:2:4)</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>28</v>
+      </c>
+      <c r="R150" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 1/3/7/28 days (Table 4); no flexural or split tensile tested</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 4. Mix proportions given only as ratio 1:2:4 with w/c=0.5 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>OPC reduced by weight of binder equal to RHA percentage. 7 batches B-1..B-7 at RHA 0/5/10/15/20/25/30%. w/c fixed 0.5. kg/m3 not reported. Note: 7-day comp values are lower than 3-day in the source table (reported as-is). RHA burnt at low temp (~200C) so reduced pozzolanic activity; strengths decline markedly beyond 10%.</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>Table 4 Average Compressive Strength (MPa). 1d: 0%22.13,5%23.07,10%23.00,15%20.27,20%17.27,25%15.60,30%15.27. 3d: 24.43,24.40,21.13,19.23,15.80,14.73,12.20. 7d: 20.67,20.60,20.53,17.97,16.43,14.53,13.87. 28d: 24.63,24.30,24.47,21.07,15.33,14.10,13.33. Table 3 slump and Table 1 RHA properties.</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>2022/03_Rice_Husk_Ash_RHA_Based_Concrete_Workability_and_Compressive_Strength_with_Different_Dosages_and_Curing_Ages.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>SM1 (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>345</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>690</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>3</v>
+      </c>
+      <c r="R151" t="n">
+        <v>3.229</v>
+      </c>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>SM1 (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>345</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>690</v>
+      </c>
+      <c r="N152" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>7</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6.932</v>
+      </c>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="n">
+        <v>1.179</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>SM1 (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>345</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>690</v>
+      </c>
+      <c r="N153" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>28</v>
+      </c>
+      <c r="R153" t="n">
+        <v>13.563</v>
+      </c>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="n">
+        <v>1.891</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>SM1 (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>345</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>690</v>
+      </c>
+      <c r="N154" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>56</v>
+      </c>
+      <c r="R154" t="n">
+        <v>23.251</v>
+      </c>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="n">
+        <v>3.358</v>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>SM2 (6% RHA)</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="K155" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="L155" t="n">
+        <v>6</v>
+      </c>
+      <c r="M155" t="n">
+        <v>690</v>
+      </c>
+      <c r="N155" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>3</v>
+      </c>
+      <c r="R155" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="n">
+        <v>1</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>SM2 (6% RHA)</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="K156" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="L156" t="n">
+        <v>6</v>
+      </c>
+      <c r="M156" t="n">
+        <v>690</v>
+      </c>
+      <c r="N156" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>7</v>
+      </c>
+      <c r="R156" t="n">
+        <v>7.535</v>
+      </c>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>SM2 (6% RHA)</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="K157" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="L157" t="n">
+        <v>6</v>
+      </c>
+      <c r="M157" t="n">
+        <v>690</v>
+      </c>
+      <c r="N157" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>28</v>
+      </c>
+      <c r="R157" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="n">
+        <v>2.124</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>SM2 (6% RHA)</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>324.3</v>
+      </c>
+      <c r="K158" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="L158" t="n">
+        <v>6</v>
+      </c>
+      <c r="M158" t="n">
+        <v>690</v>
+      </c>
+      <c r="N158" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>56</v>
+      </c>
+      <c r="R158" t="n">
+        <v>25.404</v>
+      </c>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="n">
+        <v>3.563</v>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>SM3 (12% RHA)</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>303.6</v>
+      </c>
+      <c r="K159" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="L159" t="n">
+        <v>12</v>
+      </c>
+      <c r="M159" t="n">
+        <v>690</v>
+      </c>
+      <c r="N159" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>3</v>
+      </c>
+      <c r="R159" t="n">
+        <v>3.294</v>
+      </c>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>SM3 (12% RHA)</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>303.6</v>
+      </c>
+      <c r="K160" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="L160" t="n">
+        <v>12</v>
+      </c>
+      <c r="M160" t="n">
+        <v>690</v>
+      </c>
+      <c r="N160" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>7</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>SM3 (12% RHA)</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>303.6</v>
+      </c>
+      <c r="K161" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="L161" t="n">
+        <v>12</v>
+      </c>
+      <c r="M161" t="n">
+        <v>690</v>
+      </c>
+      <c r="N161" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>28</v>
+      </c>
+      <c r="R161" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>SM3 (12% RHA)</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>303.6</v>
+      </c>
+      <c r="K162" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="L162" t="n">
+        <v>12</v>
+      </c>
+      <c r="M162" t="n">
+        <v>690</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>56</v>
+      </c>
+      <c r="R162" t="n">
+        <v>21.744</v>
+      </c>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="n">
+        <v>3.049</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>SM4 (18% RHA)</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="K163" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="L163" t="n">
+        <v>18</v>
+      </c>
+      <c r="M163" t="n">
+        <v>690</v>
+      </c>
+      <c r="N163" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>3</v>
+      </c>
+      <c r="R163" t="n">
+        <v>2.885</v>
+      </c>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>SM4 (18% RHA)</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="K164" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="L164" t="n">
+        <v>18</v>
+      </c>
+      <c r="M164" t="n">
+        <v>690</v>
+      </c>
+      <c r="N164" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>7</v>
+      </c>
+      <c r="R164" t="n">
+        <v>5.813</v>
+      </c>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="n">
+        <v>0.9320000000000001</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>SM4 (18% RHA)</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="K165" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="L165" t="n">
+        <v>18</v>
+      </c>
+      <c r="M165" t="n">
+        <v>690</v>
+      </c>
+      <c r="N165" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>28</v>
+      </c>
+      <c r="R165" t="n">
+        <v>12.056</v>
+      </c>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="n">
+        <v>1.597</v>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>SM4 (18% RHA)</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="K166" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="L166" t="n">
+        <v>18</v>
+      </c>
+      <c r="M166" t="n">
+        <v>690</v>
+      </c>
+      <c r="N166" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>56</v>
+      </c>
+      <c r="R166" t="n">
+        <v>20.022</v>
+      </c>
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="n">
+        <v>2.844</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>SM5 (24% RHA)</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>262.2</v>
+      </c>
+      <c r="K167" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="L167" t="n">
+        <v>24</v>
+      </c>
+      <c r="M167" t="n">
+        <v>690</v>
+      </c>
+      <c r="N167" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>3</v>
+      </c>
+      <c r="R167" t="n">
+        <v>2.583</v>
+      </c>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>SM5 (24% RHA)</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>262.2</v>
+      </c>
+      <c r="K168" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="L168" t="n">
+        <v>24</v>
+      </c>
+      <c r="M168" t="n">
+        <v>690</v>
+      </c>
+      <c r="N168" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>7</v>
+      </c>
+      <c r="R168" t="n">
+        <v>5.425</v>
+      </c>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>SM5 (24% RHA)</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>262.2</v>
+      </c>
+      <c r="K169" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="L169" t="n">
+        <v>24</v>
+      </c>
+      <c r="M169" t="n">
+        <v>690</v>
+      </c>
+      <c r="N169" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>28</v>
+      </c>
+      <c r="R169" t="n">
+        <v>11.303</v>
+      </c>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2022_10</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Effect of Using Rice Husk Ash as Partial Replacement of Cement on Properties of Fresh and Hardened Concrete</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Ajwad, Ahmad, Abdullah, Jaffar, Ilyas, Adnan</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Pakistan (Lahore; University of Management and Technology)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Brick/block kiln near Lahore, Pakistan; sieved (#4, #40) and ball-milled to ~600 m2/kg</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Concrete M15 grade (mix 1:2:4)</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>SM5 (24% RHA)</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>262.2</v>
+      </c>
+      <c r="K170" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="L170" t="n">
+        <v>24</v>
+      </c>
+      <c r="M170" t="n">
+        <v>690</v>
+      </c>
+      <c r="N170" t="n">
+        <v>1380</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>56</v>
+      </c>
+      <c r="R170" t="n">
+        <v>17.438</v>
+      </c>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Compressive (Table 4) and split-cylinder tensile (Table 5) tabulated at 3/7/28/56 days; flexural (modulus of rupture) only in Fig 12 (4-6 MPa range) -&gt; left blank</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Comp &amp; split MPa verbatim from Tables 4 &amp; 5. kg/m3 per m3 from Table 6 (cement 345, fine 690, coarse 1380) with total binder held constant at 345 kg/m3; cement/RHA split computed per replacement level; water=0.6*345=207 kg/m3.</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>RHA 0/6/12/18/24% by weight of cement; w/b 0.6 constant; binder 345 kg/m3 constant. Cement/RHA per level: 0%-&gt;345/0; 6%-&gt;324.3/20.7; 12%-&gt;303.6/41.4; 18%-&gt;282.9/62.1; 24%-&gt;262.2/82.8. Reported 28d comp ~13.5 MPa (low for M15). Flexural ~4-6 MPa figure-only.</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>Table 6 per-m3 quantities (raw 0%: cement 345 kg, fine 690 kg, coarse 1380 kg; 6%: cement 324.3 + RHA 20.7). Table 4 comp MPa 3/7/28/56d. Table 5 split MPa 3/7/28/56d. w/b 0.6.</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>2022/10_Effect_of_Using_Rice_Husk_Ash_as_Partial_Replacement_of_Cement_on_Properties_of_Fresh_and_Hardened_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>M1-0 (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>500</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>780</v>
+      </c>
+      <c r="N171" t="n">
+        <v>820</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>7</v>
+      </c>
+      <c r="R171" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="S171" t="inlineStr"/>
+      <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>M1-0 (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>500</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>780</v>
+      </c>
+      <c r="N172" t="n">
+        <v>820</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>28</v>
+      </c>
+      <c r="R172" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="S172" t="inlineStr"/>
+      <c r="T172" t="inlineStr"/>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>M1-2.5 (2.5% RHA)</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="K173" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L173" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M173" t="n">
+        <v>780</v>
+      </c>
+      <c r="N173" t="n">
+        <v>820</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>7</v>
+      </c>
+      <c r="R173" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="S173" t="inlineStr"/>
+      <c r="T173" t="inlineStr"/>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>M1-2.5 (2.5% RHA)</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>487.5</v>
+      </c>
+      <c r="K174" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L174" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M174" t="n">
+        <v>780</v>
+      </c>
+      <c r="N174" t="n">
+        <v>820</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>28</v>
+      </c>
+      <c r="R174" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="S174" t="inlineStr"/>
+      <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>M1-5 (5% RHA)</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>475</v>
+      </c>
+      <c r="K175" t="n">
+        <v>25</v>
+      </c>
+      <c r="L175" t="n">
+        <v>5</v>
+      </c>
+      <c r="M175" t="n">
+        <v>780</v>
+      </c>
+      <c r="N175" t="n">
+        <v>820</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>7</v>
+      </c>
+      <c r="R175" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="S175" t="inlineStr"/>
+      <c r="T175" t="inlineStr"/>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>M1-5 (5% RHA)</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>475</v>
+      </c>
+      <c r="K176" t="n">
+        <v>25</v>
+      </c>
+      <c r="L176" t="n">
+        <v>5</v>
+      </c>
+      <c r="M176" t="n">
+        <v>780</v>
+      </c>
+      <c r="N176" t="n">
+        <v>820</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>28</v>
+      </c>
+      <c r="R176" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>M1-7.5 (7.5% RHA)</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="K177" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L177" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M177" t="n">
+        <v>780</v>
+      </c>
+      <c r="N177" t="n">
+        <v>820</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>7</v>
+      </c>
+      <c r="R177" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>M1-7.5 (7.5% RHA)</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="K178" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="L178" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M178" t="n">
+        <v>780</v>
+      </c>
+      <c r="N178" t="n">
+        <v>820</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>28</v>
+      </c>
+      <c r="R178" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>M1-10 (10% RHA)</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>450</v>
+      </c>
+      <c r="K179" t="n">
+        <v>50</v>
+      </c>
+      <c r="L179" t="n">
+        <v>10</v>
+      </c>
+      <c r="M179" t="n">
+        <v>780</v>
+      </c>
+      <c r="N179" t="n">
+        <v>820</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>7</v>
+      </c>
+      <c r="R179" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>M1-10 (10% RHA)</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>450</v>
+      </c>
+      <c r="K180" t="n">
+        <v>50</v>
+      </c>
+      <c r="L180" t="n">
+        <v>10</v>
+      </c>
+      <c r="M180" t="n">
+        <v>780</v>
+      </c>
+      <c r="N180" t="n">
+        <v>820</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>28</v>
+      </c>
+      <c r="R180" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>M2-0 (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>450</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>796.5</v>
+      </c>
+      <c r="N181" t="n">
+        <v>846</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3 (strengths figure-only)</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>M2-2.5 (2.5% RHA)</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>438.75</v>
+      </c>
+      <c r="K182" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="L182" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M182" t="n">
+        <v>796.5</v>
+      </c>
+      <c r="N182" t="n">
+        <v>846</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3 (strengths figure-only)</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>M2-5 (5% RHA)</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>427.5</v>
+      </c>
+      <c r="K183" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L183" t="n">
+        <v>5</v>
+      </c>
+      <c r="M183" t="n">
+        <v>796.5</v>
+      </c>
+      <c r="N183" t="n">
+        <v>846</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3 (strengths figure-only)</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>M2-7.5 (7.5% RHA)</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>416.25</v>
+      </c>
+      <c r="K184" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="L184" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M184" t="n">
+        <v>796.5</v>
+      </c>
+      <c r="N184" t="n">
+        <v>846</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3 (strengths figure-only)</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>M2-10 (10% RHA)</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>405</v>
+      </c>
+      <c r="K185" t="n">
+        <v>45</v>
+      </c>
+      <c r="L185" t="n">
+        <v>10</v>
+      </c>
+      <c r="M185" t="n">
+        <v>796.5</v>
+      </c>
+      <c r="N185" t="n">
+        <v>846</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3 (strengths figure-only)</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>M3-0 (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>400</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>828</v>
+      </c>
+      <c r="N186" t="n">
+        <v>868</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3 (strengths figure-only)</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>M3-2.5 (2.5% RHA)</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>390</v>
+      </c>
+      <c r="K187" t="n">
+        <v>10</v>
+      </c>
+      <c r="L187" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M187" t="n">
+        <v>828</v>
+      </c>
+      <c r="N187" t="n">
+        <v>868</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3 (strengths figure-only)</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="inlineStr"/>
+      <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>M3-5 (5% RHA)</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>380</v>
+      </c>
+      <c r="K188" t="n">
+        <v>20</v>
+      </c>
+      <c r="L188" t="n">
+        <v>5</v>
+      </c>
+      <c r="M188" t="n">
+        <v>828</v>
+      </c>
+      <c r="N188" t="n">
+        <v>868</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3 (strengths figure-only)</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>M3-7.5 (7.5% RHA)</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>370</v>
+      </c>
+      <c r="K189" t="n">
+        <v>30</v>
+      </c>
+      <c r="L189" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M189" t="n">
+        <v>828</v>
+      </c>
+      <c r="N189" t="n">
+        <v>868</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3 (strengths figure-only)</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr"/>
+      <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2022_07</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Optimizing Compressive Strength Properties of Binary Blended Cement Rice Husk Concrete for Road Pavement</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Fitriani, Ahmed, Olonade, Hyndman, Idris, Rosidawani</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Indonesia (Palembang, South Sumatra; Universitas Sriwijaya) / UK pavement mix standard</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Rice mill at Gasing, South Sumatra, Indonesia; burnt at 700C for 1 hour</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Concrete for rigid road pavement (3 mix ratios) with superplasticizer</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>OPC(PCC)+RHA</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>M3-10 (10% RHA)</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>360</v>
+      </c>
+      <c r="K190" t="n">
+        <v>40</v>
+      </c>
+      <c r="L190" t="n">
+        <v>10</v>
+      </c>
+      <c r="M190" t="n">
+        <v>828</v>
+      </c>
+      <c r="N190" t="n">
+        <v>868</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>SP Sika ViscoCrete-5930 150 mL/m3 (strengths figure-only)</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="inlineStr"/>
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Compressive strength only in Figs 6-8; Strength Activity Index tabulated (Table 5). Only M1 control absolutes stated in text (M1-0: 7d 26.6, 28d 31.1 N/mm2). M2/M3 absolutes and all 56d values figure-only.</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. M1 series comp at 7d/28d COMPUTED = stated M1-0 absolute x tabulated SAI (Table 5). M2, M3 and 56d strengths NOT recoverable from text -&gt; left blank.</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>Portland Composite Cement (PCC). w/b 0.4 constant. SP Sika ViscoCrete-5930 at 150 mL/m3. RHA 0/2.5/5/7.5/10% replacing cement by weight, across 3 binder:sand:granite ratios (M1 1:1.56:1.64, M2 1:1.77:1.88, M3 1:2.07:2.17). M1-0 stated 7d=26.6, 28d=31.1 N/mm2 -&gt; M1 series back-computed via SAI; M1 7d SAI 100/115.04/115.04/111.65/94.74; 28d SAI 100/108.68/111.58/100/97.11. M2/M3 mix proportions captured; their strengths and all 56-day strengths are figure-only (blank). 28-day pavement threshold 27.5 N/mm2.</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>Table 3 per-m3 mix proportions (cement, RHA, sand, granite, water). Table 5 Strength Activity Index (%) at 7/28/56d. Text: M1-0 strength 26.6 (7d) -&gt; 31.1 N/mm2 (28d, +17%).</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>2022/07_Optimizing_Compressive_Strength_Properties_of_Binary_Blended_Cement_Rice_Husk_Concrete_for_Road_Pavement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2022_05</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground in Los Angeles abrasion machine (15 or 30 min)</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>OPC concrete with RHA (CM1 series, RHA fineness study) and plain OPC control (CM2)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>FM0 (0% RHA, control)</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>none; batch ratio cement:FA:CA = 3.07:5.38:8.56</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>7</v>
+      </c>
+      <c r="R191" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Tables 7 and 11)</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 7 (CM1) and Table 11 (CM2). CM1 proportions given only as 6-cube batch masses (Table 3), not kg/m3 -&gt; CM1 cement/agg kg/m3 left blank. CM2 proportions in kg/m3 (Table 5).</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>CM1: OPC concrete, RHA fixed at 15% by weight of cement; variable is RHA grinding/fineness (FM0=0% control; FM1=raw RHA; FM2=15 min ground; FM3=30 min ground). Batch (6 cubes): cement 3.07 kg (FM0) / 2.61 kg (FM1-3), RHA 0.46 kg, FA 5.38, CA 8.56, water 1538 mL + 171 mL extra -&gt; w/c ~0.50-0.56. CM2: separate plain OPC control mix, w/c 0.40. Companion alkali-activated (GGBS+RHA, no OPC) series recorded under paper_id 2022_05b.</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>Table 7 comp MPa: FM0 20.5/26.5; FM1 6.63/7.36; FM2 20.93/27.53; FM3 19.86/25.93 (7d/28d). Table 5 CM2 mix: cement 389, CA 1134, FA 710, water 155.57 kg/m3, w/c 0.40. Table 11: CM2 comp 17.89/27.53 (7d/28d).</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2022_05</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground in Los Angeles abrasion machine (15 or 30 min)</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>OPC concrete with RHA (CM1 series, RHA fineness study) and plain OPC control (CM2)</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>FM0 (0% RHA, control)</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>none; batch ratio cement:FA:CA = 3.07:5.38:8.56</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>28</v>
+      </c>
+      <c r="R192" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="S192" t="inlineStr"/>
+      <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Tables 7 and 11)</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 7 (CM1) and Table 11 (CM2). CM1 proportions given only as 6-cube batch masses (Table 3), not kg/m3 -&gt; CM1 cement/agg kg/m3 left blank. CM2 proportions in kg/m3 (Table 5).</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>CM1: OPC concrete, RHA fixed at 15% by weight of cement; variable is RHA grinding/fineness (FM0=0% control; FM1=raw RHA; FM2=15 min ground; FM3=30 min ground). Batch (6 cubes): cement 3.07 kg (FM0) / 2.61 kg (FM1-3), RHA 0.46 kg, FA 5.38, CA 8.56, water 1538 mL + 171 mL extra -&gt; w/c ~0.50-0.56. CM2: separate plain OPC control mix, w/c 0.40. Companion alkali-activated (GGBS+RHA, no OPC) series recorded under paper_id 2022_05b.</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>Table 7 comp MPa: FM0 20.5/26.5; FM1 6.63/7.36; FM2 20.93/27.53; FM3 19.86/25.93 (7d/28d). Table 5 CM2 mix: cement 389, CA 1134, FA 710, water 155.57 kg/m3, w/c 0.40. Table 11: CM2 comp 17.89/27.53 (7d/28d).</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2022_05</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground in Los Angeles abrasion machine (15 or 30 min)</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>OPC concrete with RHA (CM1 series, RHA fineness study) and plain OPC control (CM2)</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>FM1 (15% RHA, raw/unground)</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="n">
+        <v>15</v>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Raw RHA (no grinding), batch RHA 0.46 kg</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>7</v>
+      </c>
+      <c r="R193" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="S193" t="inlineStr"/>
+      <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Tables 7 and 11)</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 7 (CM1) and Table 11 (CM2). CM1 proportions given only as 6-cube batch masses (Table 3), not kg/m3 -&gt; CM1 cement/agg kg/m3 left blank. CM2 proportions in kg/m3 (Table 5).</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>CM1: OPC concrete, RHA fixed at 15% by weight of cement; variable is RHA grinding/fineness (FM0=0% control; FM1=raw RHA; FM2=15 min ground; FM3=30 min ground). Batch (6 cubes): cement 3.07 kg (FM0) / 2.61 kg (FM1-3), RHA 0.46 kg, FA 5.38, CA 8.56, water 1538 mL + 171 mL extra -&gt; w/c ~0.50-0.56. CM2: separate plain OPC control mix, w/c 0.40. Companion alkali-activated (GGBS+RHA, no OPC) series recorded under paper_id 2022_05b.</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>Table 7 comp MPa: FM0 20.5/26.5; FM1 6.63/7.36; FM2 20.93/27.53; FM3 19.86/25.93 (7d/28d). Table 5 CM2 mix: cement 389, CA 1134, FA 710, water 155.57 kg/m3, w/c 0.40. Table 11: CM2 comp 17.89/27.53 (7d/28d).</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2022_05</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground in Los Angeles abrasion machine (15 or 30 min)</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>OPC concrete with RHA (CM1 series, RHA fineness study) and plain OPC control (CM2)</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>FM1 (15% RHA, raw/unground)</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="n">
+        <v>15</v>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Raw RHA (no grinding), batch RHA 0.46 kg</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>28</v>
+      </c>
+      <c r="R194" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="S194" t="inlineStr"/>
+      <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Tables 7 and 11)</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 7 (CM1) and Table 11 (CM2). CM1 proportions given only as 6-cube batch masses (Table 3), not kg/m3 -&gt; CM1 cement/agg kg/m3 left blank. CM2 proportions in kg/m3 (Table 5).</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>CM1: OPC concrete, RHA fixed at 15% by weight of cement; variable is RHA grinding/fineness (FM0=0% control; FM1=raw RHA; FM2=15 min ground; FM3=30 min ground). Batch (6 cubes): cement 3.07 kg (FM0) / 2.61 kg (FM1-3), RHA 0.46 kg, FA 5.38, CA 8.56, water 1538 mL + 171 mL extra -&gt; w/c ~0.50-0.56. CM2: separate plain OPC control mix, w/c 0.40. Companion alkali-activated (GGBS+RHA, no OPC) series recorded under paper_id 2022_05b.</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>Table 7 comp MPa: FM0 20.5/26.5; FM1 6.63/7.36; FM2 20.93/27.53; FM3 19.86/25.93 (7d/28d). Table 5 CM2 mix: cement 389, CA 1134, FA 710, water 155.57 kg/m3, w/c 0.40. Table 11: CM2 comp 17.89/27.53 (7d/28d).</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2022_05</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground in Los Angeles abrasion machine (15 or 30 min)</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>OPC concrete with RHA (CM1 series, RHA fineness study) and plain OPC control (CM2)</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>FM2 (15% RHA, 15 min ground)</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="n">
+        <v>15</v>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>RHA ground 15 min (fineness 310 m2/kg)</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>7</v>
+      </c>
+      <c r="R195" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="S195" t="inlineStr"/>
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Tables 7 and 11)</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 7 (CM1) and Table 11 (CM2). CM1 proportions given only as 6-cube batch masses (Table 3), not kg/m3 -&gt; CM1 cement/agg kg/m3 left blank. CM2 proportions in kg/m3 (Table 5).</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>CM1: OPC concrete, RHA fixed at 15% by weight of cement; variable is RHA grinding/fineness (FM0=0% control; FM1=raw RHA; FM2=15 min ground; FM3=30 min ground). Batch (6 cubes): cement 3.07 kg (FM0) / 2.61 kg (FM1-3), RHA 0.46 kg, FA 5.38, CA 8.56, water 1538 mL + 171 mL extra -&gt; w/c ~0.50-0.56. CM2: separate plain OPC control mix, w/c 0.40. Companion alkali-activated (GGBS+RHA, no OPC) series recorded under paper_id 2022_05b.</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>Table 7 comp MPa: FM0 20.5/26.5; FM1 6.63/7.36; FM2 20.93/27.53; FM3 19.86/25.93 (7d/28d). Table 5 CM2 mix: cement 389, CA 1134, FA 710, water 155.57 kg/m3, w/c 0.40. Table 11: CM2 comp 17.89/27.53 (7d/28d).</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2022_05</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground in Los Angeles abrasion machine (15 or 30 min)</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>OPC concrete with RHA (CM1 series, RHA fineness study) and plain OPC control (CM2)</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>FM2 (15% RHA, 15 min ground)</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="n">
+        <v>15</v>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>RHA ground 15 min (fineness 310 m2/kg)</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>28</v>
+      </c>
+      <c r="R196" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="S196" t="inlineStr"/>
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Tables 7 and 11)</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 7 (CM1) and Table 11 (CM2). CM1 proportions given only as 6-cube batch masses (Table 3), not kg/m3 -&gt; CM1 cement/agg kg/m3 left blank. CM2 proportions in kg/m3 (Table 5).</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>CM1: OPC concrete, RHA fixed at 15% by weight of cement; variable is RHA grinding/fineness (FM0=0% control; FM1=raw RHA; FM2=15 min ground; FM3=30 min ground). Batch (6 cubes): cement 3.07 kg (FM0) / 2.61 kg (FM1-3), RHA 0.46 kg, FA 5.38, CA 8.56, water 1538 mL + 171 mL extra -&gt; w/c ~0.50-0.56. CM2: separate plain OPC control mix, w/c 0.40. Companion alkali-activated (GGBS+RHA, no OPC) series recorded under paper_id 2022_05b.</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>Table 7 comp MPa: FM0 20.5/26.5; FM1 6.63/7.36; FM2 20.93/27.53; FM3 19.86/25.93 (7d/28d). Table 5 CM2 mix: cement 389, CA 1134, FA 710, water 155.57 kg/m3, w/c 0.40. Table 11: CM2 comp 17.89/27.53 (7d/28d).</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2022_05</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground in Los Angeles abrasion machine (15 or 30 min)</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>OPC concrete with RHA (CM1 series, RHA fineness study) and plain OPC control (CM2)</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>FM3 (15% RHA, 30 min ground)</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="n">
+        <v>15</v>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>RHA ground 30 min (fineness 800 m2/kg)</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>7</v>
+      </c>
+      <c r="R197" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="S197" t="inlineStr"/>
+      <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Tables 7 and 11)</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 7 (CM1) and Table 11 (CM2). CM1 proportions given only as 6-cube batch masses (Table 3), not kg/m3 -&gt; CM1 cement/agg kg/m3 left blank. CM2 proportions in kg/m3 (Table 5).</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>CM1: OPC concrete, RHA fixed at 15% by weight of cement; variable is RHA grinding/fineness (FM0=0% control; FM1=raw RHA; FM2=15 min ground; FM3=30 min ground). Batch (6 cubes): cement 3.07 kg (FM0) / 2.61 kg (FM1-3), RHA 0.46 kg, FA 5.38, CA 8.56, water 1538 mL + 171 mL extra -&gt; w/c ~0.50-0.56. CM2: separate plain OPC control mix, w/c 0.40. Companion alkali-activated (GGBS+RHA, no OPC) series recorded under paper_id 2022_05b.</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>Table 7 comp MPa: FM0 20.5/26.5; FM1 6.63/7.36; FM2 20.93/27.53; FM3 19.86/25.93 (7d/28d). Table 5 CM2 mix: cement 389, CA 1134, FA 710, water 155.57 kg/m3, w/c 0.40. Table 11: CM2 comp 17.89/27.53 (7d/28d).</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2022_05</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground in Los Angeles abrasion machine (15 or 30 min)</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>OPC concrete with RHA (CM1 series, RHA fineness study) and plain OPC control (CM2)</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>FM3 (15% RHA, 30 min ground)</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="n">
+        <v>15</v>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>RHA ground 30 min (fineness 800 m2/kg)</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>28</v>
+      </c>
+      <c r="R198" t="n">
+        <v>25.93</v>
+      </c>
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Tables 7 and 11)</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 7 (CM1) and Table 11 (CM2). CM1 proportions given only as 6-cube batch masses (Table 3), not kg/m3 -&gt; CM1 cement/agg kg/m3 left blank. CM2 proportions in kg/m3 (Table 5).</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>CM1: OPC concrete, RHA fixed at 15% by weight of cement; variable is RHA grinding/fineness (FM0=0% control; FM1=raw RHA; FM2=15 min ground; FM3=30 min ground). Batch (6 cubes): cement 3.07 kg (FM0) / 2.61 kg (FM1-3), RHA 0.46 kg, FA 5.38, CA 8.56, water 1538 mL + 171 mL extra -&gt; w/c ~0.50-0.56. CM2: separate plain OPC control mix, w/c 0.40. Companion alkali-activated (GGBS+RHA, no OPC) series recorded under paper_id 2022_05b.</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>Table 7 comp MPa: FM0 20.5/26.5; FM1 6.63/7.36; FM2 20.93/27.53; FM3 19.86/25.93 (7d/28d). Table 5 CM2 mix: cement 389, CA 1134, FA 710, water 155.57 kg/m3, w/c 0.40. Table 11: CM2 comp 17.89/27.53 (7d/28d).</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2022_05</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground in Los Angeles abrasion machine (15 or 30 min)</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>OPC concrete with RHA (CM1 series, RHA fineness study) and plain OPC control (CM2)</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>CM2 (plain OPC control)</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>389</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>710</v>
+      </c>
+      <c r="N199" t="n">
+        <v>1134</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>7</v>
+      </c>
+      <c r="R199" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="S199" t="inlineStr"/>
+      <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Tables 7 and 11)</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 7 (CM1) and Table 11 (CM2). CM1 proportions given only as 6-cube batch masses (Table 3), not kg/m3 -&gt; CM1 cement/agg kg/m3 left blank. CM2 proportions in kg/m3 (Table 5).</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>CM1: OPC concrete, RHA fixed at 15% by weight of cement; variable is RHA grinding/fineness (FM0=0% control; FM1=raw RHA; FM2=15 min ground; FM3=30 min ground). Batch (6 cubes): cement 3.07 kg (FM0) / 2.61 kg (FM1-3), RHA 0.46 kg, FA 5.38, CA 8.56, water 1538 mL + 171 mL extra -&gt; w/c ~0.50-0.56. CM2: separate plain OPC control mix, w/c 0.40. Companion alkali-activated (GGBS+RHA, no OPC) series recorded under paper_id 2022_05b.</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>Table 7 comp MPa: FM0 20.5/26.5; FM1 6.63/7.36; FM2 20.93/27.53; FM3 19.86/25.93 (7d/28d). Table 5 CM2 mix: cement 389, CA 1134, FA 710, water 155.57 kg/m3, w/c 0.40. Table 11: CM2 comp 17.89/27.53 (7d/28d).</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2022_05</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground in Los Angeles abrasion machine (15 or 30 min)</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>OPC concrete with RHA (CM1 series, RHA fineness study) and plain OPC control (CM2)</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>CM2 (plain OPC control)</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>389</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>710</v>
+      </c>
+      <c r="N200" t="n">
+        <v>1134</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>28</v>
+      </c>
+      <c r="R200" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="S200" t="inlineStr"/>
+      <c r="T200" t="inlineStr"/>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Tables 7 and 11)</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 7 (CM1) and Table 11 (CM2). CM1 proportions given only as 6-cube batch masses (Table 3), not kg/m3 -&gt; CM1 cement/agg kg/m3 left blank. CM2 proportions in kg/m3 (Table 5).</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>CM1: OPC concrete, RHA fixed at 15% by weight of cement; variable is RHA grinding/fineness (FM0=0% control; FM1=raw RHA; FM2=15 min ground; FM3=30 min ground). Batch (6 cubes): cement 3.07 kg (FM0) / 2.61 kg (FM1-3), RHA 0.46 kg, FA 5.38, CA 8.56, water 1538 mL + 171 mL extra -&gt; w/c ~0.50-0.56. CM2: separate plain OPC control mix, w/c 0.40. Companion alkali-activated (GGBS+RHA, no OPC) series recorded under paper_id 2022_05b.</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>Table 7 comp MPa: FM0 20.5/26.5; FM1 6.63/7.36; FM2 20.93/27.53; FM3 19.86/25.93 (7d/28d). Table 5 CM2 mix: cement 389, CA 1134, FA 710, water 155.57 kg/m3, w/c 0.40. Table 11: CM2 comp 17.89/27.53 (7d/28d).</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2022_05b</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete (alkali-activated GGBS+RHA series)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground (15 min)</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Alkali-activated concrete (GGBS + RHA binder, NaOH 10M activator; NO Portland cement)</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Alkali-activated GGBS+RHA (no OPC)</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>M0 (0% RHA, GGBS only)</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>710</v>
+      </c>
+      <c r="N201" t="n">
+        <v>1134</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>GGBS 328 kg/m3; NaOH 10M 213.2 kg/m3; a/b 0.65; no OPC</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="n">
+        <v>7</v>
+      </c>
+      <c r="R201" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="S201" t="inlineStr"/>
+      <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Table 9)</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 4; comp MPa verbatim from Table 9.</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>NOT OPC concrete - alkali-activated (geopolymer) binder. RHA replaces GGBS (slag) at 0/10/20/30% of total binder. No cement; cement_kg_m3 left blank. Alkali activator solution/binder (a/b) ratio 0.65; NaOH 10 molar (213.2 kg/m3). GGBS per mix: M0 328, M1 295.2, M2 262.4, M3 229.6 kg/m3. rha_pct here = % of total binder (GGBS+RHA). Provided with binder flag so it can be filtered out of OPC-only modeling.</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>Table 4 mix (kg/m3): GGBS 328/295.2/262.4/229.6; RHA 0/32.8/65.6/98.4; CA 1134; FA 710; NaOH 213.2; a/b 0.65. Table 9 comp MPa 7d/28d: M0 4.46/24.6; M1 12/27.33; M2 9.6/25.4; M3 9.2/24.23.</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2022_05b</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete (alkali-activated GGBS+RHA series)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground (15 min)</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Alkali-activated concrete (GGBS + RHA binder, NaOH 10M activator; NO Portland cement)</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Alkali-activated GGBS+RHA (no OPC)</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>M0 (0% RHA, GGBS only)</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
+        <v>710</v>
+      </c>
+      <c r="N202" t="n">
+        <v>1134</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>GGBS 328 kg/m3; NaOH 10M 213.2 kg/m3; a/b 0.65; no OPC</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="n">
+        <v>28</v>
+      </c>
+      <c r="R202" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="S202" t="inlineStr"/>
+      <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Table 9)</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 4; comp MPa verbatim from Table 9.</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>NOT OPC concrete - alkali-activated (geopolymer) binder. RHA replaces GGBS (slag) at 0/10/20/30% of total binder. No cement; cement_kg_m3 left blank. Alkali activator solution/binder (a/b) ratio 0.65; NaOH 10 molar (213.2 kg/m3). GGBS per mix: M0 328, M1 295.2, M2 262.4, M3 229.6 kg/m3. rha_pct here = % of total binder (GGBS+RHA). Provided with binder flag so it can be filtered out of OPC-only modeling.</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>Table 4 mix (kg/m3): GGBS 328/295.2/262.4/229.6; RHA 0/32.8/65.6/98.4; CA 1134; FA 710; NaOH 213.2; a/b 0.65. Table 9 comp MPa 7d/28d: M0 4.46/24.6; M1 12/27.33; M2 9.6/25.4; M3 9.2/24.23.</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2022_05b</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete (alkali-activated GGBS+RHA series)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground (15 min)</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Alkali-activated concrete (GGBS + RHA binder, NaOH 10M activator; NO Portland cement)</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Alkali-activated GGBS+RHA (no OPC)</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>M1 (10% RHA of binder)</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="L203" t="n">
+        <v>10</v>
+      </c>
+      <c r="M203" t="n">
+        <v>710</v>
+      </c>
+      <c r="N203" t="n">
+        <v>1134</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>GGBS 295.2 kg/m3; NaOH 10M 213.2 kg/m3; a/b 0.65; no OPC</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="n">
+        <v>7</v>
+      </c>
+      <c r="R203" t="n">
+        <v>12</v>
+      </c>
+      <c r="S203" t="inlineStr"/>
+      <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Table 9)</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 4; comp MPa verbatim from Table 9.</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>NOT OPC concrete - alkali-activated (geopolymer) binder. RHA replaces GGBS (slag) at 0/10/20/30% of total binder. No cement; cement_kg_m3 left blank. Alkali activator solution/binder (a/b) ratio 0.65; NaOH 10 molar (213.2 kg/m3). GGBS per mix: M0 328, M1 295.2, M2 262.4, M3 229.6 kg/m3. rha_pct here = % of total binder (GGBS+RHA). Provided with binder flag so it can be filtered out of OPC-only modeling.</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>Table 4 mix (kg/m3): GGBS 328/295.2/262.4/229.6; RHA 0/32.8/65.6/98.4; CA 1134; FA 710; NaOH 213.2; a/b 0.65. Table 9 comp MPa 7d/28d: M0 4.46/24.6; M1 12/27.33; M2 9.6/25.4; M3 9.2/24.23.</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2022_05b</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete (alkali-activated GGBS+RHA series)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground (15 min)</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Alkali-activated concrete (GGBS + RHA binder, NaOH 10M activator; NO Portland cement)</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Alkali-activated GGBS+RHA (no OPC)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>M1 (10% RHA of binder)</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="L204" t="n">
+        <v>10</v>
+      </c>
+      <c r="M204" t="n">
+        <v>710</v>
+      </c>
+      <c r="N204" t="n">
+        <v>1134</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>GGBS 295.2 kg/m3; NaOH 10M 213.2 kg/m3; a/b 0.65; no OPC</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="n">
+        <v>28</v>
+      </c>
+      <c r="R204" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Table 9)</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 4; comp MPa verbatim from Table 9.</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>NOT OPC concrete - alkali-activated (geopolymer) binder. RHA replaces GGBS (slag) at 0/10/20/30% of total binder. No cement; cement_kg_m3 left blank. Alkali activator solution/binder (a/b) ratio 0.65; NaOH 10 molar (213.2 kg/m3). GGBS per mix: M0 328, M1 295.2, M2 262.4, M3 229.6 kg/m3. rha_pct here = % of total binder (GGBS+RHA). Provided with binder flag so it can be filtered out of OPC-only modeling.</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>Table 4 mix (kg/m3): GGBS 328/295.2/262.4/229.6; RHA 0/32.8/65.6/98.4; CA 1134; FA 710; NaOH 213.2; a/b 0.65. Table 9 comp MPa 7d/28d: M0 4.46/24.6; M1 12/27.33; M2 9.6/25.4; M3 9.2/24.23.</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2022_05b</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete (alkali-activated GGBS+RHA series)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground (15 min)</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Alkali-activated concrete (GGBS + RHA binder, NaOH 10M activator; NO Portland cement)</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Alkali-activated GGBS+RHA (no OPC)</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>M2 (20% RHA of binder)</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="L205" t="n">
+        <v>20</v>
+      </c>
+      <c r="M205" t="n">
+        <v>710</v>
+      </c>
+      <c r="N205" t="n">
+        <v>1134</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>GGBS 262.4 kg/m3; NaOH 10M 213.2 kg/m3; a/b 0.65; no OPC</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="n">
+        <v>7</v>
+      </c>
+      <c r="R205" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Table 9)</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 4; comp MPa verbatim from Table 9.</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>NOT OPC concrete - alkali-activated (geopolymer) binder. RHA replaces GGBS (slag) at 0/10/20/30% of total binder. No cement; cement_kg_m3 left blank. Alkali activator solution/binder (a/b) ratio 0.65; NaOH 10 molar (213.2 kg/m3). GGBS per mix: M0 328, M1 295.2, M2 262.4, M3 229.6 kg/m3. rha_pct here = % of total binder (GGBS+RHA). Provided with binder flag so it can be filtered out of OPC-only modeling.</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>Table 4 mix (kg/m3): GGBS 328/295.2/262.4/229.6; RHA 0/32.8/65.6/98.4; CA 1134; FA 710; NaOH 213.2; a/b 0.65. Table 9 comp MPa 7d/28d: M0 4.46/24.6; M1 12/27.33; M2 9.6/25.4; M3 9.2/24.23.</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2022_05b</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete (alkali-activated GGBS+RHA series)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground (15 min)</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Alkali-activated concrete (GGBS + RHA binder, NaOH 10M activator; NO Portland cement)</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Alkali-activated GGBS+RHA (no OPC)</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>M2 (20% RHA of binder)</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="L206" t="n">
+        <v>20</v>
+      </c>
+      <c r="M206" t="n">
+        <v>710</v>
+      </c>
+      <c r="N206" t="n">
+        <v>1134</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>GGBS 262.4 kg/m3; NaOH 10M 213.2 kg/m3; a/b 0.65; no OPC</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="n">
+        <v>28</v>
+      </c>
+      <c r="R206" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="S206" t="inlineStr"/>
+      <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Table 9)</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 4; comp MPa verbatim from Table 9.</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>NOT OPC concrete - alkali-activated (geopolymer) binder. RHA replaces GGBS (slag) at 0/10/20/30% of total binder. No cement; cement_kg_m3 left blank. Alkali activator solution/binder (a/b) ratio 0.65; NaOH 10 molar (213.2 kg/m3). GGBS per mix: M0 328, M1 295.2, M2 262.4, M3 229.6 kg/m3. rha_pct here = % of total binder (GGBS+RHA). Provided with binder flag so it can be filtered out of OPC-only modeling.</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>Table 4 mix (kg/m3): GGBS 328/295.2/262.4/229.6; RHA 0/32.8/65.6/98.4; CA 1134; FA 710; NaOH 213.2; a/b 0.65. Table 9 comp MPa 7d/28d: M0 4.46/24.6; M1 12/27.33; M2 9.6/25.4; M3 9.2/24.23.</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2022_05b</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete (alkali-activated GGBS+RHA series)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground (15 min)</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Alkali-activated concrete (GGBS + RHA binder, NaOH 10M activator; NO Portland cement)</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Alkali-activated GGBS+RHA (no OPC)</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>M3 (30% RHA of binder)</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="L207" t="n">
+        <v>30</v>
+      </c>
+      <c r="M207" t="n">
+        <v>710</v>
+      </c>
+      <c r="N207" t="n">
+        <v>1134</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>GGBS 229.6 kg/m3; NaOH 10M 213.2 kg/m3; a/b 0.65; no OPC</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="n">
+        <v>7</v>
+      </c>
+      <c r="R207" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Table 9)</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 4; comp MPa verbatim from Table 9.</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>NOT OPC concrete - alkali-activated (geopolymer) binder. RHA replaces GGBS (slag) at 0/10/20/30% of total binder. No cement; cement_kg_m3 left blank. Alkali activator solution/binder (a/b) ratio 0.65; NaOH 10 molar (213.2 kg/m3). GGBS per mix: M0 328, M1 295.2, M2 262.4, M3 229.6 kg/m3. rha_pct here = % of total binder (GGBS+RHA). Provided with binder flag so it can be filtered out of OPC-only modeling.</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>Table 4 mix (kg/m3): GGBS 328/295.2/262.4/229.6; RHA 0/32.8/65.6/98.4; CA 1134; FA 710; NaOH 213.2; a/b 0.65. Table 9 comp MPa 7d/28d: M0 4.46/24.6; M1 12/27.33; M2 9.6/25.4; M3 9.2/24.23.</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2022_05b</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Study on Slag-Rice Husk Ash based Alkali Activated Concrete (alkali-activated GGBS+RHA series)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Das, Laskar, Hussain</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>India (Assam; Jorhat Engineering College / NIT Mizoram)</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Agro-based biomass industry, Assam, India; ground (15 min)</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Alkali-activated concrete (GGBS + RHA binder, NaOH 10M activator; NO Portland cement)</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Alkali-activated GGBS+RHA (no OPC)</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>M3 (30% RHA of binder)</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="L208" t="n">
+        <v>30</v>
+      </c>
+      <c r="M208" t="n">
+        <v>710</v>
+      </c>
+      <c r="N208" t="n">
+        <v>1134</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>GGBS 229.6 kg/m3; NaOH 10M 213.2 kg/m3; a/b 0.65; no OPC</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="n">
+        <v>28</v>
+      </c>
+      <c r="R208" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="S208" t="inlineStr"/>
+      <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Compressive strength tabulated at 7 and 28 days (Table 9)</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 4; comp MPa verbatim from Table 9.</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>NOT OPC concrete - alkali-activated (geopolymer) binder. RHA replaces GGBS (slag) at 0/10/20/30% of total binder. No cement; cement_kg_m3 left blank. Alkali activator solution/binder (a/b) ratio 0.65; NaOH 10 molar (213.2 kg/m3). GGBS per mix: M0 328, M1 295.2, M2 262.4, M3 229.6 kg/m3. rha_pct here = % of total binder (GGBS+RHA). Provided with binder flag so it can be filtered out of OPC-only modeling.</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>Table 4 mix (kg/m3): GGBS 328/295.2/262.4/229.6; RHA 0/32.8/65.6/98.4; CA 1134; FA 710; NaOH 213.2; a/b 0.65. Table 9 comp MPa 7d/28d: M0 4.46/24.6; M1 12/27.33; M2 9.6/25.4; M3 9.2/24.23.</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>2022/05_Study_on_Slag-Rice_Husk_Ash_based_Alkali_Activated_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2022_14</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Quantification of Hydration Products in Rice Husk Ash (RHA)-Blended Cement Concrete with Crumb Waste Rubber Tires (CWRT) and its Correlation with Mechanical Performance</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>David, De Jesus, Mendoza</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Philippines (De La Salle University)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Open-air burning (RHA-O), Philippines; ground in Los Angeles abrasion machine to ASTM C618 fineness</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>RHA-blended cement concrete with crumb waste rubber tire (CWRT) as fine-aggregate replacement</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>R0C0 (control, 0% RHA, 0% rubber)</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>418</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>779</v>
+      </c>
+      <c r="N209" t="n">
+        <v>1151</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>CWRT 0</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>28</v>
+      </c>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Compressive and splitting tensile (28 days) only in Fig 6; only split tensile R17.5C0 = 3.06 MPa stated in text (+31.2% vs control -&gt; control 2.33 MPa derived). Comp absolutes not stated -&gt; blank.</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. Split tensile R17.5C0 = 3.06 MPa verbatim; control R0C0 split = 2.33 COMPUTED (3.06/1.312). All compressive strengths and remaining split values are figure-only -&gt; blank.</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Concrete per ACI 211.1 at w/c 0.5 (note: batch water 241 / binder 418 ~ 0.58; reported design w/c 0.5). RHA-O fixed at 17.5% of cement; CWRT replaces fine aggregate by volume at 0/5/10/15%. Mortar series (Table 2) and high-temperature data also in paper but strengths figure-only. Optimal: 17.5% RHA-O + 5% CWRT comparable comp + higher split than control.</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>Table 3 (kg/m3, w/c 0.5): R0C0 cement 418/RHA 0/FA 779/CWRT 0/CA 1151/water 241; R0C10 418/0/701/38/1151/241; R17.5C0 345/73/779/0/1151/241; R17.5C5 345/73/740/19/1151/241; R17.5C10 345/73/701/38/1151/241; R17.5C15 345/73/662/57/1151/241. Split tensile R17.5C0 3.06 MPa (+31.2%); RHA-O+CWRT split +7.2% to +15.1% of control.</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>2022/14_QUANTIFICATION_OF_HYDRATION_PRODUCTS_IN_RICE_HUSK_ASH_RHA-BLENDED_CEMENT_CONCRETE_WITH_CRUMB_WASTE_RUBBER_TIRES_CWRT_amp.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2022_14</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Quantification of Hydration Products in Rice Husk Ash (RHA)-Blended Cement Concrete with Crumb Waste Rubber Tires (CWRT) and its Correlation with Mechanical Performance</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>David, De Jesus, Mendoza</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Philippines (De La Salle University)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Open-air burning (RHA-O), Philippines; ground in Los Angeles abrasion machine to ASTM C618 fineness</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>RHA-blended cement concrete with crumb waste rubber tire (CWRT) as fine-aggregate replacement</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>R0C10 (0% RHA, 10% CWRT)</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>418</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
+        <v>701</v>
+      </c>
+      <c r="N210" t="n">
+        <v>1151</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Crumb waste rubber tire (CWRT) 38 kg/m3 (10% of fine agg by vol)</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Compressive and splitting tensile (28 days) only in Fig 6; only split tensile R17.5C0 = 3.06 MPa stated in text (+31.2% vs control -&gt; control 2.33 MPa derived). Comp absolutes not stated -&gt; blank.</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. Split tensile R17.5C0 = 3.06 MPa verbatim; control R0C0 split = 2.33 COMPUTED (3.06/1.312). All compressive strengths and remaining split values are figure-only -&gt; blank.</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Concrete per ACI 211.1 at w/c 0.5 (note: batch water 241 / binder 418 ~ 0.58; reported design w/c 0.5). RHA-O fixed at 17.5% of cement; CWRT replaces fine aggregate by volume at 0/5/10/15%. Mortar series (Table 2) and high-temperature data also in paper but strengths figure-only. Optimal: 17.5% RHA-O + 5% CWRT comparable comp + higher split than control.</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>Table 3 (kg/m3, w/c 0.5): R0C0 cement 418/RHA 0/FA 779/CWRT 0/CA 1151/water 241; R0C10 418/0/701/38/1151/241; R17.5C0 345/73/779/0/1151/241; R17.5C5 345/73/740/19/1151/241; R17.5C10 345/73/701/38/1151/241; R17.5C15 345/73/662/57/1151/241. Split tensile R17.5C0 3.06 MPa (+31.2%); RHA-O+CWRT split +7.2% to +15.1% of control.</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>2022/14_QUANTIFICATION_OF_HYDRATION_PRODUCTS_IN_RICE_HUSK_ASH_RHA-BLENDED_CEMENT_CONCRETE_WITH_CRUMB_WASTE_RUBBER_TIRES_CWRT_amp.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2022_14</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Quantification of Hydration Products in Rice Husk Ash (RHA)-Blended Cement Concrete with Crumb Waste Rubber Tires (CWRT) and its Correlation with Mechanical Performance</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>David, De Jesus, Mendoza</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Philippines (De La Salle University)</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Open-air burning (RHA-O), Philippines; ground in Los Angeles abrasion machine to ASTM C618 fineness</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>RHA-blended cement concrete with crumb waste rubber tire (CWRT) as fine-aggregate replacement</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>R17.5C0 (17.5% RHA, 0% rubber)</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>345</v>
+      </c>
+      <c r="K211" t="n">
+        <v>73</v>
+      </c>
+      <c r="L211" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="M211" t="n">
+        <v>779</v>
+      </c>
+      <c r="N211" t="n">
+        <v>1151</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>CWRT 0</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>28</v>
+      </c>
+      <c r="R211" t="inlineStr"/>
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Compressive and splitting tensile (28 days) only in Fig 6; only split tensile R17.5C0 = 3.06 MPa stated in text (+31.2% vs control -&gt; control 2.33 MPa derived). Comp absolutes not stated -&gt; blank.</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. Split tensile R17.5C0 = 3.06 MPa verbatim; control R0C0 split = 2.33 COMPUTED (3.06/1.312). All compressive strengths and remaining split values are figure-only -&gt; blank.</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Concrete per ACI 211.1 at w/c 0.5 (note: batch water 241 / binder 418 ~ 0.58; reported design w/c 0.5). RHA-O fixed at 17.5% of cement; CWRT replaces fine aggregate by volume at 0/5/10/15%. Mortar series (Table 2) and high-temperature data also in paper but strengths figure-only. Optimal: 17.5% RHA-O + 5% CWRT comparable comp + higher split than control.</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>Table 3 (kg/m3, w/c 0.5): R0C0 cement 418/RHA 0/FA 779/CWRT 0/CA 1151/water 241; R0C10 418/0/701/38/1151/241; R17.5C0 345/73/779/0/1151/241; R17.5C5 345/73/740/19/1151/241; R17.5C10 345/73/701/38/1151/241; R17.5C15 345/73/662/57/1151/241. Split tensile R17.5C0 3.06 MPa (+31.2%); RHA-O+CWRT split +7.2% to +15.1% of control.</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>2022/14_QUANTIFICATION_OF_HYDRATION_PRODUCTS_IN_RICE_HUSK_ASH_RHA-BLENDED_CEMENT_CONCRETE_WITH_CRUMB_WASTE_RUBBER_TIRES_CWRT_amp.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2022_14</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Quantification of Hydration Products in Rice Husk Ash (RHA)-Blended Cement Concrete with Crumb Waste Rubber Tires (CWRT) and its Correlation with Mechanical Performance</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>David, De Jesus, Mendoza</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Philippines (De La Salle University)</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Open-air burning (RHA-O), Philippines; ground in Los Angeles abrasion machine to ASTM C618 fineness</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>RHA-blended cement concrete with crumb waste rubber tire (CWRT) as fine-aggregate replacement</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>R17.5C5 (17.5% RHA, 5% CWRT)</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>345</v>
+      </c>
+      <c r="K212" t="n">
+        <v>73</v>
+      </c>
+      <c r="L212" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="M212" t="n">
+        <v>740</v>
+      </c>
+      <c r="N212" t="n">
+        <v>1151</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Crumb waste rubber tire (CWRT) 19 kg/m3 (5% of fine agg by vol)</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Compressive and splitting tensile (28 days) only in Fig 6; only split tensile R17.5C0 = 3.06 MPa stated in text (+31.2% vs control -&gt; control 2.33 MPa derived). Comp absolutes not stated -&gt; blank.</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. Split tensile R17.5C0 = 3.06 MPa verbatim; control R0C0 split = 2.33 COMPUTED (3.06/1.312). All compressive strengths and remaining split values are figure-only -&gt; blank.</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Concrete per ACI 211.1 at w/c 0.5 (note: batch water 241 / binder 418 ~ 0.58; reported design w/c 0.5). RHA-O fixed at 17.5% of cement; CWRT replaces fine aggregate by volume at 0/5/10/15%. Mortar series (Table 2) and high-temperature data also in paper but strengths figure-only. Optimal: 17.5% RHA-O + 5% CWRT comparable comp + higher split than control.</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>Table 3 (kg/m3, w/c 0.5): R0C0 cement 418/RHA 0/FA 779/CWRT 0/CA 1151/water 241; R0C10 418/0/701/38/1151/241; R17.5C0 345/73/779/0/1151/241; R17.5C5 345/73/740/19/1151/241; R17.5C10 345/73/701/38/1151/241; R17.5C15 345/73/662/57/1151/241. Split tensile R17.5C0 3.06 MPa (+31.2%); RHA-O+CWRT split +7.2% to +15.1% of control.</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>2022/14_QUANTIFICATION_OF_HYDRATION_PRODUCTS_IN_RICE_HUSK_ASH_RHA-BLENDED_CEMENT_CONCRETE_WITH_CRUMB_WASTE_RUBBER_TIRES_CWRT_amp.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2022_14</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Quantification of Hydration Products in Rice Husk Ash (RHA)-Blended Cement Concrete with Crumb Waste Rubber Tires (CWRT) and its Correlation with Mechanical Performance</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>David, De Jesus, Mendoza</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Philippines (De La Salle University)</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Open-air burning (RHA-O), Philippines; ground in Los Angeles abrasion machine to ASTM C618 fineness</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>RHA-blended cement concrete with crumb waste rubber tire (CWRT) as fine-aggregate replacement</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>R17.5C10 (17.5% RHA, 10% CWRT)</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>345</v>
+      </c>
+      <c r="K213" t="n">
+        <v>73</v>
+      </c>
+      <c r="L213" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="M213" t="n">
+        <v>701</v>
+      </c>
+      <c r="N213" t="n">
+        <v>1151</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Crumb waste rubber tire (CWRT) 38 kg/m3 (10% of fine agg by vol)</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="inlineStr"/>
+      <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Compressive and splitting tensile (28 days) only in Fig 6; only split tensile R17.5C0 = 3.06 MPa stated in text (+31.2% vs control -&gt; control 2.33 MPa derived). Comp absolutes not stated -&gt; blank.</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. Split tensile R17.5C0 = 3.06 MPa verbatim; control R0C0 split = 2.33 COMPUTED (3.06/1.312). All compressive strengths and remaining split values are figure-only -&gt; blank.</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Concrete per ACI 211.1 at w/c 0.5 (note: batch water 241 / binder 418 ~ 0.58; reported design w/c 0.5). RHA-O fixed at 17.5% of cement; CWRT replaces fine aggregate by volume at 0/5/10/15%. Mortar series (Table 2) and high-temperature data also in paper but strengths figure-only. Optimal: 17.5% RHA-O + 5% CWRT comparable comp + higher split than control.</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>Table 3 (kg/m3, w/c 0.5): R0C0 cement 418/RHA 0/FA 779/CWRT 0/CA 1151/water 241; R0C10 418/0/701/38/1151/241; R17.5C0 345/73/779/0/1151/241; R17.5C5 345/73/740/19/1151/241; R17.5C10 345/73/701/38/1151/241; R17.5C15 345/73/662/57/1151/241. Split tensile R17.5C0 3.06 MPa (+31.2%); RHA-O+CWRT split +7.2% to +15.1% of control.</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>2022/14_QUANTIFICATION_OF_HYDRATION_PRODUCTS_IN_RICE_HUSK_ASH_RHA-BLENDED_CEMENT_CONCRETE_WITH_CRUMB_WASTE_RUBBER_TIRES_CWRT_amp.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2022_14</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Quantification of Hydration Products in Rice Husk Ash (RHA)-Blended Cement Concrete with Crumb Waste Rubber Tires (CWRT) and its Correlation with Mechanical Performance</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>David, De Jesus, Mendoza</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Philippines (De La Salle University)</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Open-air burning (RHA-O), Philippines; ground in Los Angeles abrasion machine to ASTM C618 fineness</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>RHA-blended cement concrete with crumb waste rubber tire (CWRT) as fine-aggregate replacement</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>R17.5C15 (17.5% RHA, 15% CWRT)</t>
+        </is>
+      </c>
+      <c r="J214" t="n">
+        <v>345</v>
+      </c>
+      <c r="K214" t="n">
+        <v>73</v>
+      </c>
+      <c r="L214" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="M214" t="n">
+        <v>662</v>
+      </c>
+      <c r="N214" t="n">
+        <v>1151</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Crumb waste rubber tire (CWRT) 57 kg/m3 (15% of fine agg by vol)</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
+      <c r="S214" t="inlineStr"/>
+      <c r="T214" t="inlineStr"/>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Compressive and splitting tensile (28 days) only in Fig 6; only split tensile R17.5C0 = 3.06 MPa stated in text (+31.2% vs control -&gt; control 2.33 MPa derived). Comp absolutes not stated -&gt; blank.</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 3. Split tensile R17.5C0 = 3.06 MPa verbatim; control R0C0 split = 2.33 COMPUTED (3.06/1.312). All compressive strengths and remaining split values are figure-only -&gt; blank.</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr">
+        <is>
+          <t>Concrete per ACI 211.1 at w/c 0.5 (note: batch water 241 / binder 418 ~ 0.58; reported design w/c 0.5). RHA-O fixed at 17.5% of cement; CWRT replaces fine aggregate by volume at 0/5/10/15%. Mortar series (Table 2) and high-temperature data also in paper but strengths figure-only. Optimal: 17.5% RHA-O + 5% CWRT comparable comp + higher split than control.</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>Table 3 (kg/m3, w/c 0.5): R0C0 cement 418/RHA 0/FA 779/CWRT 0/CA 1151/water 241; R0C10 418/0/701/38/1151/241; R17.5C0 345/73/779/0/1151/241; R17.5C5 345/73/740/19/1151/241; R17.5C10 345/73/701/38/1151/241; R17.5C15 345/73/662/57/1151/241. Split tensile R17.5C0 3.06 MPa (+31.2%); RHA-O+CWRT split +7.2% to +15.1% of control.</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>2022/14_QUANTIFICATION_OF_HYDRATION_PRODUCTS_IN_RICE_HUSK_ASH_RHA-BLENDED_CEMENT_CONCRETE_WITH_CRUMB_WASTE_RUBBER_TIRES_CWRT_amp.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13197,7 +22613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13525,6 +22941,206 @@
       <c r="D16" t="inlineStr">
         <is>
           <t>Biochemical extraction from rice husk; no concrete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2022_01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Factors affecting the CO2 emissions, cost efficiency and eco-strength efficiency of concrete containing rice husk ash: A database study</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Database/meta-analysis compiling &gt;1000 RHA-concrete data points from the literature; individual mix+strength rows are in Table 1 / supplementary (not cleanly in body text). Logged in Cited_sources_to_fetch as a high-priority bulk source rather than extracted here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2022_02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Optimization of Green Concrete Containing Fly Ash and Rice Husk Ash Based on Hydro-Mechanical Properties and Life Cycle Assessment Considerations</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ANN/EPR model-development paper built on a compiled literature database (additional SCM was either FA OR RHA, not both); no new primary experimental RHA mix+strength rows extractable from body text. Compiled DB noted in Cited_sources_to_fetch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2022_04</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Soft computing models to predict the compressive strength of GGBS/FA-geopolymer concrete</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GGBS/FA geopolymer compressive-strength ML modeling; no rice husk ash, no new experimental RHA mix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2022_06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Green Concrete: An Eco-Friendly Alternative to the OPC Concrete</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Review article (fly ash/RHA/silica fume/GGBFS/glass); only qualitative trends and figure values cited from other studies; no primary experimental mix+strength data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2022_08</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Performance Evaluation of Rice-husk Ash Based Bacterial Concrete</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bacterial self-healing RHA concrete; RHA described as fine-aggregate substitute (0/5/10/15) and cube notations (F/G/C/FB/CB/GB) are not mapped to RHA% in the text, so rows cannot be reliably assigned. Single mix design (w/c 0.46; cement 406.22, fine 523.64, coarse 1244.40 kg/m3) noted but not extractable per-RHA-level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2022_09</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Use of recycled coal bottom ash in reinforced concrete beams as replacement for aggregate</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Recycled coal bottom ash as aggregate replacement; no rice husk ash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2022_11</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Evaluation of structural performances of metakaolin based geopolymer concrete</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Metakaolin geopolymer concrete; no rice husk ash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2022_12</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Influence of rice husk ash substitution on some physical, mechanical and durability properties of the metakaolin-based geopolymer mortar</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Metakaolin-based geopolymer MORTAR (no OPC) in which RHA substitutes SAND (25/50/75% by wt), i.e. RHA is an aggregate/filler, not a cement replacement - out of scope for the OPC RHA-cement-replacement schema. Comp &amp; flexural data noted for reference: MK comp 45.68/40.47 &amp; flex 8.53/8.95; MK-RHA25 49.13/53.60 &amp; 8.44/8.81; MK-RHA50 50.12/53.65 &amp; 8.39/7.69; MK-RHA75 35.13/33.85 &amp; 7.18/5.80 (7d/28d, MPa).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2022_13</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Rice husk char as a potential electrode material for supercapacitors</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Energy storage / electrode material; no concrete or mortar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2022_15</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Highly active heterogeneous hydrogenation catalysts prepared from cobalt complexes and rice husk waste</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Catalysis/chemistry; no concrete or mortar.</t>
         </is>
       </c>
     </row>
@@ -13539,7 +23155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13820,6 +23436,56 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>10.1016/j.conbuildmat.2018.05.101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2022_01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hashmi/Ince et al. (2022). Factors affecting the CO2 emissions, cost efficiency and eco-strength efficiency of concrete containing rice husk ash: A database study. Construction and Building Materials, 332, 126905.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HIGH PRIORITY: compiled database of 1018 RHA-concrete data points from ~60 literature sources (Table 1 lists authors, number of data points, 28-day compressive strength, water:binder ratio, mix constituents, plasticizers). Obtain the article's Table 1 / supplementary database to bulk-import mix proportions + 28-day strength rows and the underlying source papers.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10.1016/j.conbuildmat.2022.126905</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2022_02</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mater/Bakhoum et al. (2022). Optimization of Green Concrete Containing Fly Ash and Rice Husk Ash ... Civil Engineering Journal, 8(12).</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ANN/EPR model trained on a compiled literature database of FA-or-RHA concrete (compressive strength at 3/7/28/60/90 days; split tensile, flexural, bond, modulus of elasticity, permeability). Ranges: binder 340-630 kg/m3, Fc28 20-105 MPa. Obtain its dataset/supplementary for individual mix rows.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10.28991/cej-2022-08-12-018</t>
         </is>
       </c>
     </row>

--- a/RHA_concrete_ML_dataset.xlsx
+++ b/RHA_concrete_ML_dataset.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z214"/>
+  <dimension ref="A1:Z282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -22376,6 +22376,7122 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Control (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>7</v>
+      </c>
+      <c r="R215" t="n">
+        <v>17.955</v>
+      </c>
+      <c r="S215" t="inlineStr"/>
+      <c r="T215" t="inlineStr"/>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Control (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>14</v>
+      </c>
+      <c r="R216" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Control (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P217" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>28</v>
+      </c>
+      <c r="R217" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="S217" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T217" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>C10 (10% RHA)</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="n">
+        <v>10</v>
+      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>7</v>
+      </c>
+      <c r="R218" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="S218" t="inlineStr"/>
+      <c r="T218" t="inlineStr"/>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>C10 (10% RHA)</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="n">
+        <v>10</v>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>14</v>
+      </c>
+      <c r="R219" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="S219" t="inlineStr"/>
+      <c r="T219" t="inlineStr"/>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>C10 (10% RHA)</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="n">
+        <v>10</v>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>28</v>
+      </c>
+      <c r="R220" t="n">
+        <v>30</v>
+      </c>
+      <c r="S220" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="T220" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>C15 (15% RHA)</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="n">
+        <v>15</v>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>7</v>
+      </c>
+      <c r="R221" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="S221" t="inlineStr"/>
+      <c r="T221" t="inlineStr"/>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>C15 (15% RHA)</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="n">
+        <v>15</v>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>14</v>
+      </c>
+      <c r="R222" t="n">
+        <v>29.09</v>
+      </c>
+      <c r="S222" t="inlineStr"/>
+      <c r="T222" t="inlineStr"/>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>C15 (15% RHA)</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="n">
+        <v>15</v>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>28</v>
+      </c>
+      <c r="R223" t="n">
+        <v>32</v>
+      </c>
+      <c r="S223" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="T223" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>C20 (20% RHA)</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="n">
+        <v>20</v>
+      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>7</v>
+      </c>
+      <c r="R224" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="S224" t="inlineStr"/>
+      <c r="T224" t="inlineStr"/>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>C20 (20% RHA)</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="n">
+        <v>20</v>
+      </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>14</v>
+      </c>
+      <c r="R225" t="n">
+        <v>30</v>
+      </c>
+      <c r="S225" t="inlineStr"/>
+      <c r="T225" t="inlineStr"/>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>C20 (20% RHA)</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="n">
+        <v>20</v>
+      </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>28</v>
+      </c>
+      <c r="R226" t="n">
+        <v>33</v>
+      </c>
+      <c r="S226" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="T226" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>C25 (25% RHA)</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="n">
+        <v>25</v>
+      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>7</v>
+      </c>
+      <c r="R227" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="S227" t="inlineStr"/>
+      <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>C25 (25% RHA)</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="n">
+        <v>25</v>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>14</v>
+      </c>
+      <c r="R228" t="n">
+        <v>30</v>
+      </c>
+      <c r="S228" t="inlineStr"/>
+      <c r="T228" t="inlineStr"/>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>C25 (25% RHA)</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="n">
+        <v>25</v>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>28</v>
+      </c>
+      <c r="R229" t="n">
+        <v>33</v>
+      </c>
+      <c r="S229" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T229" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>C30 (30% RHA)</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="n">
+        <v>30</v>
+      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>7</v>
+      </c>
+      <c r="R230" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="S230" t="inlineStr"/>
+      <c r="T230" t="inlineStr"/>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>C30 (30% RHA)</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="n">
+        <v>30</v>
+      </c>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>14</v>
+      </c>
+      <c r="R231" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="S231" t="inlineStr"/>
+      <c r="T231" t="inlineStr"/>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2023_01</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Effect of Rice Husk Ash on the Properties of Concrete</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Singh, Shukla</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>India (Gwalior, Madhya Pradesh; MITS Gwalior)</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Indian rice husk; husk incinerated (short combustion ~500-600C); silica content 84-92%. Specific mill not named.</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Concrete M20 grade (mix ratio 1:1.5:3, IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>C30 (30% RHA)</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="n">
+        <v>30</v>
+      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Plasticizer (polymer base) 1% by wt of cement; mix 1:1.5:3</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>28</v>
+      </c>
+      <c r="R232" t="n">
+        <v>29</v>
+      </c>
+      <c r="S232" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T232" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Compressive tabulated at 7/14/28 days (Table 6); flexural and split tensile tabulated at 28 days only (Table 7, '4 weeks').</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Comp MPa verbatim from Table 6; flexural &amp; split MPa verbatim from Table 7. Mix given only as ratio 1:1.5:3 with w/c 0.45 (no kg/m3 reported) -&gt; cement/agg kg/m3 left blank.</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr">
+        <is>
+          <t>OPC 53 grade. RHA replacement 0/10/15/20/25/30% (Control, C10-C30). w/c 0.45 constant; plasticizer (polymer base) 1% by weight of cement. kg/m3 not reported (ratio 1:1.5:3 only). Abstract intro mentions 2.5/5/7.5/10% but the actual specimen series is 10-30% (Table 4). Optimum ~25% by compressive strength.</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>Table 6 comp (7/14/28d): Control 17.955/25.91/28.5; C10 18.9/27.27/30; C15 20.16/29.09/32; C20 20.79/30.00/33; C25 20.79/30.00/33; C30 18.27/26.36/29. Table 7 (28d): flex/split Control 4.2/3.1; C10 4.27/3.1; C15 4.34/3.2; C20 4.34/3.2; C25 4.25/3.3; C30 4.2/3.1.</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>2023/01_Effect_of_Rice_Husk_Ash_on_the_Properties_of_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>M1 (control, 0% RHA, 0% BA)</t>
+        </is>
+      </c>
+      <c r="J233" t="n">
+        <v>348.32</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" t="n">
+        <v>790</v>
+      </c>
+      <c r="N233" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Bagasse ash 0; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>7</v>
+      </c>
+      <c r="R233" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="S233" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="T233" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>M1 (control, 0% RHA, 0% BA)</t>
+        </is>
+      </c>
+      <c r="J234" t="n">
+        <v>348.32</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="n">
+        <v>0</v>
+      </c>
+      <c r="M234" t="n">
+        <v>790</v>
+      </c>
+      <c r="N234" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Bagasse ash 0; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>14</v>
+      </c>
+      <c r="R234" t="n">
+        <v>38</v>
+      </c>
+      <c r="S234" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="T234" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>M1 (control, 0% RHA, 0% BA)</t>
+        </is>
+      </c>
+      <c r="J235" t="n">
+        <v>348.32</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0</v>
+      </c>
+      <c r="M235" t="n">
+        <v>790</v>
+      </c>
+      <c r="N235" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Bagasse ash 0; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>28</v>
+      </c>
+      <c r="R235" t="n">
+        <v>42</v>
+      </c>
+      <c r="S235" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="T235" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>M2 (30% RHA, 0% BA)</t>
+        </is>
+      </c>
+      <c r="J236" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K236" t="n">
+        <v>104.49</v>
+      </c>
+      <c r="L236" t="n">
+        <v>30</v>
+      </c>
+      <c r="M236" t="n">
+        <v>790</v>
+      </c>
+      <c r="N236" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Bagasse ash 0; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>7</v>
+      </c>
+      <c r="R236" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="S236" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="T236" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>M2 (30% RHA, 0% BA)</t>
+        </is>
+      </c>
+      <c r="J237" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K237" t="n">
+        <v>104.49</v>
+      </c>
+      <c r="L237" t="n">
+        <v>30</v>
+      </c>
+      <c r="M237" t="n">
+        <v>790</v>
+      </c>
+      <c r="N237" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Bagasse ash 0; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>14</v>
+      </c>
+      <c r="R237" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="S237" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="T237" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>M2 (30% RHA, 0% BA)</t>
+        </is>
+      </c>
+      <c r="J238" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K238" t="n">
+        <v>104.49</v>
+      </c>
+      <c r="L238" t="n">
+        <v>30</v>
+      </c>
+      <c r="M238" t="n">
+        <v>790</v>
+      </c>
+      <c r="N238" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Bagasse ash 0; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P238" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>28</v>
+      </c>
+      <c r="R238" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="S238" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T238" t="n">
+        <v>3</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>M3 (25% RHA, 5% BA)</t>
+        </is>
+      </c>
+      <c r="J239" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K239" t="n">
+        <v>87.08</v>
+      </c>
+      <c r="L239" t="n">
+        <v>25</v>
+      </c>
+      <c r="M239" t="n">
+        <v>790</v>
+      </c>
+      <c r="N239" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Bagasse ash 17.41 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>7</v>
+      </c>
+      <c r="R239" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="S239" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T239" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>M3 (25% RHA, 5% BA)</t>
+        </is>
+      </c>
+      <c r="J240" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K240" t="n">
+        <v>87.08</v>
+      </c>
+      <c r="L240" t="n">
+        <v>25</v>
+      </c>
+      <c r="M240" t="n">
+        <v>790</v>
+      </c>
+      <c r="N240" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Bagasse ash 17.41 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P240" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>14</v>
+      </c>
+      <c r="R240" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="S240" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T240" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>M3 (25% RHA, 5% BA)</t>
+        </is>
+      </c>
+      <c r="J241" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K241" t="n">
+        <v>87.08</v>
+      </c>
+      <c r="L241" t="n">
+        <v>25</v>
+      </c>
+      <c r="M241" t="n">
+        <v>790</v>
+      </c>
+      <c r="N241" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Bagasse ash 17.41 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>28</v>
+      </c>
+      <c r="R241" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="S241" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="T241" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>M4 (20% RHA, 10% BA)</t>
+        </is>
+      </c>
+      <c r="J242" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K242" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="L242" t="n">
+        <v>20</v>
+      </c>
+      <c r="M242" t="n">
+        <v>790</v>
+      </c>
+      <c r="N242" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Bagasse ash 34.8 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P242" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>7</v>
+      </c>
+      <c r="R242" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="S242" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="T242" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>M4 (20% RHA, 10% BA)</t>
+        </is>
+      </c>
+      <c r="J243" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K243" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="L243" t="n">
+        <v>20</v>
+      </c>
+      <c r="M243" t="n">
+        <v>790</v>
+      </c>
+      <c r="N243" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Bagasse ash 34.8 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P243" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>14</v>
+      </c>
+      <c r="R243" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="S243" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="T243" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>M4 (20% RHA, 10% BA)</t>
+        </is>
+      </c>
+      <c r="J244" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K244" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="L244" t="n">
+        <v>20</v>
+      </c>
+      <c r="M244" t="n">
+        <v>790</v>
+      </c>
+      <c r="N244" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Bagasse ash 34.8 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P244" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>28</v>
+      </c>
+      <c r="R244" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="S244" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="T244" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>M5 (15% RHA, 15% BA)</t>
+        </is>
+      </c>
+      <c r="J245" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K245" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="L245" t="n">
+        <v>15</v>
+      </c>
+      <c r="M245" t="n">
+        <v>790</v>
+      </c>
+      <c r="N245" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Bagasse ash 52.24 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P245" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>7</v>
+      </c>
+      <c r="R245" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="S245" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T245" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>M5 (15% RHA, 15% BA)</t>
+        </is>
+      </c>
+      <c r="J246" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K246" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="L246" t="n">
+        <v>15</v>
+      </c>
+      <c r="M246" t="n">
+        <v>790</v>
+      </c>
+      <c r="N246" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>Bagasse ash 52.24 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P246" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>14</v>
+      </c>
+      <c r="R246" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="S246" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T246" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>M5 (15% RHA, 15% BA)</t>
+        </is>
+      </c>
+      <c r="J247" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K247" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="L247" t="n">
+        <v>15</v>
+      </c>
+      <c r="M247" t="n">
+        <v>790</v>
+      </c>
+      <c r="N247" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Bagasse ash 52.24 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P247" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>28</v>
+      </c>
+      <c r="R247" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="S247" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="T247" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>M6 (10% RHA, 20% BA)</t>
+        </is>
+      </c>
+      <c r="J248" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K248" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="L248" t="n">
+        <v>10</v>
+      </c>
+      <c r="M248" t="n">
+        <v>790</v>
+      </c>
+      <c r="N248" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Bagasse ash 69.66 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P248" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>7</v>
+      </c>
+      <c r="R248" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="S248" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T248" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>M6 (10% RHA, 20% BA)</t>
+        </is>
+      </c>
+      <c r="J249" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K249" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="L249" t="n">
+        <v>10</v>
+      </c>
+      <c r="M249" t="n">
+        <v>790</v>
+      </c>
+      <c r="N249" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Bagasse ash 69.66 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P249" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>14</v>
+      </c>
+      <c r="R249" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="S249" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T249" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>M6 (10% RHA, 20% BA)</t>
+        </is>
+      </c>
+      <c r="J250" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K250" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="L250" t="n">
+        <v>10</v>
+      </c>
+      <c r="M250" t="n">
+        <v>790</v>
+      </c>
+      <c r="N250" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Bagasse ash 69.66 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P250" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>28</v>
+      </c>
+      <c r="R250" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="S250" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="T250" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>M7 (5% RHA, 25% BA)</t>
+        </is>
+      </c>
+      <c r="J251" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K251" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="L251" t="n">
+        <v>5</v>
+      </c>
+      <c r="M251" t="n">
+        <v>790</v>
+      </c>
+      <c r="N251" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Bagasse ash 87.08 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P251" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>7</v>
+      </c>
+      <c r="R251" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="S251" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T251" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>M7 (5% RHA, 25% BA)</t>
+        </is>
+      </c>
+      <c r="J252" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K252" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="L252" t="n">
+        <v>5</v>
+      </c>
+      <c r="M252" t="n">
+        <v>790</v>
+      </c>
+      <c r="N252" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Bagasse ash 87.08 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P252" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>14</v>
+      </c>
+      <c r="R252" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="S252" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T252" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>M7 (5% RHA, 25% BA)</t>
+        </is>
+      </c>
+      <c r="J253" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K253" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="L253" t="n">
+        <v>5</v>
+      </c>
+      <c r="M253" t="n">
+        <v>790</v>
+      </c>
+      <c r="N253" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Bagasse ash 87.08 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P253" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>28</v>
+      </c>
+      <c r="R253" t="n">
+        <v>31</v>
+      </c>
+      <c r="S253" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T253" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>M8 (0% RHA, 30% BA)</t>
+        </is>
+      </c>
+      <c r="J254" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K254" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" t="n">
+        <v>0</v>
+      </c>
+      <c r="M254" t="n">
+        <v>790</v>
+      </c>
+      <c r="N254" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Bagasse ash 104.49 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P254" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>7</v>
+      </c>
+      <c r="R254" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="S254" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="T254" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>M8 (0% RHA, 30% BA)</t>
+        </is>
+      </c>
+      <c r="J255" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K255" t="n">
+        <v>0</v>
+      </c>
+      <c r="L255" t="n">
+        <v>0</v>
+      </c>
+      <c r="M255" t="n">
+        <v>790</v>
+      </c>
+      <c r="N255" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Bagasse ash 104.49 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P255" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>14</v>
+      </c>
+      <c r="R255" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="S255" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T255" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2023_02</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>An Experimental Study on Concrete with Partial Replacement of Cement By Rice Husk Ash and Bagasse Ash</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Dhanalakshmi, Jeyaseela, Karthika, Leema Margret</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>India (Sivakasi, Tamil Nadu; P.S.R Engineering College)</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Not specified (agro-waste rice husk ash; pozzolanic). Used with sugarcane bagasse ash.</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>OPC+RHA+BA</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>M8 (0% RHA, 30% BA)</t>
+        </is>
+      </c>
+      <c r="J256" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="K256" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" t="n">
+        <v>0</v>
+      </c>
+      <c r="M256" t="n">
+        <v>790</v>
+      </c>
+      <c r="N256" t="n">
+        <v>1038.41</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Bagasse ash 104.49 kg/m3; SP Conplast 340 5.23 kg/m3; water 191.57 kg/m3</t>
+        </is>
+      </c>
+      <c r="P256" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>28</v>
+      </c>
+      <c r="R256" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="S256" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T256" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Compressive (Table 3), split tensile (Table 4) and flexural (Table 5) all tabulated at 7/14/28 days.</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>All kg/m3 verbatim from Table 2; all strengths verbatim from Tables 3-5.</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>Ternary binder: cement + RHA + sugarcane bagasse ash (BA). Total binder ~348.3 kg/m3 constant; for M2-M8 cement fixed at 243.82 (70%) and the remaining 30% split between RHA and BA. RHA% (of binder): M1 0; M2 30; M3 25; M4 20; M5 15; M6 10; M7 5; M8 0. w/c 0.55; SP Conplast 340 = 5.23 kg/m3; FA 790, CA 1038.41, water 191.57 kg/m3 for all mixes. M4 (20%RHA+10%BA) optimum. M6 14d flexural printed as '302' = OCR error for 3.02.</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>Table 2 (kg/m3): cement/RHA/BA per mix as below; FA 790, CA 1038.41, water 191.57, SP 5.23 all mixes. Table 3 comp 7/14/28d; Table 4 split 7/14/28d; Table 5 flexural 7/14/28d.</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>2023/02_An_Experimental_Study_on_Concrete_with_Partial_Replacement_of_Cement_By_Rice_Husk_Ash_and_Bagasse_Ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>CM (control, 0% RHA)</t>
+        </is>
+      </c>
+      <c r="J257" t="n">
+        <v>400</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="n">
+        <v>0</v>
+      </c>
+      <c r="M257" t="n">
+        <v>655</v>
+      </c>
+      <c r="N257" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P257" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>7</v>
+      </c>
+      <c r="R257" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="S257" t="inlineStr"/>
+      <c r="T257" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>CM (control, 0% RHA)</t>
+        </is>
+      </c>
+      <c r="J258" t="n">
+        <v>400</v>
+      </c>
+      <c r="K258" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" t="n">
+        <v>0</v>
+      </c>
+      <c r="M258" t="n">
+        <v>655</v>
+      </c>
+      <c r="N258" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P258" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>28</v>
+      </c>
+      <c r="R258" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="S258" t="inlineStr"/>
+      <c r="T258" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>RHA5 (5% RHA)</t>
+        </is>
+      </c>
+      <c r="J259" t="n">
+        <v>380</v>
+      </c>
+      <c r="K259" t="n">
+        <v>20</v>
+      </c>
+      <c r="L259" t="n">
+        <v>5</v>
+      </c>
+      <c r="M259" t="n">
+        <v>655</v>
+      </c>
+      <c r="N259" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P259" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>7</v>
+      </c>
+      <c r="R259" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="S259" t="inlineStr"/>
+      <c r="T259" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>RHA5 (5% RHA)</t>
+        </is>
+      </c>
+      <c r="J260" t="n">
+        <v>380</v>
+      </c>
+      <c r="K260" t="n">
+        <v>20</v>
+      </c>
+      <c r="L260" t="n">
+        <v>5</v>
+      </c>
+      <c r="M260" t="n">
+        <v>655</v>
+      </c>
+      <c r="N260" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>28</v>
+      </c>
+      <c r="R260" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="S260" t="inlineStr"/>
+      <c r="T260" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>RHA10 (10% RHA)</t>
+        </is>
+      </c>
+      <c r="J261" t="n">
+        <v>360</v>
+      </c>
+      <c r="K261" t="n">
+        <v>40</v>
+      </c>
+      <c r="L261" t="n">
+        <v>10</v>
+      </c>
+      <c r="M261" t="n">
+        <v>655</v>
+      </c>
+      <c r="N261" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>7</v>
+      </c>
+      <c r="R261" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="S261" t="inlineStr"/>
+      <c r="T261" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>RHA10 (10% RHA)</t>
+        </is>
+      </c>
+      <c r="J262" t="n">
+        <v>360</v>
+      </c>
+      <c r="K262" t="n">
+        <v>40</v>
+      </c>
+      <c r="L262" t="n">
+        <v>10</v>
+      </c>
+      <c r="M262" t="n">
+        <v>655</v>
+      </c>
+      <c r="N262" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>28</v>
+      </c>
+      <c r="R262" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="S262" t="inlineStr"/>
+      <c r="T262" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>RHA15 (15% RHA)</t>
+        </is>
+      </c>
+      <c r="J263" t="n">
+        <v>340</v>
+      </c>
+      <c r="K263" t="n">
+        <v>60</v>
+      </c>
+      <c r="L263" t="n">
+        <v>15</v>
+      </c>
+      <c r="M263" t="n">
+        <v>655</v>
+      </c>
+      <c r="N263" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P263" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>7</v>
+      </c>
+      <c r="R263" t="n">
+        <v>33.11</v>
+      </c>
+      <c r="S263" t="inlineStr"/>
+      <c r="T263" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>RHA15 (15% RHA)</t>
+        </is>
+      </c>
+      <c r="J264" t="n">
+        <v>340</v>
+      </c>
+      <c r="K264" t="n">
+        <v>60</v>
+      </c>
+      <c r="L264" t="n">
+        <v>15</v>
+      </c>
+      <c r="M264" t="n">
+        <v>655</v>
+      </c>
+      <c r="N264" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>28</v>
+      </c>
+      <c r="R264" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="S264" t="inlineStr"/>
+      <c r="T264" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>RHA20 (20% RHA)</t>
+        </is>
+      </c>
+      <c r="J265" t="n">
+        <v>320</v>
+      </c>
+      <c r="K265" t="n">
+        <v>80</v>
+      </c>
+      <c r="L265" t="n">
+        <v>20</v>
+      </c>
+      <c r="M265" t="n">
+        <v>655</v>
+      </c>
+      <c r="N265" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P265" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>7</v>
+      </c>
+      <c r="R265" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="S265" t="inlineStr"/>
+      <c r="T265" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>RHA20 (20% RHA)</t>
+        </is>
+      </c>
+      <c r="J266" t="n">
+        <v>320</v>
+      </c>
+      <c r="K266" t="n">
+        <v>80</v>
+      </c>
+      <c r="L266" t="n">
+        <v>20</v>
+      </c>
+      <c r="M266" t="n">
+        <v>655</v>
+      </c>
+      <c r="N266" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>28</v>
+      </c>
+      <c r="R266" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="S266" t="inlineStr"/>
+      <c r="T266" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>R15W5 (15% RHA + 5% WHA)</t>
+        </is>
+      </c>
+      <c r="J267" t="n">
+        <v>360</v>
+      </c>
+      <c r="K267" t="n">
+        <v>60</v>
+      </c>
+      <c r="L267" t="n">
+        <v>15</v>
+      </c>
+      <c r="M267" t="n">
+        <v>655</v>
+      </c>
+      <c r="N267" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Water hyacinth ash 20 kg/m3; PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q267" t="inlineStr"/>
+      <c r="R267" t="inlineStr"/>
+      <c r="S267" t="inlineStr"/>
+      <c r="T267" t="inlineStr"/>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>R15W10 (15% RHA + 10% WHA)</t>
+        </is>
+      </c>
+      <c r="J268" t="n">
+        <v>320</v>
+      </c>
+      <c r="K268" t="n">
+        <v>60</v>
+      </c>
+      <c r="L268" t="n">
+        <v>15</v>
+      </c>
+      <c r="M268" t="n">
+        <v>655</v>
+      </c>
+      <c r="N268" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Water hyacinth ash 40 kg/m3; PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q268" t="inlineStr"/>
+      <c r="R268" t="inlineStr"/>
+      <c r="S268" t="inlineStr"/>
+      <c r="T268" t="inlineStr"/>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>R15W15 (15% RHA + 15% WHA)</t>
+        </is>
+      </c>
+      <c r="J269" t="n">
+        <v>280</v>
+      </c>
+      <c r="K269" t="n">
+        <v>60</v>
+      </c>
+      <c r="L269" t="n">
+        <v>15</v>
+      </c>
+      <c r="M269" t="n">
+        <v>655</v>
+      </c>
+      <c r="N269" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Water hyacinth ash 60 kg/m3; PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q269" t="inlineStr"/>
+      <c r="R269" t="inlineStr"/>
+      <c r="S269" t="inlineStr"/>
+      <c r="T269" t="inlineStr"/>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2023_10</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Experimental investigation on properties of concrete with rice husk ash and water hyacinth ash</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Varghese, Vasudev R</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>India (Ernakulam, Kerala; Toc H Institute of Science and Technology)</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Not specified (by-product of thermal treatment of rice husks; pozzolanic). Used with water hyacinth ash (WHA).</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Concrete M30 grade (IS 10262:2019)</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>OPC+RHA (and OPC+RHA+WHA series)</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>R15W20 (15% RHA + 20% WHA)</t>
+        </is>
+      </c>
+      <c r="J270" t="n">
+        <v>240</v>
+      </c>
+      <c r="K270" t="n">
+        <v>60</v>
+      </c>
+      <c r="L270" t="n">
+        <v>15</v>
+      </c>
+      <c r="M270" t="n">
+        <v>655</v>
+      </c>
+      <c r="N270" t="n">
+        <v>1259</v>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Water hyacinth ash 80 kg/m3; PCE superplasticizer 0.4%; water 144 kg/m3</t>
+        </is>
+      </c>
+      <c r="P270" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q270" t="inlineStr"/>
+      <c r="R270" t="inlineStr"/>
+      <c r="S270" t="inlineStr"/>
+      <c r="T270" t="inlineStr"/>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>RHA-only series: compressive (Table 3) and split tensile (Table 5) at 7/28 days - clean. RHA+WHA combination series: mix proportions in Table 2, but strength Tables 4 &amp; 6 appear duplicated/mislabeled (values repeat the RHA-only series and contradict the stated optimum R15W10 = 33.22/43.1 MPa), so combo strengths left blank.</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>kg/m3 verbatim from Table 2. RHA-series comp from Table 3, split from Table 5 (verbatim). WHA-combo strengths NOT recorded (Tables 4 &amp; 6 internally inconsistent).</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>OPC 53 grade; M-sand fine aggregate; PCE superplasticizer 0.4%. w/c reported 0.42 (note: tabulated batch water 144 / cement 400 = 0.36; recorded as stated 0.42). Total binder 400 kg/m3 constant. RHA% of binder = RHA/400 (RHA5=5%, RHA10=10%, RHA15=15%, RHA20=20%). Combo mixes hold RHA at 15% (60 kg/m3) and add WHA 5/10/15/20%. Optimum: RHA15 (comp 42.73 MPa @28d); combination optimum R15W10. FA 655, CA 1259, water 144 kg/m3 all mixes.</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>Table 2 kg/m3 (cement/RHA/WHA): CM 400/0/0; RHA5 380/20/0; RHA10 360/40/0; RHA15 340/60/0; RHA20 320/80/0; R15W5 360/60/20; R15W10 320/60/40; R15W15 280/60/60; R15W20 240/60/80; FA 655, CA 1259, water 144 all. Table 3 comp (7/28d): CM 27.5/37.2; RHA5 28.6/37.9; RHA10 31.63/40.31; RHA15 33.11/42.73; RHA20 24.45/32.5. Table 5 split (7/28d): CM 2.24/2.97; RHA5 2.4/3.25; RHA10 2.52/3.56; RHA15 2.63/3.78; RHA20 2.12/2.71.</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>2023/10_Experimental_investigation_on_properties_of_concrete_with_rice_husk_ash_and_water_hyacinth_ash.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2023_13</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Effect of Rice-Husk as Replacement Cement on Mechanical Properties Concrete</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Abu Bakar, Abdul Kudus, Mustaffa, Jamadin, Abbas, Hassan, Kamaruddin</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Malaysia (Shah Alam, Selangor; Universiti Teknologi MARA)</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Local rice paddy, Malaysia; dried and furnace-burned to ash, then ground to required fineness.</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Concrete (target 30 MPa)</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Control (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="n">
+        <v>0</v>
+      </c>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>SP MasterGlenium Sky 8333 1% of cement; proportion ~1:2.05:2.50 (batch)</t>
+        </is>
+      </c>
+      <c r="P271" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>7</v>
+      </c>
+      <c r="R271" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="S271" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="T271" t="inlineStr"/>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>Compressive (Fig 4) and flexural (Fig 5) at 7/14/28 days; no split tensile. Values taken from the printed data labels on the figures.</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>Comp &amp; flexural MPa from Fig 4/Fig 5 data labels (printed numbers). Mix Table 1 values are mislabeled batch masses (cement 16.13 etc.), not true kg/m3 -&gt; cement/agg kg/m3 left blank; only proportion ratio and w/c retained.</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>OPC 42.5 (Tasek Cement); 10 mm coarse aggregate; SP MasterGlenium Sky 8333 at 1% of cement weight. RHA replacement 0/5/10/15%. w/c constant 0.54. Table 1 'kg/m3' values are actually batch masses (cement 16.13, RHA 0.81-2.42, fine 31.47-33.05, coarse 38.45-40.38, water 8.31-8.72) giving proportion ~1:2.05:2.50 with w/c 0.54; not recorded as kg/m3. Flexural at 5% (3.85 MPa) lowest; 10% RHA highest flexural (4.90 MPa). Compressive decreases with RHA (control 49.83 -&gt; 5% 35.15 -&gt; 15% 31.50 at 28d).</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>Fig 4 comp (7/14/28d): Control 40.80/45.86/49.83; 5%RHA 25.98/29.64/35.15; 10%RHA 24.60/28.75/33.00; 15%RHA 23.23/26.76/31.50. Fig 5 flexural (7/14/28d): Control 3.98/4.44/4.61; 5%RHA 3.75/3.80/3.85; 10%RHA 3.65/4.51/4.90; 15%RHA 2.65/4.50/4.70. Table 1 batch proportions ~1:2.05:2.50, w/c 0.54.</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>2023/13_Effect_of_Rice-Husk_as_Replacement_Cement_on_Mechanical_Properties_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2023_13</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Effect of Rice-Husk as Replacement Cement on Mechanical Properties Concrete</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Abu Bakar, Abdul Kudus, Mustaffa, Jamadin, Abbas, Hassan, Kamaruddin</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Malaysia (Shah Alam, Selangor; Universiti Teknologi MARA)</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Local rice paddy, Malaysia; dried and furnace-burned to ash, then ground to required fineness.</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Concrete (target 30 MPa)</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Control (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="n">
+        <v>0</v>
+      </c>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>SP MasterGlenium Sky 8333 1% of cement; proportion ~1:2.05:2.50 (batch)</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>14</v>
+      </c>
+      <c r="R272" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="S272" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="T272" t="inlineStr"/>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>Compressive (Fig 4) and flexural (Fig 5) at 7/14/28 days; no split tensile. Values taken from the printed data labels on the figures.</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>Comp &amp; flexural MPa from Fig 4/Fig 5 data labels (printed numbers). Mix Table 1 values are mislabeled batch masses (cement 16.13 etc.), not true kg/m3 -&gt; cement/agg kg/m3 left blank; only proportion ratio and w/c retained.</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>OPC 42.5 (Tasek Cement); 10 mm coarse aggregate; SP MasterGlenium Sky 8333 at 1% of cement weight. RHA replacement 0/5/10/15%. w/c constant 0.54. Table 1 'kg/m3' values are actually batch masses (cement 16.13, RHA 0.81-2.42, fine 31.47-33.05, coarse 38.45-40.38, water 8.31-8.72) giving proportion ~1:2.05:2.50 with w/c 0.54; not recorded as kg/m3. Flexural at 5% (3.85 MPa) lowest; 10% RHA highest flexural (4.90 MPa). Compressive decreases with RHA (control 49.83 -&gt; 5% 35.15 -&gt; 15% 31.50 at 28d).</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>Fig 4 comp (7/14/28d): Control 40.80/45.86/49.83; 5%RHA 25.98/29.64/35.15; 10%RHA 24.60/28.75/33.00; 15%RHA 23.23/26.76/31.50. Fig 5 flexural (7/14/28d): Control 3.98/4.44/4.61; 5%RHA 3.75/3.80/3.85; 10%RHA 3.65/4.51/4.90; 15%RHA 2.65/4.50/4.70. Table 1 batch proportions ~1:2.05:2.50, w/c 0.54.</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>2023/13_Effect_of_Rice-Husk_as_Replacement_Cement_on_Mechanical_Properties_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2023_13</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Effect of Rice-Husk as Replacement Cement on Mechanical Properties Concrete</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Abu Bakar, Abdul Kudus, Mustaffa, Jamadin, Abbas, Hassan, Kamaruddin</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Malaysia (Shah Alam, Selangor; Universiti Teknologi MARA)</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Local rice paddy, Malaysia; dried and furnace-burned to ash, then ground to required fineness.</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Concrete (target 30 MPa)</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Control (0% RHA)</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="n">
+        <v>0</v>
+      </c>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>SP MasterGlenium Sky 8333 1% of cement; proportion ~1:2.05:2.50 (batch)</t>
+        </is>
+      </c>
+      <c r="P273" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>28</v>
+      </c>
+      <c r="R273" t="n">
+        <v>49.83</v>
+      </c>
+      <c r="S273" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="T273" t="inlineStr"/>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Compressive (Fig 4) and flexural (Fig 5) at 7/14/28 days; no split tensile. Values taken from the printed data labels on the figures.</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>Comp &amp; flexural MPa from Fig 4/Fig 5 data labels (printed numbers). Mix Table 1 values are mislabeled batch masses (cement 16.13 etc.), not true kg/m3 -&gt; cement/agg kg/m3 left blank; only proportion ratio and w/c retained.</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>OPC 42.5 (Tasek Cement); 10 mm coarse aggregate; SP MasterGlenium Sky 8333 at 1% of cement weight. RHA replacement 0/5/10/15%. w/c constant 0.54. Table 1 'kg/m3' values are actually batch masses (cement 16.13, RHA 0.81-2.42, fine 31.47-33.05, coarse 38.45-40.38, water 8.31-8.72) giving proportion ~1:2.05:2.50 with w/c 0.54; not recorded as kg/m3. Flexural at 5% (3.85 MPa) lowest; 10% RHA highest flexural (4.90 MPa). Compressive decreases with RHA (control 49.83 -&gt; 5% 35.15 -&gt; 15% 31.50 at 28d).</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>Fig 4 comp (7/14/28d): Control 40.80/45.86/49.83; 5%RHA 25.98/29.64/35.15; 10%RHA 24.60/28.75/33.00; 15%RHA 23.23/26.76/31.50. Fig 5 flexural (7/14/28d): Control 3.98/4.44/4.61; 5%RHA 3.75/3.80/3.85; 10%RHA 3.65/4.51/4.90; 15%RHA 2.65/4.50/4.70. Table 1 batch proportions ~1:2.05:2.50, w/c 0.54.</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>2023/13_Effect_of_Rice-Husk_as_Replacement_Cement_on_Mechanical_Properties_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2023_13</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Effect of Rice-Husk as Replacement Cement on Mechanical Properties Concrete</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Abu Bakar, Abdul Kudus, Mustaffa, Jamadin, Abbas, Hassan, Kamaruddin</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Malaysia (Shah Alam, Selangor; Universiti Teknologi MARA)</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Local rice paddy, Malaysia; dried and furnace-burned to ash, then ground to required fineness.</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Concrete (target 30 MPa)</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>5% RHA</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="n">
+        <v>5</v>
+      </c>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>SP MasterGlenium Sky 8333 1% of cement; proportion ~1:2.05:2.50 (batch)</t>
+        </is>
+      </c>
+      <c r="P274" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>7</v>
+      </c>
+      <c r="R274" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="S274" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T274" t="inlineStr"/>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>Compressive (Fig 4) and flexural (Fig 5) at 7/14/28 days; no split tensile. Values taken from the printed data labels on the figures.</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>Comp &amp; flexural MPa from Fig 4/Fig 5 data labels (printed numbers). Mix Table 1 values are mislabeled batch masses (cement 16.13 etc.), not true kg/m3 -&gt; cement/agg kg/m3 left blank; only proportion ratio and w/c retained.</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>OPC 42.5 (Tasek Cement); 10 mm coarse aggregate; SP MasterGlenium Sky 8333 at 1% of cement weight. RHA replacement 0/5/10/15%. w/c constant 0.54. Table 1 'kg/m3' values are actually batch masses (cement 16.13, RHA 0.81-2.42, fine 31.47-33.05, coarse 38.45-40.38, water 8.31-8.72) giving proportion ~1:2.05:2.50 with w/c 0.54; not recorded as kg/m3. Flexural at 5% (3.85 MPa) lowest; 10% RHA highest flexural (4.90 MPa). Compressive decreases with RHA (control 49.83 -&gt; 5% 35.15 -&gt; 15% 31.50 at 28d).</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>Fig 4 comp (7/14/28d): Control 40.80/45.86/49.83; 5%RHA 25.98/29.64/35.15; 10%RHA 24.60/28.75/33.00; 15%RHA 23.23/26.76/31.50. Fig 5 flexural (7/14/28d): Control 3.98/4.44/4.61; 5%RHA 3.75/3.80/3.85; 10%RHA 3.65/4.51/4.90; 15%RHA 2.65/4.50/4.70. Table 1 batch proportions ~1:2.05:2.50, w/c 0.54.</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>2023/13_Effect_of_Rice-Husk_as_Replacement_Cement_on_Mechanical_Properties_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2023_13</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Effect of Rice-Husk as Replacement Cement on Mechanical Properties Concrete</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Abu Bakar, Abdul Kudus, Mustaffa, Jamadin, Abbas, Hassan, Kamaruddin</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Malaysia (Shah Alam, Selangor; Universiti Teknologi MARA)</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Local rice paddy, Malaysia; dried and furnace-burned to ash, then ground to required fineness.</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Concrete (target 30 MPa)</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>5% RHA</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="n">
+        <v>5</v>
+      </c>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>SP MasterGlenium Sky 8333 1% of cement; proportion ~1:2.05:2.50 (batch)</t>
+        </is>
+      </c>
+      <c r="P275" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>14</v>
+      </c>
+      <c r="R275" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="S275" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T275" t="inlineStr"/>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>Compressive (Fig 4) and flexural (Fig 5) at 7/14/28 days; no split tensile. Values taken from the printed data labels on the figures.</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>Comp &amp; flexural MPa from Fig 4/Fig 5 data labels (printed numbers). Mix Table 1 values are mislabeled batch masses (cement 16.13 etc.), not true kg/m3 -&gt; cement/agg kg/m3 left blank; only proportion ratio and w/c retained.</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>OPC 42.5 (Tasek Cement); 10 mm coarse aggregate; SP MasterGlenium Sky 8333 at 1% of cement weight. RHA replacement 0/5/10/15%. w/c constant 0.54. Table 1 'kg/m3' values are actually batch masses (cement 16.13, RHA 0.81-2.42, fine 31.47-33.05, coarse 38.45-40.38, water 8.31-8.72) giving proportion ~1:2.05:2.50 with w/c 0.54; not recorded as kg/m3. Flexural at 5% (3.85 MPa) lowest; 10% RHA highest flexural (4.90 MPa). Compressive decreases with RHA (control 49.83 -&gt; 5% 35.15 -&gt; 15% 31.50 at 28d).</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>Fig 4 comp (7/14/28d): Control 40.80/45.86/49.83; 5%RHA 25.98/29.64/35.15; 10%RHA 24.60/28.75/33.00; 15%RHA 23.23/26.76/31.50. Fig 5 flexural (7/14/28d): Control 3.98/4.44/4.61; 5%RHA 3.75/3.80/3.85; 10%RHA 3.65/4.51/4.90; 15%RHA 2.65/4.50/4.70. Table 1 batch proportions ~1:2.05:2.50, w/c 0.54.</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>2023/13_Effect_of_Rice-Husk_as_Replacement_Cement_on_Mechanical_Properties_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2023_13</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Effect of Rice-Husk as Replacement Cement on Mechanical Properties Concrete</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Abu Bakar, Abdul Kudus, Mustaffa, Jamadin, Abbas, Hassan, Kamaruddin</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Malaysia (Shah Alam, Selangor; Universiti Teknologi MARA)</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Local rice paddy, Malaysia; dried and furnace-burned to ash, then ground to required fineness.</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Concrete (target 30 MPa)</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>5% RHA</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="n">
+        <v>5</v>
+      </c>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>SP MasterGlenium Sky 8333 1% of cement; proportion ~1:2.05:2.50 (batch)</t>
+        </is>
+      </c>
+      <c r="P276" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>28</v>
+      </c>
+      <c r="R276" t="n">
+        <v>35.15</v>
+      </c>
+      <c r="S276" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T276" t="inlineStr"/>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>Compressive (Fig 4) and flexural (Fig 5) at 7/14/28 days; no split tensile. Values taken from the printed data labels on the figures.</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>Comp &amp; flexural MPa from Fig 4/Fig 5 data labels (printed numbers). Mix Table 1 values are mislabeled batch masses (cement 16.13 etc.), not true kg/m3 -&gt; cement/agg kg/m3 left blank; only proportion ratio and w/c retained.</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>OPC 42.5 (Tasek Cement); 10 mm coarse aggregate; SP MasterGlenium Sky 8333 at 1% of cement weight. RHA replacement 0/5/10/15%. w/c constant 0.54. Table 1 'kg/m3' values are actually batch masses (cement 16.13, RHA 0.81-2.42, fine 31.47-33.05, coarse 38.45-40.38, water 8.31-8.72) giving proportion ~1:2.05:2.50 with w/c 0.54; not recorded as kg/m3. Flexural at 5% (3.85 MPa) lowest; 10% RHA highest flexural (4.90 MPa). Compressive decreases with RHA (control 49.83 -&gt; 5% 35.15 -&gt; 15% 31.50 at 28d).</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>Fig 4 comp (7/14/28d): Control 40.80/45.86/49.83; 5%RHA 25.98/29.64/35.15; 10%RHA 24.60/28.75/33.00; 15%RHA 23.23/26.76/31.50. Fig 5 flexural (7/14/28d): Control 3.98/4.44/4.61; 5%RHA 3.75/3.80/3.85; 10%RHA 3.65/4.51/4.90; 15%RHA 2.65/4.50/4.70. Table 1 batch proportions ~1:2.05:2.50, w/c 0.54.</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>2023/13_Effect_of_Rice-Husk_as_Replacement_Cement_on_Mechanical_Properties_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2023_13</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Effect of Rice-Husk as Replacement Cement on Mechanical Properties Concrete</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Abu Bakar, Abdul Kudus, Mustaffa, Jamadin, Abbas, Hassan, Kamaruddin</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Malaysia (Shah Alam, Selangor; Universiti Teknologi MARA)</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Local rice paddy, Malaysia; dried and furnace-burned to ash, then ground to required fineness.</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Concrete (target 30 MPa)</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>10% RHA</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="n">
+        <v>10</v>
+      </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>SP MasterGlenium Sky 8333 1% of cement; proportion ~1:2.05:2.50 (batch)</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>7</v>
+      </c>
+      <c r="R277" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="S277" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T277" t="inlineStr"/>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>Compressive (Fig 4) and flexural (Fig 5) at 7/14/28 days; no split tensile. Values taken from the printed data labels on the figures.</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>Comp &amp; flexural MPa from Fig 4/Fig 5 data labels (printed numbers). Mix Table 1 values are mislabeled batch masses (cement 16.13 etc.), not true kg/m3 -&gt; cement/agg kg/m3 left blank; only proportion ratio and w/c retained.</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>OPC 42.5 (Tasek Cement); 10 mm coarse aggregate; SP MasterGlenium Sky 8333 at 1% of cement weight. RHA replacement 0/5/10/15%. w/c constant 0.54. Table 1 'kg/m3' values are actually batch masses (cement 16.13, RHA 0.81-2.42, fine 31.47-33.05, coarse 38.45-40.38, water 8.31-8.72) giving proportion ~1:2.05:2.50 with w/c 0.54; not recorded as kg/m3. Flexural at 5% (3.85 MPa) lowest; 10% RHA highest flexural (4.90 MPa). Compressive decreases with RHA (control 49.83 -&gt; 5% 35.15 -&gt; 15% 31.50 at 28d).</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>Fig 4 comp (7/14/28d): Control 40.80/45.86/49.83; 5%RHA 25.98/29.64/35.15; 10%RHA 24.60/28.75/33.00; 15%RHA 23.23/26.76/31.50. Fig 5 flexural (7/14/28d): Control 3.98/4.44/4.61; 5%RHA 3.75/3.80/3.85; 10%RHA 3.65/4.51/4.90; 15%RHA 2.65/4.50/4.70. Table 1 batch proportions ~1:2.05:2.50, w/c 0.54.</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>2023/13_Effect_of_Rice-Husk_as_Replacement_Cement_on_Mechanical_Properties_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2023_13</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Effect of Rice-Husk as Replacement Cement on Mechanical Properties Concrete</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Abu Bakar, Abdul Kudus, Mustaffa, Jamadin, Abbas, Hassan, Kamaruddin</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Malaysia (Shah Alam, Selangor; Universiti Teknologi MARA)</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Local rice paddy, Malaysia; dried and furnace-burned to ash, then ground to required fineness.</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Concrete (target 30 MPa)</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>10% RHA</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="n">
+        <v>10</v>
+      </c>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>SP MasterGlenium Sky 8333 1% of cement; proportion ~1:2.05:2.50 (batch)</t>
+        </is>
+      </c>
+      <c r="P278" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>14</v>
+      </c>
+      <c r="R278" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="S278" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="T278" t="inlineStr"/>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>Compressive (Fig 4) and flexural (Fig 5) at 7/14/28 days; no split tensile. Values taken from the printed data labels on the figures.</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>Comp &amp; flexural MPa from Fig 4/Fig 5 data labels (printed numbers). Mix Table 1 values are mislabeled batch masses (cement 16.13 etc.), not true kg/m3 -&gt; cement/agg kg/m3 left blank; only proportion ratio and w/c retained.</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>OPC 42.5 (Tasek Cement); 10 mm coarse aggregate; SP MasterGlenium Sky 8333 at 1% of cement weight. RHA replacement 0/5/10/15%. w/c constant 0.54. Table 1 'kg/m3' values are actually batch masses (cement 16.13, RHA 0.81-2.42, fine 31.47-33.05, coarse 38.45-40.38, water 8.31-8.72) giving proportion ~1:2.05:2.50 with w/c 0.54; not recorded as kg/m3. Flexural at 5% (3.85 MPa) lowest; 10% RHA highest flexural (4.90 MPa). Compressive decreases with RHA (control 49.83 -&gt; 5% 35.15 -&gt; 15% 31.50 at 28d).</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>Fig 4 comp (7/14/28d): Control 40.80/45.86/49.83; 5%RHA 25.98/29.64/35.15; 10%RHA 24.60/28.75/33.00; 15%RHA 23.23/26.76/31.50. Fig 5 flexural (7/14/28d): Control 3.98/4.44/4.61; 5%RHA 3.75/3.80/3.85; 10%RHA 3.65/4.51/4.90; 15%RHA 2.65/4.50/4.70. Table 1 batch proportions ~1:2.05:2.50, w/c 0.54.</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>2023/13_Effect_of_Rice-Husk_as_Replacement_Cement_on_Mechanical_Properties_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2023_13</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Effect of Rice-Husk as Replacement Cement on Mechanical Properties Concrete</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Abu Bakar, Abdul Kudus, Mustaffa, Jamadin, Abbas, Hassan, Kamaruddin</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Malaysia (Shah Alam, Selangor; Universiti Teknologi MARA)</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Local rice paddy, Malaysia; dried and furnace-burned to ash, then ground to required fineness.</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Concrete (target 30 MPa)</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>10% RHA</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="n">
+        <v>10</v>
+      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>SP MasterGlenium Sky 8333 1% of cement; proportion ~1:2.05:2.50 (batch)</t>
+        </is>
+      </c>
+      <c r="P279" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>28</v>
+      </c>
+      <c r="R279" t="n">
+        <v>33</v>
+      </c>
+      <c r="S279" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T279" t="inlineStr"/>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Compressive (Fig 4) and flexural (Fig 5) at 7/14/28 days; no split tensile. Values taken from the printed data labels on the figures.</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>Comp &amp; flexural MPa from Fig 4/Fig 5 data labels (printed numbers). Mix Table 1 values are mislabeled batch masses (cement 16.13 etc.), not true kg/m3 -&gt; cement/agg kg/m3 left blank; only proportion ratio and w/c retained.</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>OPC 42.5 (Tasek Cement); 10 mm coarse aggregate; SP MasterGlenium Sky 8333 at 1% of cement weight. RHA replacement 0/5/10/15%. w/c constant 0.54. Table 1 'kg/m3' values are actually batch masses (cement 16.13, RHA 0.81-2.42, fine 31.47-33.05, coarse 38.45-40.38, water 8.31-8.72) giving proportion ~1:2.05:2.50 with w/c 0.54; not recorded as kg/m3. Flexural at 5% (3.85 MPa) lowest; 10% RHA highest flexural (4.90 MPa). Compressive decreases with RHA (control 49.83 -&gt; 5% 35.15 -&gt; 15% 31.50 at 28d).</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>Fig 4 comp (7/14/28d): Control 40.80/45.86/49.83; 5%RHA 25.98/29.64/35.15; 10%RHA 24.60/28.75/33.00; 15%RHA 23.23/26.76/31.50. Fig 5 flexural (7/14/28d): Control 3.98/4.44/4.61; 5%RHA 3.75/3.80/3.85; 10%RHA 3.65/4.51/4.90; 15%RHA 2.65/4.50/4.70. Table 1 batch proportions ~1:2.05:2.50, w/c 0.54.</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>2023/13_Effect_of_Rice-Husk_as_Replacement_Cement_on_Mechanical_Properties_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2023_13</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Effect of Rice-Husk as Replacement Cement on Mechanical Properties Concrete</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Abu Bakar, Abdul Kudus, Mustaffa, Jamadin, Abbas, Hassan, Kamaruddin</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Malaysia (Shah Alam, Selangor; Universiti Teknologi MARA)</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Local rice paddy, Malaysia; dried and furnace-burned to ash, then ground to required fineness.</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Concrete (target 30 MPa)</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>15% RHA</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="n">
+        <v>15</v>
+      </c>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>SP MasterGlenium Sky 8333 1% of cement; proportion ~1:2.05:2.50 (batch)</t>
+        </is>
+      </c>
+      <c r="P280" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>7</v>
+      </c>
+      <c r="R280" t="n">
+        <v>23.23</v>
+      </c>
+      <c r="S280" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T280" t="inlineStr"/>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>Compressive (Fig 4) and flexural (Fig 5) at 7/14/28 days; no split tensile. Values taken from the printed data labels on the figures.</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>Comp &amp; flexural MPa from Fig 4/Fig 5 data labels (printed numbers). Mix Table 1 values are mislabeled batch masses (cement 16.13 etc.), not true kg/m3 -&gt; cement/agg kg/m3 left blank; only proportion ratio and w/c retained.</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>OPC 42.5 (Tasek Cement); 10 mm coarse aggregate; SP MasterGlenium Sky 8333 at 1% of cement weight. RHA replacement 0/5/10/15%. w/c constant 0.54. Table 1 'kg/m3' values are actually batch masses (cement 16.13, RHA 0.81-2.42, fine 31.47-33.05, coarse 38.45-40.38, water 8.31-8.72) giving proportion ~1:2.05:2.50 with w/c 0.54; not recorded as kg/m3. Flexural at 5% (3.85 MPa) lowest; 10% RHA highest flexural (4.90 MPa). Compressive decreases with RHA (control 49.83 -&gt; 5% 35.15 -&gt; 15% 31.50 at 28d).</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>Fig 4 comp (7/14/28d): Control 40.80/45.86/49.83; 5%RHA 25.98/29.64/35.15; 10%RHA 24.60/28.75/33.00; 15%RHA 23.23/26.76/31.50. Fig 5 flexural (7/14/28d): Control 3.98/4.44/4.61; 5%RHA 3.75/3.80/3.85; 10%RHA 3.65/4.51/4.90; 15%RHA 2.65/4.50/4.70. Table 1 batch proportions ~1:2.05:2.50, w/c 0.54.</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>2023/13_Effect_of_Rice-Husk_as_Replacement_Cement_on_Mechanical_Properties_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2023_13</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Effect of Rice-Husk as Replacement Cement on Mechanical Properties Concrete</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Abu Bakar, Abdul Kudus, Mustaffa, Jamadin, Abbas, Hassan, Kamaruddin</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Malaysia (Shah Alam, Selangor; Universiti Teknologi MARA)</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Local rice paddy, Malaysia; dried and furnace-burned to ash, then ground to required fineness.</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Concrete (target 30 MPa)</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>15% RHA</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="n">
+        <v>15</v>
+      </c>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>SP MasterGlenium Sky 8333 1% of cement; proportion ~1:2.05:2.50 (batch)</t>
+        </is>
+      </c>
+      <c r="P281" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>14</v>
+      </c>
+      <c r="R281" t="n">
+        <v>26.76</v>
+      </c>
+      <c r="S281" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T281" t="inlineStr"/>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>Compressive (Fig 4) and flexural (Fig 5) at 7/14/28 days; no split tensile. Values taken from the printed data labels on the figures.</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>Comp &amp; flexural MPa from Fig 4/Fig 5 data labels (printed numbers). Mix Table 1 values are mislabeled batch masses (cement 16.13 etc.), not true kg/m3 -&gt; cement/agg kg/m3 left blank; only proportion ratio and w/c retained.</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>OPC 42.5 (Tasek Cement); 10 mm coarse aggregate; SP MasterGlenium Sky 8333 at 1% of cement weight. RHA replacement 0/5/10/15%. w/c constant 0.54. Table 1 'kg/m3' values are actually batch masses (cement 16.13, RHA 0.81-2.42, fine 31.47-33.05, coarse 38.45-40.38, water 8.31-8.72) giving proportion ~1:2.05:2.50 with w/c 0.54; not recorded as kg/m3. Flexural at 5% (3.85 MPa) lowest; 10% RHA highest flexural (4.90 MPa). Compressive decreases with RHA (control 49.83 -&gt; 5% 35.15 -&gt; 15% 31.50 at 28d).</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>Fig 4 comp (7/14/28d): Control 40.80/45.86/49.83; 5%RHA 25.98/29.64/35.15; 10%RHA 24.60/28.75/33.00; 15%RHA 23.23/26.76/31.50. Fig 5 flexural (7/14/28d): Control 3.98/4.44/4.61; 5%RHA 3.75/3.80/3.85; 10%RHA 3.65/4.51/4.90; 15%RHA 2.65/4.50/4.70. Table 1 batch proportions ~1:2.05:2.50, w/c 0.54.</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>2023/13_Effect_of_Rice-Husk_as_Replacement_Cement_on_Mechanical_Properties_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2023_13</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Effect of Rice-Husk as Replacement Cement on Mechanical Properties Concrete</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Abu Bakar, Abdul Kudus, Mustaffa, Jamadin, Abbas, Hassan, Kamaruddin</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Malaysia (Shah Alam, Selangor; Universiti Teknologi MARA)</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Local rice paddy, Malaysia; dried and furnace-burned to ash, then ground to required fineness.</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Concrete (target 30 MPa)</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>OPC+RHA</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>15% RHA</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="n">
+        <v>15</v>
+      </c>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>SP MasterGlenium Sky 8333 1% of cement; proportion ~1:2.05:2.50 (batch)</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>28</v>
+      </c>
+      <c r="R282" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="S282" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T282" t="inlineStr"/>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>Compressive (Fig 4) and flexural (Fig 5) at 7/14/28 days; no split tensile. Values taken from the printed data labels on the figures.</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>Comp &amp; flexural MPa from Fig 4/Fig 5 data labels (printed numbers). Mix Table 1 values are mislabeled batch masses (cement 16.13 etc.), not true kg/m3 -&gt; cement/agg kg/m3 left blank; only proportion ratio and w/c retained.</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>OPC 42.5 (Tasek Cement); 10 mm coarse aggregate; SP MasterGlenium Sky 8333 at 1% of cement weight. RHA replacement 0/5/10/15%. w/c constant 0.54. Table 1 'kg/m3' values are actually batch masses (cement 16.13, RHA 0.81-2.42, fine 31.47-33.05, coarse 38.45-40.38, water 8.31-8.72) giving proportion ~1:2.05:2.50 with w/c 0.54; not recorded as kg/m3. Flexural at 5% (3.85 MPa) lowest; 10% RHA highest flexural (4.90 MPa). Compressive decreases with RHA (control 49.83 -&gt; 5% 35.15 -&gt; 15% 31.50 at 28d).</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>Fig 4 comp (7/14/28d): Control 40.80/45.86/49.83; 5%RHA 25.98/29.64/35.15; 10%RHA 24.60/28.75/33.00; 15%RHA 23.23/26.76/31.50. Fig 5 flexural (7/14/28d): Control 3.98/4.44/4.61; 5%RHA 3.75/3.80/3.85; 10%RHA 3.65/4.51/4.90; 15%RHA 2.65/4.50/4.70. Table 1 batch proportions ~1:2.05:2.50, w/c 0.54.</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>2023/13_Effect_of_Rice-Husk_as_Replacement_Cement_on_Mechanical_Properties_Concrete.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22613,7 +29729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23141,6 +30257,226 @@
       <c r="D26" t="inlineStr">
         <is>
           <t>Catalysis/chemistry; no concrete or mortar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2023_03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Development of sustainable high performance geopolymer concrete and mortar using agricultural biomass - A strength performance and sustainability analysis</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Alkali-activated GEOPOLYMER concrete and mortar (precursors silica fume / GGBS / RHA; no OPC) combined with ANN / multi-linear / swarm regression modeling. RHA is a geopolymer precursor, not an OPC cement replacement - out of scope for the OPC RHA-cement schema. Contains experimental geopolymer mix+strength data that could be mined separately if no-OPC systems are later included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2023_04</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>RETRACTED: Experimental study on the properties of ultra-high-strength geopolymer concrete with polypropylene fibers and ...</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>RETRACTED article; also a no-OPC geopolymer concrete with polypropylene fibers. Excluded on both grounds (retraction + out-of-scope binder).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2023_05</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Phytochemical and Nutrient Composition of Rice Husks</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Food/agricultural chemistry of rice husks (phytochemical and nutrient composition); no concrete or mortar, no mix or strength data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2023_06</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Utilizing rice husk ash as a bio-waste material in geopolymer composites with aluminium oxide</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No-OPC geopolymer composite (RHA + aluminium oxide); RHA used as a silica/bio-waste precursor in a geopolymer matrix, not as OPC cement replacement in concrete - out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2023_07</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Effect of Bio-Cementation with Rice Husk Ash on Permeability of Silty Sand</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Geotechnical soil stabilization (bio-cementation / MICP of silty sand) using RHA; measures permeability of soil, not concrete/mortar mix design or strength - out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2023_08</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Potential utilization of natural zeolite, fly ash and rice husk ash for geopolymer concrete production</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No-OPC GEOPOLYMER concrete from natural zeolite + fly ash + RHA; mix designed on Al/Si ratio (1:2 to 1:4), max comp ~16.74 MPa. RHA is a geopolymer precursor, not an OPC cement replacement - out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2023_09</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>A Study on Characteristics of Brake Pad Composite Materials by Varying the Composition of Epoxy, Rice Husk, Al2O3 and Fe2O3</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Epoxy/friction brake-pad composite material; no concrete or mortar, no cementitious mix or strength data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2023_11</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Experimental investigation on marble dust, rice husk ash and fly ash based geopolymer brick</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>No-OPC geopolymer BRICK (marble dust + RHA + fly ash); masonry-brick product, not OPC concrete/mortar with RHA cement replacement - out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2023_12</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Performance of bituminous paving mixtures containing recycled concrete aggregate, fly ash and rice husk ash: A probabilistic ...</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Asphalt / bituminous paving mixture (RCA + fly ash + RHA as filler); no cementitious concrete mix or compressive/flexural/split strengths - out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2023_14</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Utilization of Fly Ash and Rice Husk Ash in Cold Mix Asphalt as Filler</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Cold-mix asphalt with fly ash and RHA used as mineral filler; bituminous material, not OPC concrete/mortar - out of scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2023_15</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Central composite design application in the optimization of the effect of pumice stone on lightweight concrete properties</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Lightweight concrete with pumice stone coarse-aggregate replacement (RSM/CCD optimization). RHA appears only as a literature citation, not in the experimental mixes - no RHA data to extract.</t>
         </is>
       </c>
     </row>
